--- a/grupos/4ALCV - Estadisticos 20222.xlsx
+++ b/grupos/4ALCV - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="156">
   <si>
     <t>Materia</t>
   </si>
@@ -201,21 +201,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
+    <t>Desc Desc Desc</t>
+  </si>
+  <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
     <t>Gomez Lopez Javier</t>
   </si>
   <si>
-    <t>Polanco Domínguez Rosa María</t>
-  </si>
-  <si>
     <t>Rivera Serra Alma Lilian</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
-  </si>
-  <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
@@ -252,241 +252,241 @@
     <t>GARCIA</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>RUGERIO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>TENTZOHUA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>LAGUNES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>VALIENTE</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>QUIÑONES</t>
+  </si>
+  <si>
+    <t>MENA</t>
+  </si>
+  <si>
+    <t>LEÓN</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>CRISTAL YOSELIN</t>
+  </si>
+  <si>
+    <t>REYLI</t>
+  </si>
+  <si>
+    <t>EVELYN JOHANA</t>
+  </si>
+  <si>
+    <t>MARYFER</t>
+  </si>
+  <si>
+    <t>YARED</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>MIROSLAVA</t>
+  </si>
+  <si>
+    <t>BERENICE</t>
+  </si>
+  <si>
+    <t>MARIA TERESA</t>
+  </si>
+  <si>
+    <t>VANESSA AMAIRANY</t>
+  </si>
+  <si>
+    <t>REGINA ISABEL</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>DIANA IVONNE</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>JOSE ISAAC</t>
+  </si>
+  <si>
+    <t>FATIMA MARILYN</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>ITZEL ABIGAIL</t>
+  </si>
+  <si>
+    <t>INGRID AMERICA</t>
+  </si>
+  <si>
+    <t>JAIME</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>LUIS REY</t>
+  </si>
+  <si>
+    <t>ALONDRA YURIDIA</t>
+  </si>
+  <si>
+    <t>KIMBERLY</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>ALMA KAREN</t>
+  </si>
+  <si>
+    <t>GABRIELA</t>
+  </si>
+  <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>RUBI</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>FLOR GUADALUPE</t>
+  </si>
+  <si>
     <t>GUILLEN</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>MANZANET</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>RUGERIO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SANJUAN</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>TENTZOHUA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>VALIENTE</t>
-  </si>
-  <si>
     <t>LINARES</t>
   </si>
   <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>BRETON</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
     <t>ANDRADE</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>QUIÑONES</t>
-  </si>
-  <si>
-    <t>MENA</t>
-  </si>
-  <si>
-    <t>LEÓN</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>CRISTAL YOSELIN</t>
-  </si>
-  <si>
-    <t>REYLI</t>
-  </si>
-  <si>
-    <t>EVELYN JOHANA</t>
-  </si>
-  <si>
-    <t>MARYFER</t>
-  </si>
-  <si>
-    <t>YARED</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
-  </si>
-  <si>
-    <t>BERENICE</t>
-  </si>
-  <si>
     <t>EDITH</t>
   </si>
   <si>
-    <t>MARIA TERESA</t>
-  </si>
-  <si>
-    <t>VANESSA AMAIRANY</t>
-  </si>
-  <si>
-    <t>REGINA ISABEL</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
     <t>JADE EMILY</t>
-  </si>
-  <si>
-    <t>DIANA IVONNE</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>JOSE ISAAC</t>
-  </si>
-  <si>
-    <t>FATIMA MARILYN</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>ITZEL ABIGAIL</t>
-  </si>
-  <si>
-    <t>INGRID AMERICA</t>
-  </si>
-  <si>
-    <t>JAIME</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>LUIS REY</t>
-  </si>
-  <si>
-    <t>ALONDRA YURIDIA</t>
-  </si>
-  <si>
-    <t>KIMBERLY</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>ALMA KAREN</t>
-  </si>
-  <si>
-    <t>GABRIELA</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>RUBI</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>FLOR GUADALUPE</t>
   </si>
 </sst>
 </file>
@@ -991,7 +991,7 @@
         <v>5</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>-1</v>
@@ -1003,10 +1003,10 @@
         <v>6</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -1054,7 +1054,7 @@
         <v>5</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y4">
         <v>-1</v>
@@ -1066,10 +1066,10 @@
         <v>6</v>
       </c>
       <c r="AB4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC4">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1080,7 +1080,7 @@
         <v>9</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D5">
         <v>-1</v>
@@ -1092,10 +1092,10 @@
         <v>8</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -1143,7 +1143,7 @@
         <v>9</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>-1</v>
@@ -1155,10 +1155,10 @@
         <v>8</v>
       </c>
       <c r="AB5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC5">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1169,7 +1169,7 @@
         <v>9</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D6">
         <v>-1</v>
@@ -1181,10 +1181,10 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -1232,7 +1232,7 @@
         <v>9</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>-1</v>
@@ -1244,10 +1244,10 @@
         <v>5</v>
       </c>
       <c r="AB6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC6">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1258,7 +1258,7 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>-1</v>
@@ -1270,10 +1270,10 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -1321,7 +1321,7 @@
         <v>7</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y7">
         <v>-1</v>
@@ -1333,10 +1333,10 @@
         <v>5</v>
       </c>
       <c r="AB7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1347,7 +1347,7 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D8">
         <v>-1</v>
@@ -1359,10 +1359,10 @@
         <v>8</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -1410,7 +1410,7 @@
         <v>7</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y8">
         <v>-1</v>
@@ -1422,10 +1422,10 @@
         <v>8</v>
       </c>
       <c r="AB8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC8">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1436,7 +1436,7 @@
         <v>7</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D9">
         <v>-1</v>
@@ -1448,10 +1448,10 @@
         <v>8</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -1499,7 +1499,7 @@
         <v>7</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>-1</v>
@@ -1511,10 +1511,10 @@
         <v>8</v>
       </c>
       <c r="AB9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC9">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1525,7 +1525,7 @@
         <v>7</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D10">
         <v>-1</v>
@@ -1537,10 +1537,10 @@
         <v>8</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I10">
         <v>-1</v>
@@ -1588,7 +1588,7 @@
         <v>7</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y10">
         <v>-1</v>
@@ -1600,10 +1600,10 @@
         <v>8</v>
       </c>
       <c r="AB10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC10">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1614,7 +1614,7 @@
         <v>5</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D11">
         <v>-1</v>
@@ -1626,10 +1626,10 @@
         <v>6</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -1677,7 +1677,7 @@
         <v>5</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>-1</v>
@@ -1689,10 +1689,10 @@
         <v>6</v>
       </c>
       <c r="AB11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC11">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1703,7 +1703,7 @@
         <v>5</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D12">
         <v>-1</v>
@@ -1715,10 +1715,10 @@
         <v>5</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -1766,7 +1766,7 @@
         <v>5</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y12">
         <v>-1</v>
@@ -1778,10 +1778,10 @@
         <v>5</v>
       </c>
       <c r="AB12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC12">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1792,7 +1792,7 @@
         <v>5</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D13">
         <v>-1</v>
@@ -1804,10 +1804,10 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -1855,7 +1855,7 @@
         <v>5</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y13">
         <v>-1</v>
@@ -1867,10 +1867,10 @@
         <v>5</v>
       </c>
       <c r="AB13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1881,7 +1881,7 @@
         <v>10</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D14">
         <v>-1</v>
@@ -1893,10 +1893,10 @@
         <v>8</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -1944,7 +1944,7 @@
         <v>10</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y14">
         <v>-1</v>
@@ -1956,10 +1956,10 @@
         <v>8</v>
       </c>
       <c r="AB14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC14">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1970,10 +1970,10 @@
         <v>7</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1997,10 +1997,10 @@
         <v>7</v>
       </c>
       <c r="AB15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC15">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -2011,7 +2011,7 @@
         <v>5</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D16">
         <v>-1</v>
@@ -2023,10 +2023,10 @@
         <v>7</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -2074,7 +2074,7 @@
         <v>5</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y16">
         <v>-1</v>
@@ -2086,10 +2086,10 @@
         <v>7</v>
       </c>
       <c r="AB16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC16">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2100,7 +2100,7 @@
         <v>8</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D17">
         <v>-1</v>
@@ -2112,10 +2112,10 @@
         <v>8</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -2163,7 +2163,7 @@
         <v>8</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y17">
         <v>-1</v>
@@ -2175,10 +2175,10 @@
         <v>8</v>
       </c>
       <c r="AB17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC17">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2189,7 +2189,7 @@
         <v>6</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D18">
         <v>-1</v>
@@ -2201,10 +2201,10 @@
         <v>8</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -2252,7 +2252,7 @@
         <v>6</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>-1</v>
@@ -2264,10 +2264,10 @@
         <v>8</v>
       </c>
       <c r="AB18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC18">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2278,7 +2278,7 @@
         <v>9</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D19">
         <v>-1</v>
@@ -2290,10 +2290,10 @@
         <v>8</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -2341,7 +2341,7 @@
         <v>9</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>-1</v>
@@ -2353,10 +2353,10 @@
         <v>8</v>
       </c>
       <c r="AB19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC19">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2367,10 +2367,10 @@
         <v>10</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2394,10 +2394,10 @@
         <v>10</v>
       </c>
       <c r="AB20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC20">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2408,7 +2408,7 @@
         <v>8</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D21">
         <v>-1</v>
@@ -2420,10 +2420,10 @@
         <v>8</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -2471,7 +2471,7 @@
         <v>8</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>-1</v>
@@ -2483,10 +2483,10 @@
         <v>8</v>
       </c>
       <c r="AB21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC21">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2497,7 +2497,7 @@
         <v>8</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D22">
         <v>-1</v>
@@ -2509,10 +2509,10 @@
         <v>8</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -2560,7 +2560,7 @@
         <v>8</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>-1</v>
@@ -2572,10 +2572,10 @@
         <v>8</v>
       </c>
       <c r="AB22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC22">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2586,7 +2586,7 @@
         <v>8</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D23">
         <v>-1</v>
@@ -2598,10 +2598,10 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -2649,7 +2649,7 @@
         <v>8</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>-1</v>
@@ -2661,10 +2661,10 @@
         <v>5</v>
       </c>
       <c r="AB23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC23">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2675,7 +2675,7 @@
         <v>8</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D24">
         <v>-1</v>
@@ -2687,10 +2687,10 @@
         <v>8</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -2738,7 +2738,7 @@
         <v>8</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y24">
         <v>-1</v>
@@ -2750,10 +2750,10 @@
         <v>8</v>
       </c>
       <c r="AB24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC24">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2764,7 +2764,7 @@
         <v>6</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D25">
         <v>-1</v>
@@ -2776,10 +2776,10 @@
         <v>6</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I25">
         <v>-1</v>
@@ -2827,7 +2827,7 @@
         <v>6</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y25">
         <v>-1</v>
@@ -2839,10 +2839,10 @@
         <v>6</v>
       </c>
       <c r="AB25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC25">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2853,7 +2853,7 @@
         <v>7</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D26">
         <v>-1</v>
@@ -2865,10 +2865,10 @@
         <v>8</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I26">
         <v>-1</v>
@@ -2916,7 +2916,7 @@
         <v>7</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y26">
         <v>-1</v>
@@ -2928,10 +2928,10 @@
         <v>8</v>
       </c>
       <c r="AB26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC26">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2942,7 +2942,7 @@
         <v>7</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D27">
         <v>-1</v>
@@ -2954,10 +2954,10 @@
         <v>8</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -3005,7 +3005,7 @@
         <v>7</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y27">
         <v>-1</v>
@@ -3017,10 +3017,10 @@
         <v>8</v>
       </c>
       <c r="AB27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC27">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3043,10 +3043,10 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I28">
         <v>-1</v>
@@ -3106,10 +3106,10 @@
         <v>5</v>
       </c>
       <c r="AB28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC28">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3120,7 +3120,7 @@
         <v>9</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D29">
         <v>-1</v>
@@ -3132,10 +3132,10 @@
         <v>8</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I29">
         <v>-1</v>
@@ -3183,7 +3183,7 @@
         <v>9</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y29">
         <v>-1</v>
@@ -3195,10 +3195,10 @@
         <v>8</v>
       </c>
       <c r="AB29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC29">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3209,7 +3209,7 @@
         <v>7</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D30">
         <v>-1</v>
@@ -3221,10 +3221,10 @@
         <v>6</v>
       </c>
       <c r="G30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I30">
         <v>-1</v>
@@ -3272,7 +3272,7 @@
         <v>7</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>-1</v>
@@ -3284,10 +3284,10 @@
         <v>6</v>
       </c>
       <c r="AB30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC30">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3298,7 +3298,7 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D31">
         <v>-1</v>
@@ -3310,10 +3310,10 @@
         <v>5</v>
       </c>
       <c r="G31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -3361,7 +3361,7 @@
         <v>6</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y31">
         <v>-1</v>
@@ -3373,10 +3373,10 @@
         <v>5</v>
       </c>
       <c r="AB31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC31">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3387,7 +3387,7 @@
         <v>8</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D32">
         <v>-1</v>
@@ -3399,10 +3399,10 @@
         <v>8</v>
       </c>
       <c r="G32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -3450,7 +3450,7 @@
         <v>8</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y32">
         <v>-1</v>
@@ -3462,10 +3462,10 @@
         <v>8</v>
       </c>
       <c r="AB32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC32">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3476,7 +3476,7 @@
         <v>6</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D33">
         <v>-1</v>
@@ -3488,10 +3488,10 @@
         <v>6</v>
       </c>
       <c r="G33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -3539,7 +3539,7 @@
         <v>6</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y33">
         <v>-1</v>
@@ -3551,10 +3551,10 @@
         <v>6</v>
       </c>
       <c r="AB33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC33">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3565,7 +3565,7 @@
         <v>5</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D34">
         <v>-1</v>
@@ -3577,10 +3577,10 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -3628,7 +3628,7 @@
         <v>5</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y34">
         <v>-1</v>
@@ -3640,10 +3640,10 @@
         <v>5</v>
       </c>
       <c r="AB34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC34">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -3654,7 +3654,7 @@
         <v>6</v>
       </c>
       <c r="C35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D35">
         <v>-1</v>
@@ -3666,10 +3666,10 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -3717,7 +3717,7 @@
         <v>6</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y35">
         <v>-1</v>
@@ -3729,10 +3729,10 @@
         <v>5</v>
       </c>
       <c r="AB35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC35">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:29">
@@ -3743,7 +3743,7 @@
         <v>6</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D36">
         <v>-1</v>
@@ -3755,10 +3755,10 @@
         <v>5</v>
       </c>
       <c r="G36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I36">
         <v>-1</v>
@@ -3806,7 +3806,7 @@
         <v>6</v>
       </c>
       <c r="X36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y36">
         <v>-1</v>
@@ -3818,10 +3818,10 @@
         <v>5</v>
       </c>
       <c r="AB36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC36">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:29">
@@ -3832,7 +3832,7 @@
         <v>5</v>
       </c>
       <c r="C37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D37">
         <v>-1</v>
@@ -3844,10 +3844,10 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I37">
         <v>-1</v>
@@ -3895,7 +3895,7 @@
         <v>5</v>
       </c>
       <c r="X37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y37">
         <v>-1</v>
@@ -3907,10 +3907,10 @@
         <v>5</v>
       </c>
       <c r="AB37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC37">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:29">
@@ -3921,7 +3921,7 @@
         <v>7</v>
       </c>
       <c r="C38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D38">
         <v>-1</v>
@@ -3933,10 +3933,10 @@
         <v>8</v>
       </c>
       <c r="G38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -3984,7 +3984,7 @@
         <v>7</v>
       </c>
       <c r="X38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y38">
         <v>-1</v>
@@ -3996,10 +3996,10 @@
         <v>8</v>
       </c>
       <c r="AB38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC38">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -4132,7 +4132,7 @@
         <v>120</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -4144,10 +4144,10 @@
         <v>100</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4200,7 +4200,7 @@
         <v>120</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -4212,10 +4212,10 @@
         <v>90</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4268,7 +4268,7 @@
         <v>120</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -4280,10 +4280,10 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4336,7 +4336,7 @@
         <v>115</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -4348,10 +4348,10 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4404,7 +4404,7 @@
         <v>120</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -4416,10 +4416,10 @@
         <v>100</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4472,7 +4472,7 @@
         <v>115</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -4484,10 +4484,10 @@
         <v>100</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -4540,7 +4540,7 @@
         <v>115</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -4552,10 +4552,10 @@
         <v>100</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -4608,7 +4608,7 @@
         <v>115</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -4620,10 +4620,10 @@
         <v>100</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -4676,7 +4676,7 @@
         <v>115</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -4688,10 +4688,10 @@
         <v>75</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -4744,7 +4744,7 @@
         <v>115</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -4756,10 +4756,10 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -4812,7 +4812,7 @@
         <v>120</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -4824,10 +4824,10 @@
         <v>100</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -4880,10 +4880,10 @@
         <v>90</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M15">
         <v>0</v>
@@ -4912,7 +4912,7 @@
         <v>115</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -4924,10 +4924,10 @@
         <v>90</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>120</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -4992,10 +4992,10 @@
         <v>100</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -5048,7 +5048,7 @@
         <v>115</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -5060,10 +5060,10 @@
         <v>90</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -5116,7 +5116,7 @@
         <v>120</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -5128,10 +5128,10 @@
         <v>100</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -5184,10 +5184,10 @@
         <v>95</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M20">
         <v>0</v>
@@ -5216,7 +5216,7 @@
         <v>120</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -5228,10 +5228,10 @@
         <v>100</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -5284,7 +5284,7 @@
         <v>120</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -5296,10 +5296,10 @@
         <v>100</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -5352,7 +5352,7 @@
         <v>120</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -5364,10 +5364,10 @@
         <v>95</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -5420,7 +5420,7 @@
         <v>120</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -5432,10 +5432,10 @@
         <v>100</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -5488,7 +5488,7 @@
         <v>115</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -5500,10 +5500,10 @@
         <v>100</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -5556,7 +5556,7 @@
         <v>120</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -5568,10 +5568,10 @@
         <v>100</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -5624,7 +5624,7 @@
         <v>120</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -5636,10 +5636,10 @@
         <v>100</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -5704,10 +5704,10 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -5760,7 +5760,7 @@
         <v>120</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -5772,10 +5772,10 @@
         <v>100</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -5828,7 +5828,7 @@
         <v>115</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -5840,10 +5840,10 @@
         <v>90</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -5896,7 +5896,7 @@
         <v>115</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -5908,10 +5908,10 @@
         <v>90</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -5964,7 +5964,7 @@
         <v>120</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -5976,10 +5976,10 @@
         <v>100</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -6032,7 +6032,7 @@
         <v>115</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -6044,10 +6044,10 @@
         <v>90</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -6100,7 +6100,7 @@
         <v>115</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -6112,10 +6112,10 @@
         <v>75</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -6168,7 +6168,7 @@
         <v>115</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -6180,10 +6180,10 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -6236,7 +6236,7 @@
         <v>115</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -6248,10 +6248,10 @@
         <v>25</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -6304,7 +6304,7 @@
         <v>110</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -6316,10 +6316,10 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -6372,7 +6372,7 @@
         <v>120</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>100</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -6484,7 +6484,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>60</v>
@@ -6513,115 +6513,124 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
       </c>
       <c r="C3">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>31.43</v>
+      </c>
+      <c r="H3">
+        <v>6.8</v>
       </c>
       <c r="I3">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>24.24</v>
+      </c>
+      <c r="H4">
+        <v>6.8</v>
       </c>
       <c r="I4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>18.18</v>
+      </c>
+      <c r="H5">
+        <v>7.2</v>
       </c>
       <c r="I5">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>100</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C6">
         <v>35</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>68.56999999999999</v>
+        <v>82.86</v>
       </c>
       <c r="G6">
-        <v>31.43</v>
+        <v>17.14</v>
       </c>
       <c r="H6">
-        <v>6.8</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6632,28 +6641,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>64</v>
       </c>
       <c r="C7">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D7">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>75.76000000000001</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="G7">
-        <v>24.24</v>
+        <v>14.29</v>
       </c>
       <c r="H7">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6701,7 +6710,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F138"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6736,13 +6745,13 @@
         <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
         <v>60</v>
@@ -6750,79 +6759,79 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920071</v>
+        <v>21330051920074</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920071</v>
+        <v>20330051920378</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920071</v>
+        <v>21330051920075</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920074</v>
+        <v>21330051920108</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
         <v>60</v>
@@ -6830,13 +6839,13 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920074</v>
+        <v>21330051920076</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
         <v>123</v>
@@ -6845,64 +6854,64 @@
         <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920074</v>
+        <v>21330051920077</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920074</v>
+        <v>21330051920078</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920378</v>
+        <v>21330051920079</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D10" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
         <v>60</v>
@@ -6910,79 +6919,79 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920378</v>
+        <v>21330051920260</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920378</v>
+        <v>21330051920080</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="D12" t="s">
         <v>124</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920378</v>
+        <v>21330051920082</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920075</v>
+        <v>21330051920083</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="D14" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
         <v>60</v>
@@ -6990,79 +6999,79 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920075</v>
+        <v>21330051920084</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D15" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920075</v>
+        <v>21330051920085</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
         <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920075</v>
+        <v>21330051920086</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D17" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="E17" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920108</v>
+        <v>20330051920302</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D18" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F18" t="s">
         <v>60</v>
@@ -7070,159 +7079,159 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920108</v>
+        <v>21330051920089</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D19" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920108</v>
+        <v>21330051920092</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="D20" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F20" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>21330051920108</v>
+        <v>21330051920093</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D21" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="E21" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920076</v>
+        <v>21330051920094</v>
       </c>
       <c r="B22" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="D22" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="E22" t="s">
         <v>6</v>
       </c>
       <c r="F22" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>21330051920076</v>
+        <v>21330051920094</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="D23" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="E23" t="s">
         <v>7</v>
       </c>
       <c r="F23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>21330051920076</v>
+        <v>21330051920094</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="E24" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>21330051920076</v>
+        <v>21330051920096</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="D25" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="E25" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F25" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>21330051920077</v>
+        <v>21330051920097</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="D26" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E26" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F26" t="s">
         <v>60</v>
@@ -7230,79 +7239,79 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>21330051920077</v>
+        <v>21330051920099</v>
       </c>
       <c r="B27" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="D27" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="E27" t="s">
         <v>7</v>
       </c>
       <c r="F27" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>21330051920077</v>
+        <v>21330051920100</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="D28" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="E28" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F28" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>21330051920077</v>
+        <v>21330051920383</v>
       </c>
       <c r="B29" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D29" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="E29" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F29" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>21330051920078</v>
+        <v>21330051920102</v>
       </c>
       <c r="B30" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="C30" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="D30" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E30" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F30" t="s">
         <v>60</v>
@@ -7310,79 +7319,79 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>21330051920078</v>
+        <v>21330051920103</v>
       </c>
       <c r="B31" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="D31" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="E31" t="s">
         <v>7</v>
       </c>
       <c r="F31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>21330051920078</v>
+        <v>21330051920104</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="C32" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="D32" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="E32" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F32" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>21330051920078</v>
+        <v>21330051920105</v>
       </c>
       <c r="B33" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="D33" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="E33" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F33" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>21330051920079</v>
+        <v>21330051920107</v>
       </c>
       <c r="B34" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C34" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="D34" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="E34" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F34" t="s">
         <v>60</v>
@@ -7390,2082 +7399,42 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>21330051920079</v>
+        <v>21330051920109</v>
       </c>
       <c r="B35" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="C35" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D35" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="E35" t="s">
         <v>7</v>
       </c>
       <c r="F35" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>21330051920079</v>
+        <v>21330051920387</v>
       </c>
       <c r="B36" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="C36" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="D36" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="E36" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F36" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>21330051920079</v>
-      </c>
-      <c r="B37" t="s">
-        <v>76</v>
-      </c>
-      <c r="C37" t="s">
-        <v>104</v>
-      </c>
-      <c r="D37" t="s">
-        <v>130</v>
-      </c>
-      <c r="E37" t="s">
-        <v>11</v>
-      </c>
-      <c r="F37" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>19330051920195</v>
-      </c>
-      <c r="B38" t="s">
-        <v>77</v>
-      </c>
-      <c r="C38" t="s">
-        <v>105</v>
-      </c>
-      <c r="D38" t="s">
-        <v>131</v>
-      </c>
-      <c r="E38" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>19330051920195</v>
-      </c>
-      <c r="B39" t="s">
-        <v>77</v>
-      </c>
-      <c r="C39" t="s">
-        <v>105</v>
-      </c>
-      <c r="D39" t="s">
-        <v>131</v>
-      </c>
-      <c r="E39" t="s">
-        <v>11</v>
-      </c>
-      <c r="F39" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>21330051920260</v>
-      </c>
-      <c r="B40" t="s">
-        <v>78</v>
-      </c>
-      <c r="C40" t="s">
-        <v>106</v>
-      </c>
-      <c r="D40" t="s">
-        <v>132</v>
-      </c>
-      <c r="E40" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" t="s">
         <v>60</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>21330051920260</v>
-      </c>
-      <c r="B41" t="s">
-        <v>78</v>
-      </c>
-      <c r="C41" t="s">
-        <v>106</v>
-      </c>
-      <c r="D41" t="s">
-        <v>132</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>21330051920260</v>
-      </c>
-      <c r="B42" t="s">
-        <v>78</v>
-      </c>
-      <c r="C42" t="s">
-        <v>106</v>
-      </c>
-      <c r="D42" t="s">
-        <v>132</v>
-      </c>
-      <c r="E42" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>21330051920260</v>
-      </c>
-      <c r="B43" t="s">
-        <v>78</v>
-      </c>
-      <c r="C43" t="s">
-        <v>106</v>
-      </c>
-      <c r="D43" t="s">
-        <v>132</v>
-      </c>
-      <c r="E43" t="s">
-        <v>11</v>
-      </c>
-      <c r="F43" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>21330051920080</v>
-      </c>
-      <c r="B44" t="s">
-        <v>78</v>
-      </c>
-      <c r="C44" t="s">
-        <v>80</v>
-      </c>
-      <c r="D44" t="s">
-        <v>128</v>
-      </c>
-      <c r="E44" t="s">
-        <v>6</v>
-      </c>
-      <c r="F44" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>21330051920080</v>
-      </c>
-      <c r="B45" t="s">
-        <v>78</v>
-      </c>
-      <c r="C45" t="s">
-        <v>80</v>
-      </c>
-      <c r="D45" t="s">
-        <v>128</v>
-      </c>
-      <c r="E45" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>21330051920080</v>
-      </c>
-      <c r="B46" t="s">
-        <v>78</v>
-      </c>
-      <c r="C46" t="s">
-        <v>80</v>
-      </c>
-      <c r="D46" t="s">
-        <v>128</v>
-      </c>
-      <c r="E46" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>21330051920080</v>
-      </c>
-      <c r="B47" t="s">
-        <v>78</v>
-      </c>
-      <c r="C47" t="s">
-        <v>80</v>
-      </c>
-      <c r="D47" t="s">
-        <v>128</v>
-      </c>
-      <c r="E47" t="s">
-        <v>11</v>
-      </c>
-      <c r="F47" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>21330051920082</v>
-      </c>
-      <c r="B48" t="s">
-        <v>79</v>
-      </c>
-      <c r="C48" t="s">
-        <v>107</v>
-      </c>
-      <c r="D48" t="s">
-        <v>133</v>
-      </c>
-      <c r="E48" t="s">
-        <v>6</v>
-      </c>
-      <c r="F48" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>21330051920082</v>
-      </c>
-      <c r="B49" t="s">
-        <v>79</v>
-      </c>
-      <c r="C49" t="s">
-        <v>107</v>
-      </c>
-      <c r="D49" t="s">
-        <v>133</v>
-      </c>
-      <c r="E49" t="s">
-        <v>7</v>
-      </c>
-      <c r="F49" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>21330051920082</v>
-      </c>
-      <c r="B50" t="s">
-        <v>79</v>
-      </c>
-      <c r="C50" t="s">
-        <v>107</v>
-      </c>
-      <c r="D50" t="s">
-        <v>133</v>
-      </c>
-      <c r="E50" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>21330051920082</v>
-      </c>
-      <c r="B51" t="s">
-        <v>79</v>
-      </c>
-      <c r="C51" t="s">
-        <v>107</v>
-      </c>
-      <c r="D51" t="s">
-        <v>133</v>
-      </c>
-      <c r="E51" t="s">
-        <v>11</v>
-      </c>
-      <c r="F51" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>21330051920083</v>
-      </c>
-      <c r="B52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C52" t="s">
-        <v>79</v>
-      </c>
-      <c r="D52" t="s">
-        <v>134</v>
-      </c>
-      <c r="E52" t="s">
-        <v>6</v>
-      </c>
-      <c r="F52" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>21330051920083</v>
-      </c>
-      <c r="B53" t="s">
-        <v>80</v>
-      </c>
-      <c r="C53" t="s">
-        <v>79</v>
-      </c>
-      <c r="D53" t="s">
-        <v>134</v>
-      </c>
-      <c r="E53" t="s">
-        <v>7</v>
-      </c>
-      <c r="F53" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>21330051920083</v>
-      </c>
-      <c r="B54" t="s">
-        <v>80</v>
-      </c>
-      <c r="C54" t="s">
-        <v>79</v>
-      </c>
-      <c r="D54" t="s">
-        <v>134</v>
-      </c>
-      <c r="E54" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>21330051920083</v>
-      </c>
-      <c r="B55" t="s">
-        <v>80</v>
-      </c>
-      <c r="C55" t="s">
-        <v>79</v>
-      </c>
-      <c r="D55" t="s">
-        <v>134</v>
-      </c>
-      <c r="E55" t="s">
-        <v>11</v>
-      </c>
-      <c r="F55" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>21330051920084</v>
-      </c>
-      <c r="B56" t="s">
-        <v>81</v>
-      </c>
-      <c r="C56" t="s">
-        <v>108</v>
-      </c>
-      <c r="D56" t="s">
-        <v>135</v>
-      </c>
-      <c r="E56" t="s">
-        <v>6</v>
-      </c>
-      <c r="F56" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>21330051920084</v>
-      </c>
-      <c r="B57" t="s">
-        <v>81</v>
-      </c>
-      <c r="C57" t="s">
-        <v>108</v>
-      </c>
-      <c r="D57" t="s">
-        <v>135</v>
-      </c>
-      <c r="E57" t="s">
-        <v>7</v>
-      </c>
-      <c r="F57" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>21330051920084</v>
-      </c>
-      <c r="B58" t="s">
-        <v>81</v>
-      </c>
-      <c r="C58" t="s">
-        <v>108</v>
-      </c>
-      <c r="D58" t="s">
-        <v>135</v>
-      </c>
-      <c r="E58" t="s">
-        <v>10</v>
-      </c>
-      <c r="F58" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>21330051920084</v>
-      </c>
-      <c r="B59" t="s">
-        <v>81</v>
-      </c>
-      <c r="C59" t="s">
-        <v>108</v>
-      </c>
-      <c r="D59" t="s">
-        <v>135</v>
-      </c>
-      <c r="E59" t="s">
-        <v>11</v>
-      </c>
-      <c r="F59" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>19330051920286</v>
-      </c>
-      <c r="B60" t="s">
-        <v>82</v>
-      </c>
-      <c r="C60" t="s">
-        <v>109</v>
-      </c>
-      <c r="D60" t="s">
-        <v>136</v>
-      </c>
-      <c r="E60" t="s">
-        <v>10</v>
-      </c>
-      <c r="F60" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>19330051920286</v>
-      </c>
-      <c r="B61" t="s">
-        <v>82</v>
-      </c>
-      <c r="C61" t="s">
-        <v>109</v>
-      </c>
-      <c r="D61" t="s">
-        <v>136</v>
-      </c>
-      <c r="E61" t="s">
-        <v>11</v>
-      </c>
-      <c r="F61" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>21330051920085</v>
-      </c>
-      <c r="B62" t="s">
-        <v>83</v>
-      </c>
-      <c r="C62" t="s">
-        <v>103</v>
-      </c>
-      <c r="D62" t="s">
-        <v>137</v>
-      </c>
-      <c r="E62" t="s">
-        <v>6</v>
-      </c>
-      <c r="F62" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>21330051920085</v>
-      </c>
-      <c r="B63" t="s">
-        <v>83</v>
-      </c>
-      <c r="C63" t="s">
-        <v>103</v>
-      </c>
-      <c r="D63" t="s">
-        <v>137</v>
-      </c>
-      <c r="E63" t="s">
-        <v>7</v>
-      </c>
-      <c r="F63" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>21330051920085</v>
-      </c>
-      <c r="B64" t="s">
-        <v>83</v>
-      </c>
-      <c r="C64" t="s">
-        <v>103</v>
-      </c>
-      <c r="D64" t="s">
-        <v>137</v>
-      </c>
-      <c r="E64" t="s">
-        <v>10</v>
-      </c>
-      <c r="F64" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>21330051920085</v>
-      </c>
-      <c r="B65" t="s">
-        <v>83</v>
-      </c>
-      <c r="C65" t="s">
-        <v>103</v>
-      </c>
-      <c r="D65" t="s">
-        <v>137</v>
-      </c>
-      <c r="E65" t="s">
-        <v>11</v>
-      </c>
-      <c r="F65" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>21330051920086</v>
-      </c>
-      <c r="B66" t="s">
-        <v>83</v>
-      </c>
-      <c r="C66" t="s">
-        <v>110</v>
-      </c>
-      <c r="D66" t="s">
-        <v>138</v>
-      </c>
-      <c r="E66" t="s">
-        <v>6</v>
-      </c>
-      <c r="F66" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>21330051920086</v>
-      </c>
-      <c r="B67" t="s">
-        <v>83</v>
-      </c>
-      <c r="C67" t="s">
-        <v>110</v>
-      </c>
-      <c r="D67" t="s">
-        <v>138</v>
-      </c>
-      <c r="E67" t="s">
-        <v>7</v>
-      </c>
-      <c r="F67" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>21330051920086</v>
-      </c>
-      <c r="B68" t="s">
-        <v>83</v>
-      </c>
-      <c r="C68" t="s">
-        <v>110</v>
-      </c>
-      <c r="D68" t="s">
-        <v>138</v>
-      </c>
-      <c r="E68" t="s">
-        <v>10</v>
-      </c>
-      <c r="F68" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>21330051920086</v>
-      </c>
-      <c r="B69" t="s">
-        <v>83</v>
-      </c>
-      <c r="C69" t="s">
-        <v>110</v>
-      </c>
-      <c r="D69" t="s">
-        <v>138</v>
-      </c>
-      <c r="E69" t="s">
-        <v>11</v>
-      </c>
-      <c r="F69" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>20330051920302</v>
-      </c>
-      <c r="B70" t="s">
-        <v>83</v>
-      </c>
-      <c r="C70" t="s">
-        <v>111</v>
-      </c>
-      <c r="D70" t="s">
-        <v>139</v>
-      </c>
-      <c r="E70" t="s">
-        <v>6</v>
-      </c>
-      <c r="F70" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>20330051920302</v>
-      </c>
-      <c r="B71" t="s">
-        <v>83</v>
-      </c>
-      <c r="C71" t="s">
-        <v>111</v>
-      </c>
-      <c r="D71" t="s">
-        <v>139</v>
-      </c>
-      <c r="E71" t="s">
-        <v>7</v>
-      </c>
-      <c r="F71" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>20330051920302</v>
-      </c>
-      <c r="B72" t="s">
-        <v>83</v>
-      </c>
-      <c r="C72" t="s">
-        <v>111</v>
-      </c>
-      <c r="D72" t="s">
-        <v>139</v>
-      </c>
-      <c r="E72" t="s">
-        <v>10</v>
-      </c>
-      <c r="F72" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>20330051920302</v>
-      </c>
-      <c r="B73" t="s">
-        <v>83</v>
-      </c>
-      <c r="C73" t="s">
-        <v>111</v>
-      </c>
-      <c r="D73" t="s">
-        <v>139</v>
-      </c>
-      <c r="E73" t="s">
-        <v>11</v>
-      </c>
-      <c r="F73" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>21330051920089</v>
-      </c>
-      <c r="B74" t="s">
-        <v>84</v>
-      </c>
-      <c r="C74" t="s">
-        <v>111</v>
-      </c>
-      <c r="D74" t="s">
-        <v>140</v>
-      </c>
-      <c r="E74" t="s">
-        <v>6</v>
-      </c>
-      <c r="F74" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>21330051920089</v>
-      </c>
-      <c r="B75" t="s">
-        <v>84</v>
-      </c>
-      <c r="C75" t="s">
-        <v>111</v>
-      </c>
-      <c r="D75" t="s">
-        <v>140</v>
-      </c>
-      <c r="E75" t="s">
-        <v>7</v>
-      </c>
-      <c r="F75" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>21330051920089</v>
-      </c>
-      <c r="B76" t="s">
-        <v>84</v>
-      </c>
-      <c r="C76" t="s">
-        <v>111</v>
-      </c>
-      <c r="D76" t="s">
-        <v>140</v>
-      </c>
-      <c r="E76" t="s">
-        <v>10</v>
-      </c>
-      <c r="F76" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>21330051920089</v>
-      </c>
-      <c r="B77" t="s">
-        <v>84</v>
-      </c>
-      <c r="C77" t="s">
-        <v>111</v>
-      </c>
-      <c r="D77" t="s">
-        <v>140</v>
-      </c>
-      <c r="E77" t="s">
-        <v>11</v>
-      </c>
-      <c r="F77" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>21330051920092</v>
-      </c>
-      <c r="B78" t="s">
-        <v>85</v>
-      </c>
-      <c r="C78" t="s">
-        <v>112</v>
-      </c>
-      <c r="D78" t="s">
-        <v>141</v>
-      </c>
-      <c r="E78" t="s">
-        <v>6</v>
-      </c>
-      <c r="F78" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>21330051920092</v>
-      </c>
-      <c r="B79" t="s">
-        <v>85</v>
-      </c>
-      <c r="C79" t="s">
-        <v>112</v>
-      </c>
-      <c r="D79" t="s">
-        <v>141</v>
-      </c>
-      <c r="E79" t="s">
-        <v>7</v>
-      </c>
-      <c r="F79" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>21330051920092</v>
-      </c>
-      <c r="B80" t="s">
-        <v>85</v>
-      </c>
-      <c r="C80" t="s">
-        <v>112</v>
-      </c>
-      <c r="D80" t="s">
-        <v>141</v>
-      </c>
-      <c r="E80" t="s">
-        <v>10</v>
-      </c>
-      <c r="F80" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>21330051920092</v>
-      </c>
-      <c r="B81" t="s">
-        <v>85</v>
-      </c>
-      <c r="C81" t="s">
-        <v>112</v>
-      </c>
-      <c r="D81" t="s">
-        <v>141</v>
-      </c>
-      <c r="E81" t="s">
-        <v>11</v>
-      </c>
-      <c r="F81" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>21330051920093</v>
-      </c>
-      <c r="B82" t="s">
-        <v>86</v>
-      </c>
-      <c r="C82" t="s">
-        <v>90</v>
-      </c>
-      <c r="D82" t="s">
-        <v>142</v>
-      </c>
-      <c r="E82" t="s">
-        <v>6</v>
-      </c>
-      <c r="F82" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>21330051920093</v>
-      </c>
-      <c r="B83" t="s">
-        <v>86</v>
-      </c>
-      <c r="C83" t="s">
-        <v>90</v>
-      </c>
-      <c r="D83" t="s">
-        <v>142</v>
-      </c>
-      <c r="E83" t="s">
-        <v>7</v>
-      </c>
-      <c r="F83" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>21330051920093</v>
-      </c>
-      <c r="B84" t="s">
-        <v>86</v>
-      </c>
-      <c r="C84" t="s">
-        <v>90</v>
-      </c>
-      <c r="D84" t="s">
-        <v>142</v>
-      </c>
-      <c r="E84" t="s">
-        <v>10</v>
-      </c>
-      <c r="F84" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>21330051920093</v>
-      </c>
-      <c r="B85" t="s">
-        <v>86</v>
-      </c>
-      <c r="C85" t="s">
-        <v>90</v>
-      </c>
-      <c r="D85" t="s">
-        <v>142</v>
-      </c>
-      <c r="E85" t="s">
-        <v>11</v>
-      </c>
-      <c r="F85" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>21330051920094</v>
-      </c>
-      <c r="B86" t="s">
-        <v>87</v>
-      </c>
-      <c r="C86" t="s">
-        <v>113</v>
-      </c>
-      <c r="D86" t="s">
-        <v>143</v>
-      </c>
-      <c r="E86" t="s">
-        <v>6</v>
-      </c>
-      <c r="F86" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>21330051920094</v>
-      </c>
-      <c r="B87" t="s">
-        <v>87</v>
-      </c>
-      <c r="C87" t="s">
-        <v>113</v>
-      </c>
-      <c r="D87" t="s">
-        <v>143</v>
-      </c>
-      <c r="E87" t="s">
-        <v>7</v>
-      </c>
-      <c r="F87" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>21330051920094</v>
-      </c>
-      <c r="B88" t="s">
-        <v>87</v>
-      </c>
-      <c r="C88" t="s">
-        <v>113</v>
-      </c>
-      <c r="D88" t="s">
-        <v>143</v>
-      </c>
-      <c r="E88" t="s">
-        <v>8</v>
-      </c>
-      <c r="F88" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>21330051920094</v>
-      </c>
-      <c r="B89" t="s">
-        <v>87</v>
-      </c>
-      <c r="C89" t="s">
-        <v>113</v>
-      </c>
-      <c r="D89" t="s">
-        <v>143</v>
-      </c>
-      <c r="E89" t="s">
-        <v>10</v>
-      </c>
-      <c r="F89" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>21330051920094</v>
-      </c>
-      <c r="B90" t="s">
-        <v>87</v>
-      </c>
-      <c r="C90" t="s">
-        <v>113</v>
-      </c>
-      <c r="D90" t="s">
-        <v>143</v>
-      </c>
-      <c r="E90" t="s">
-        <v>11</v>
-      </c>
-      <c r="F90" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>21330051920096</v>
-      </c>
-      <c r="B91" t="s">
-        <v>87</v>
-      </c>
-      <c r="C91" t="s">
-        <v>114</v>
-      </c>
-      <c r="D91" t="s">
-        <v>144</v>
-      </c>
-      <c r="E91" t="s">
-        <v>6</v>
-      </c>
-      <c r="F91" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>21330051920096</v>
-      </c>
-      <c r="B92" t="s">
-        <v>87</v>
-      </c>
-      <c r="C92" t="s">
-        <v>114</v>
-      </c>
-      <c r="D92" t="s">
-        <v>144</v>
-      </c>
-      <c r="E92" t="s">
-        <v>7</v>
-      </c>
-      <c r="F92" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>21330051920096</v>
-      </c>
-      <c r="B93" t="s">
-        <v>87</v>
-      </c>
-      <c r="C93" t="s">
-        <v>114</v>
-      </c>
-      <c r="D93" t="s">
-        <v>144</v>
-      </c>
-      <c r="E93" t="s">
-        <v>10</v>
-      </c>
-      <c r="F93" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>21330051920096</v>
-      </c>
-      <c r="B94" t="s">
-        <v>87</v>
-      </c>
-      <c r="C94" t="s">
-        <v>114</v>
-      </c>
-      <c r="D94" t="s">
-        <v>144</v>
-      </c>
-      <c r="E94" t="s">
-        <v>11</v>
-      </c>
-      <c r="F94" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>21330051920097</v>
-      </c>
-      <c r="B95" t="s">
-        <v>88</v>
-      </c>
-      <c r="C95" t="s">
-        <v>115</v>
-      </c>
-      <c r="D95" t="s">
-        <v>145</v>
-      </c>
-      <c r="E95" t="s">
-        <v>6</v>
-      </c>
-      <c r="F95" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>21330051920097</v>
-      </c>
-      <c r="B96" t="s">
-        <v>88</v>
-      </c>
-      <c r="C96" t="s">
-        <v>115</v>
-      </c>
-      <c r="D96" t="s">
-        <v>145</v>
-      </c>
-      <c r="E96" t="s">
-        <v>7</v>
-      </c>
-      <c r="F96" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97">
-        <v>21330051920097</v>
-      </c>
-      <c r="B97" t="s">
-        <v>88</v>
-      </c>
-      <c r="C97" t="s">
-        <v>115</v>
-      </c>
-      <c r="D97" t="s">
-        <v>145</v>
-      </c>
-      <c r="E97" t="s">
-        <v>10</v>
-      </c>
-      <c r="F97" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98">
-        <v>21330051920097</v>
-      </c>
-      <c r="B98" t="s">
-        <v>88</v>
-      </c>
-      <c r="C98" t="s">
-        <v>115</v>
-      </c>
-      <c r="D98" t="s">
-        <v>145</v>
-      </c>
-      <c r="E98" t="s">
-        <v>11</v>
-      </c>
-      <c r="F98" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99">
-        <v>21330051920099</v>
-      </c>
-      <c r="B99" t="s">
-        <v>89</v>
-      </c>
-      <c r="C99" t="s">
-        <v>87</v>
-      </c>
-      <c r="D99" t="s">
-        <v>146</v>
-      </c>
-      <c r="E99" t="s">
-        <v>6</v>
-      </c>
-      <c r="F99" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="A100">
-        <v>21330051920099</v>
-      </c>
-      <c r="B100" t="s">
-        <v>89</v>
-      </c>
-      <c r="C100" t="s">
-        <v>87</v>
-      </c>
-      <c r="D100" t="s">
-        <v>146</v>
-      </c>
-      <c r="E100" t="s">
-        <v>7</v>
-      </c>
-      <c r="F100" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="A101">
-        <v>21330051920099</v>
-      </c>
-      <c r="B101" t="s">
-        <v>89</v>
-      </c>
-      <c r="C101" t="s">
-        <v>87</v>
-      </c>
-      <c r="D101" t="s">
-        <v>146</v>
-      </c>
-      <c r="E101" t="s">
-        <v>10</v>
-      </c>
-      <c r="F101" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="A102">
-        <v>21330051920099</v>
-      </c>
-      <c r="B102" t="s">
-        <v>89</v>
-      </c>
-      <c r="C102" t="s">
-        <v>87</v>
-      </c>
-      <c r="D102" t="s">
-        <v>146</v>
-      </c>
-      <c r="E102" t="s">
-        <v>11</v>
-      </c>
-      <c r="F102" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="A103">
-        <v>21330051920100</v>
-      </c>
-      <c r="B103" t="s">
-        <v>90</v>
-      </c>
-      <c r="C103" t="s">
-        <v>116</v>
-      </c>
-      <c r="D103" t="s">
-        <v>147</v>
-      </c>
-      <c r="E103" t="s">
-        <v>6</v>
-      </c>
-      <c r="F103" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
-      <c r="A104">
-        <v>21330051920100</v>
-      </c>
-      <c r="B104" t="s">
-        <v>90</v>
-      </c>
-      <c r="C104" t="s">
-        <v>116</v>
-      </c>
-      <c r="D104" t="s">
-        <v>147</v>
-      </c>
-      <c r="E104" t="s">
-        <v>7</v>
-      </c>
-      <c r="F104" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
-      <c r="A105">
-        <v>21330051920100</v>
-      </c>
-      <c r="B105" t="s">
-        <v>90</v>
-      </c>
-      <c r="C105" t="s">
-        <v>116</v>
-      </c>
-      <c r="D105" t="s">
-        <v>147</v>
-      </c>
-      <c r="E105" t="s">
-        <v>10</v>
-      </c>
-      <c r="F105" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
-      <c r="A106">
-        <v>21330051920100</v>
-      </c>
-      <c r="B106" t="s">
-        <v>90</v>
-      </c>
-      <c r="C106" t="s">
-        <v>116</v>
-      </c>
-      <c r="D106" t="s">
-        <v>147</v>
-      </c>
-      <c r="E106" t="s">
-        <v>11</v>
-      </c>
-      <c r="F106" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
-      <c r="A107">
-        <v>21330051920383</v>
-      </c>
-      <c r="B107" t="s">
-        <v>91</v>
-      </c>
-      <c r="C107" t="s">
-        <v>92</v>
-      </c>
-      <c r="D107" t="s">
-        <v>148</v>
-      </c>
-      <c r="E107" t="s">
-        <v>6</v>
-      </c>
-      <c r="F107" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
-      <c r="A108">
-        <v>21330051920383</v>
-      </c>
-      <c r="B108" t="s">
-        <v>91</v>
-      </c>
-      <c r="C108" t="s">
-        <v>92</v>
-      </c>
-      <c r="D108" t="s">
-        <v>148</v>
-      </c>
-      <c r="E108" t="s">
-        <v>7</v>
-      </c>
-      <c r="F108" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="A109">
-        <v>21330051920383</v>
-      </c>
-      <c r="B109" t="s">
-        <v>91</v>
-      </c>
-      <c r="C109" t="s">
-        <v>92</v>
-      </c>
-      <c r="D109" t="s">
-        <v>148</v>
-      </c>
-      <c r="E109" t="s">
-        <v>10</v>
-      </c>
-      <c r="F109" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
-      <c r="A110">
-        <v>21330051920383</v>
-      </c>
-      <c r="B110" t="s">
-        <v>91</v>
-      </c>
-      <c r="C110" t="s">
-        <v>92</v>
-      </c>
-      <c r="D110" t="s">
-        <v>148</v>
-      </c>
-      <c r="E110" t="s">
-        <v>11</v>
-      </c>
-      <c r="F110" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
-      <c r="A111">
-        <v>21330051920102</v>
-      </c>
-      <c r="B111" t="s">
-        <v>92</v>
-      </c>
-      <c r="C111" t="s">
-        <v>72</v>
-      </c>
-      <c r="D111" t="s">
-        <v>149</v>
-      </c>
-      <c r="E111" t="s">
-        <v>6</v>
-      </c>
-      <c r="F111" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="A112">
-        <v>21330051920102</v>
-      </c>
-      <c r="B112" t="s">
-        <v>92</v>
-      </c>
-      <c r="C112" t="s">
-        <v>72</v>
-      </c>
-      <c r="D112" t="s">
-        <v>149</v>
-      </c>
-      <c r="E112" t="s">
-        <v>7</v>
-      </c>
-      <c r="F112" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="A113">
-        <v>21330051920102</v>
-      </c>
-      <c r="B113" t="s">
-        <v>92</v>
-      </c>
-      <c r="C113" t="s">
-        <v>72</v>
-      </c>
-      <c r="D113" t="s">
-        <v>149</v>
-      </c>
-      <c r="E113" t="s">
-        <v>10</v>
-      </c>
-      <c r="F113" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="A114">
-        <v>21330051920102</v>
-      </c>
-      <c r="B114" t="s">
-        <v>92</v>
-      </c>
-      <c r="C114" t="s">
-        <v>72</v>
-      </c>
-      <c r="D114" t="s">
-        <v>149</v>
-      </c>
-      <c r="E114" t="s">
-        <v>11</v>
-      </c>
-      <c r="F114" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
-      <c r="A115">
-        <v>21330051920103</v>
-      </c>
-      <c r="B115" t="s">
-        <v>93</v>
-      </c>
-      <c r="C115" t="s">
-        <v>83</v>
-      </c>
-      <c r="D115" t="s">
-        <v>150</v>
-      </c>
-      <c r="E115" t="s">
-        <v>6</v>
-      </c>
-      <c r="F115" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="A116">
-        <v>21330051920103</v>
-      </c>
-      <c r="B116" t="s">
-        <v>93</v>
-      </c>
-      <c r="C116" t="s">
-        <v>83</v>
-      </c>
-      <c r="D116" t="s">
-        <v>150</v>
-      </c>
-      <c r="E116" t="s">
-        <v>7</v>
-      </c>
-      <c r="F116" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
-      <c r="A117">
-        <v>21330051920103</v>
-      </c>
-      <c r="B117" t="s">
-        <v>93</v>
-      </c>
-      <c r="C117" t="s">
-        <v>83</v>
-      </c>
-      <c r="D117" t="s">
-        <v>150</v>
-      </c>
-      <c r="E117" t="s">
-        <v>10</v>
-      </c>
-      <c r="F117" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="A118">
-        <v>21330051920103</v>
-      </c>
-      <c r="B118" t="s">
-        <v>93</v>
-      </c>
-      <c r="C118" t="s">
-        <v>83</v>
-      </c>
-      <c r="D118" t="s">
-        <v>150</v>
-      </c>
-      <c r="E118" t="s">
-        <v>11</v>
-      </c>
-      <c r="F118" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="A119">
-        <v>21330051920104</v>
-      </c>
-      <c r="B119" t="s">
-        <v>94</v>
-      </c>
-      <c r="C119" t="s">
-        <v>117</v>
-      </c>
-      <c r="D119" t="s">
-        <v>151</v>
-      </c>
-      <c r="E119" t="s">
-        <v>6</v>
-      </c>
-      <c r="F119" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
-      <c r="A120">
-        <v>21330051920104</v>
-      </c>
-      <c r="B120" t="s">
-        <v>94</v>
-      </c>
-      <c r="C120" t="s">
-        <v>117</v>
-      </c>
-      <c r="D120" t="s">
-        <v>151</v>
-      </c>
-      <c r="E120" t="s">
-        <v>7</v>
-      </c>
-      <c r="F120" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
-      <c r="A121">
-        <v>21330051920104</v>
-      </c>
-      <c r="B121" t="s">
-        <v>94</v>
-      </c>
-      <c r="C121" t="s">
-        <v>117</v>
-      </c>
-      <c r="D121" t="s">
-        <v>151</v>
-      </c>
-      <c r="E121" t="s">
-        <v>10</v>
-      </c>
-      <c r="F121" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
-      <c r="A122">
-        <v>21330051920104</v>
-      </c>
-      <c r="B122" t="s">
-        <v>94</v>
-      </c>
-      <c r="C122" t="s">
-        <v>117</v>
-      </c>
-      <c r="D122" t="s">
-        <v>151</v>
-      </c>
-      <c r="E122" t="s">
-        <v>11</v>
-      </c>
-      <c r="F122" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="A123">
-        <v>21330051920105</v>
-      </c>
-      <c r="B123" t="s">
-        <v>95</v>
-      </c>
-      <c r="C123" t="s">
-        <v>118</v>
-      </c>
-      <c r="D123" t="s">
-        <v>152</v>
-      </c>
-      <c r="E123" t="s">
-        <v>6</v>
-      </c>
-      <c r="F123" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
-      <c r="A124">
-        <v>21330051920105</v>
-      </c>
-      <c r="B124" t="s">
-        <v>95</v>
-      </c>
-      <c r="C124" t="s">
-        <v>118</v>
-      </c>
-      <c r="D124" t="s">
-        <v>152</v>
-      </c>
-      <c r="E124" t="s">
-        <v>7</v>
-      </c>
-      <c r="F124" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="A125">
-        <v>21330051920105</v>
-      </c>
-      <c r="B125" t="s">
-        <v>95</v>
-      </c>
-      <c r="C125" t="s">
-        <v>118</v>
-      </c>
-      <c r="D125" t="s">
-        <v>152</v>
-      </c>
-      <c r="E125" t="s">
-        <v>10</v>
-      </c>
-      <c r="F125" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
-      <c r="A126">
-        <v>21330051920105</v>
-      </c>
-      <c r="B126" t="s">
-        <v>95</v>
-      </c>
-      <c r="C126" t="s">
-        <v>118</v>
-      </c>
-      <c r="D126" t="s">
-        <v>152</v>
-      </c>
-      <c r="E126" t="s">
-        <v>11</v>
-      </c>
-      <c r="F126" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="A127">
-        <v>21330051920107</v>
-      </c>
-      <c r="B127" t="s">
-        <v>96</v>
-      </c>
-      <c r="C127" t="s">
-        <v>119</v>
-      </c>
-      <c r="D127" t="s">
-        <v>153</v>
-      </c>
-      <c r="E127" t="s">
-        <v>6</v>
-      </c>
-      <c r="F127" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="A128">
-        <v>21330051920107</v>
-      </c>
-      <c r="B128" t="s">
-        <v>96</v>
-      </c>
-      <c r="C128" t="s">
-        <v>119</v>
-      </c>
-      <c r="D128" t="s">
-        <v>153</v>
-      </c>
-      <c r="E128" t="s">
-        <v>7</v>
-      </c>
-      <c r="F128" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6">
-      <c r="A129">
-        <v>21330051920107</v>
-      </c>
-      <c r="B129" t="s">
-        <v>96</v>
-      </c>
-      <c r="C129" t="s">
-        <v>119</v>
-      </c>
-      <c r="D129" t="s">
-        <v>153</v>
-      </c>
-      <c r="E129" t="s">
-        <v>10</v>
-      </c>
-      <c r="F129" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6">
-      <c r="A130">
-        <v>21330051920107</v>
-      </c>
-      <c r="B130" t="s">
-        <v>96</v>
-      </c>
-      <c r="C130" t="s">
-        <v>119</v>
-      </c>
-      <c r="D130" t="s">
-        <v>153</v>
-      </c>
-      <c r="E130" t="s">
-        <v>11</v>
-      </c>
-      <c r="F130" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
-      <c r="A131">
-        <v>21330051920109</v>
-      </c>
-      <c r="B131" t="s">
-        <v>97</v>
-      </c>
-      <c r="C131" t="s">
-        <v>120</v>
-      </c>
-      <c r="D131" t="s">
-        <v>154</v>
-      </c>
-      <c r="E131" t="s">
-        <v>6</v>
-      </c>
-      <c r="F131" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6">
-      <c r="A132">
-        <v>21330051920109</v>
-      </c>
-      <c r="B132" t="s">
-        <v>97</v>
-      </c>
-      <c r="C132" t="s">
-        <v>120</v>
-      </c>
-      <c r="D132" t="s">
-        <v>154</v>
-      </c>
-      <c r="E132" t="s">
-        <v>7</v>
-      </c>
-      <c r="F132" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
-      <c r="A133">
-        <v>21330051920109</v>
-      </c>
-      <c r="B133" t="s">
-        <v>97</v>
-      </c>
-      <c r="C133" t="s">
-        <v>120</v>
-      </c>
-      <c r="D133" t="s">
-        <v>154</v>
-      </c>
-      <c r="E133" t="s">
-        <v>10</v>
-      </c>
-      <c r="F133" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6">
-      <c r="A134">
-        <v>21330051920109</v>
-      </c>
-      <c r="B134" t="s">
-        <v>97</v>
-      </c>
-      <c r="C134" t="s">
-        <v>120</v>
-      </c>
-      <c r="D134" t="s">
-        <v>154</v>
-      </c>
-      <c r="E134" t="s">
-        <v>11</v>
-      </c>
-      <c r="F134" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6">
-      <c r="A135">
-        <v>21330051920387</v>
-      </c>
-      <c r="B135" t="s">
-        <v>98</v>
-      </c>
-      <c r="C135" t="s">
-        <v>121</v>
-      </c>
-      <c r="D135" t="s">
-        <v>155</v>
-      </c>
-      <c r="E135" t="s">
-        <v>6</v>
-      </c>
-      <c r="F135" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6">
-      <c r="A136">
-        <v>21330051920387</v>
-      </c>
-      <c r="B136" t="s">
-        <v>98</v>
-      </c>
-      <c r="C136" t="s">
-        <v>121</v>
-      </c>
-      <c r="D136" t="s">
-        <v>155</v>
-      </c>
-      <c r="E136" t="s">
-        <v>7</v>
-      </c>
-      <c r="F136" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
-      <c r="A137">
-        <v>21330051920387</v>
-      </c>
-      <c r="B137" t="s">
-        <v>98</v>
-      </c>
-      <c r="C137" t="s">
-        <v>121</v>
-      </c>
-      <c r="D137" t="s">
-        <v>155</v>
-      </c>
-      <c r="E137" t="s">
-        <v>10</v>
-      </c>
-      <c r="F137" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
-      <c r="A138">
-        <v>21330051920387</v>
-      </c>
-      <c r="B138" t="s">
-        <v>98</v>
-      </c>
-      <c r="C138" t="s">
-        <v>121</v>
-      </c>
-      <c r="D138" t="s">
-        <v>155</v>
-      </c>
-      <c r="E138" t="s">
-        <v>11</v>
-      </c>
-      <c r="F138" t="s">
-        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -9504,16 +7473,16 @@
         <v>21330051920094</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -9524,13 +7493,13 @@
         <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -9541,13 +7510,13 @@
         <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -9558,13 +7527,13 @@
         <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -9575,13 +7544,13 @@
         <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -9592,13 +7561,13 @@
         <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -9609,13 +7578,13 @@
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -9626,13 +7595,13 @@
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -9643,13 +7612,13 @@
         <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -9660,13 +7629,13 @@
         <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -9674,16 +7643,16 @@
         <v>21330051920260</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -9691,16 +7660,16 @@
         <v>21330051920080</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -9708,16 +7677,16 @@
         <v>21330051920082</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D14" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -9725,16 +7694,16 @@
         <v>21330051920083</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D15" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -9742,16 +7711,16 @@
         <v>21330051920084</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D16" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="E16">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -9759,16 +7728,16 @@
         <v>21330051920085</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -9776,16 +7745,16 @@
         <v>21330051920086</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D18" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -9793,16 +7762,16 @@
         <v>20330051920302</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D19" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -9810,16 +7779,16 @@
         <v>21330051920089</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D20" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -9827,16 +7796,16 @@
         <v>21330051920092</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D21" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E21">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -9844,16 +7813,16 @@
         <v>21330051920093</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D22" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E22">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -9861,16 +7830,16 @@
         <v>21330051920096</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D23" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -9878,16 +7847,16 @@
         <v>21330051920097</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D24" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E24">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -9895,16 +7864,16 @@
         <v>21330051920099</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D25" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E25">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -9912,16 +7881,16 @@
         <v>21330051920100</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D26" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="E26">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -9929,16 +7898,16 @@
         <v>21330051920383</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D27" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -9946,16 +7915,16 @@
         <v>21330051920102</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C28" t="s">
         <v>72</v>
       </c>
       <c r="D28" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E28">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -9963,16 +7932,16 @@
         <v>21330051920103</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D29" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -9980,16 +7949,16 @@
         <v>21330051920104</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C30" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D30" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -9997,16 +7966,16 @@
         <v>21330051920105</v>
       </c>
       <c r="B31" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C31" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D31" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="E31">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -10014,16 +7983,16 @@
         <v>21330051920107</v>
       </c>
       <c r="B32" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C32" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D32" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E32">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -10031,16 +8000,16 @@
         <v>21330051920109</v>
       </c>
       <c r="B33" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C33" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D33" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="E33">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -10048,16 +8017,16 @@
         <v>21330051920387</v>
       </c>
       <c r="B34" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C34" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D34" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="E34">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -10065,16 +8034,16 @@
         <v>19330051920195</v>
       </c>
       <c r="B35" t="s">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="C35" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="D35" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -10082,16 +8051,16 @@
         <v>19330051920286</v>
       </c>
       <c r="B36" t="s">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="C36" t="s">
-        <v>109</v>
+        <v>153</v>
       </c>
       <c r="D36" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -10101,7 +8070,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -10133,22 +8102,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920195</v>
+        <v>20330051920378</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D2" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -10156,70 +8125,599 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920195</v>
+        <v>20330051920378</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D3" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920286</v>
+        <v>21330051920076</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>62</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920286</v>
+        <v>21330051920076</v>
       </c>
       <c r="B5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" t="s">
+        <v>60</v>
+      </c>
+      <c r="G5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920302</v>
+      </c>
+      <c r="B6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D6" t="s">
+        <v>133</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920302</v>
+      </c>
+      <c r="B7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D7" t="s">
+        <v>133</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920100</v>
+      </c>
+      <c r="B8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920100</v>
+      </c>
+      <c r="B9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" t="s">
+        <v>141</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920074</v>
+      </c>
+      <c r="B10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" t="s">
+        <v>119</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920075</v>
+      </c>
+      <c r="B11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D11" t="s">
+        <v>121</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920108</v>
+      </c>
+      <c r="B12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" t="s">
+        <v>122</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920079</v>
+      </c>
+      <c r="B13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" t="s">
+        <v>102</v>
+      </c>
+      <c r="D13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E13" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920080</v>
+      </c>
+      <c r="B14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" t="s">
+        <v>124</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920083</v>
+      </c>
+      <c r="B15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15" t="s">
+        <v>129</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" t="s">
+        <v>60</v>
+      </c>
+      <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21330051920084</v>
+      </c>
+      <c r="B16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" t="s">
+        <v>130</v>
+      </c>
+      <c r="E16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" t="s">
+        <v>60</v>
+      </c>
+      <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>21330051920085</v>
+      </c>
+      <c r="B17" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" t="s">
+        <v>101</v>
+      </c>
+      <c r="D17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" t="s">
+        <v>60</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>21330051920086</v>
+      </c>
+      <c r="B18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" t="s">
+        <v>106</v>
+      </c>
+      <c r="D18" t="s">
+        <v>132</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" t="s">
+        <v>60</v>
+      </c>
+      <c r="G18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>21330051920089</v>
+      </c>
+      <c r="B19" t="s">
         <v>82</v>
       </c>
-      <c r="C5" t="s">
-        <v>109</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C19" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" t="s">
+        <v>134</v>
+      </c>
+      <c r="E19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" t="s">
+        <v>60</v>
+      </c>
+      <c r="G19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>21330051920092</v>
+      </c>
+      <c r="B20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D20" t="s">
+        <v>135</v>
+      </c>
+      <c r="E20" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" t="s">
+        <v>60</v>
+      </c>
+      <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>21330051920093</v>
+      </c>
+      <c r="B21" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" t="s">
         <v>136</v>
       </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" t="s">
-        <v>62</v>
-      </c>
-      <c r="G5">
+      <c r="E21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" t="s">
+        <v>60</v>
+      </c>
+      <c r="G21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>21330051920096</v>
+      </c>
+      <c r="B22" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" t="s">
+        <v>138</v>
+      </c>
+      <c r="E22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" t="s">
+        <v>60</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>21330051920097</v>
+      </c>
+      <c r="B23" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" t="s">
+        <v>111</v>
+      </c>
+      <c r="D23" t="s">
+        <v>139</v>
+      </c>
+      <c r="E23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F23" t="s">
+        <v>60</v>
+      </c>
+      <c r="G23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>21330051920099</v>
+      </c>
+      <c r="B24" t="s">
+        <v>87</v>
+      </c>
+      <c r="C24" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" t="s">
+        <v>140</v>
+      </c>
+      <c r="E24" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" t="s">
+        <v>60</v>
+      </c>
+      <c r="G24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>21330051920383</v>
+      </c>
+      <c r="B25" t="s">
+        <v>89</v>
+      </c>
+      <c r="C25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D25" t="s">
+        <v>142</v>
+      </c>
+      <c r="E25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F25" t="s">
+        <v>60</v>
+      </c>
+      <c r="G25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>21330051920102</v>
+      </c>
+      <c r="B26" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" t="s">
+        <v>72</v>
+      </c>
+      <c r="D26" t="s">
+        <v>143</v>
+      </c>
+      <c r="E26" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" t="s">
+        <v>60</v>
+      </c>
+      <c r="G26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>21330051920104</v>
+      </c>
+      <c r="B27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" t="s">
+        <v>113</v>
+      </c>
+      <c r="D27" t="s">
+        <v>145</v>
+      </c>
+      <c r="E27" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27" t="s">
+        <v>60</v>
+      </c>
+      <c r="G27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>21330051920387</v>
+      </c>
+      <c r="B28" t="s">
+        <v>96</v>
+      </c>
+      <c r="C28" t="s">
+        <v>117</v>
+      </c>
+      <c r="D28" t="s">
+        <v>149</v>
+      </c>
+      <c r="E28" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" t="s">
+        <v>60</v>
+      </c>
+      <c r="G28">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/4ALCV - Estadisticos 20222.xlsx
+++ b/grupos/4ALCV - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="156">
   <si>
     <t>Materia</t>
   </si>
@@ -231,6 +231,15 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>INGRID AMERICA</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
@@ -252,6 +261,9 @@
     <t>GARCIA</t>
   </si>
   <si>
+    <t>GUILLEN</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -264,6 +276,9 @@
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>MANZANET</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
@@ -276,9 +291,6 @@
     <t>PALOMARES</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>PELLICO</t>
   </si>
   <si>
@@ -330,6 +342,9 @@
     <t>VALIENTE</t>
   </si>
   <si>
+    <t>LINARES</t>
+  </si>
+  <si>
     <t>CAMPOS</t>
   </si>
   <si>
@@ -339,6 +354,9 @@
     <t>DE LA LUZ</t>
   </si>
   <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
@@ -348,9 +366,6 @@
     <t>HIPOLITO</t>
   </si>
   <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
     <t>PAZ</t>
   </si>
   <si>
@@ -402,6 +417,9 @@
     <t>BERENICE</t>
   </si>
   <si>
+    <t>EDITH</t>
+  </si>
+  <si>
     <t>MARIA TERESA</t>
   </si>
   <si>
@@ -414,6 +432,9 @@
     <t>VANESSA</t>
   </si>
   <si>
+    <t>JADE EMILY</t>
+  </si>
+  <si>
     <t>DIANA IVONNE</t>
   </si>
   <si>
@@ -432,9 +453,6 @@
     <t>ITZEL ABIGAIL</t>
   </si>
   <si>
-    <t>INGRID AMERICA</t>
-  </si>
-  <si>
     <t>JAIME</t>
   </si>
   <si>
@@ -469,24 +487,6 @@
   </si>
   <si>
     <t>FLOR GUADALUPE</t>
-  </si>
-  <si>
-    <t>GUILLEN</t>
-  </si>
-  <si>
-    <t>MANZANET</t>
-  </si>
-  <si>
-    <t>LINARES</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>EDITH</t>
-  </si>
-  <si>
-    <t>JADE EMILY</t>
   </si>
 </sst>
 </file>
@@ -994,7 +994,7 @@
         <v>5</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E4">
         <v>9</v>
@@ -1057,7 +1057,7 @@
         <v>5</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z4">
         <v>9</v>
@@ -1083,7 +1083,7 @@
         <v>8</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E5">
         <v>9</v>
@@ -1146,7 +1146,7 @@
         <v>8</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z5">
         <v>9</v>
@@ -1172,7 +1172,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -1235,7 +1235,7 @@
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z6">
         <v>6</v>
@@ -1261,7 +1261,7 @@
         <v>5</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E7">
         <v>7</v>
@@ -1324,7 +1324,7 @@
         <v>5</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z7">
         <v>7</v>
@@ -1350,7 +1350,7 @@
         <v>6</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1413,7 +1413,7 @@
         <v>6</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z8">
         <v>7</v>
@@ -1439,7 +1439,7 @@
         <v>9</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1502,7 +1502,7 @@
         <v>9</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z9">
         <v>8</v>
@@ -1528,7 +1528,7 @@
         <v>9</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E10">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>9</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z10">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>7</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E11">
         <v>7</v>
@@ -1680,7 +1680,7 @@
         <v>7</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z11">
         <v>7</v>
@@ -1706,7 +1706,7 @@
         <v>7</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E12">
         <v>8</v>
@@ -1769,7 +1769,7 @@
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z12">
         <v>8</v>
@@ -1795,7 +1795,7 @@
         <v>6</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E13">
         <v>6</v>
@@ -1858,7 +1858,7 @@
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z13">
         <v>6</v>
@@ -1884,7 +1884,7 @@
         <v>9</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E14">
         <v>8</v>
@@ -1947,7 +1947,7 @@
         <v>9</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z14">
         <v>8</v>
@@ -2014,7 +2014,7 @@
         <v>5</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E16">
         <v>6</v>
@@ -2077,7 +2077,7 @@
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z16">
         <v>6</v>
@@ -2103,7 +2103,7 @@
         <v>9</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E17">
         <v>7</v>
@@ -2166,7 +2166,7 @@
         <v>9</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z17">
         <v>7</v>
@@ -2192,7 +2192,7 @@
         <v>8</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E18">
         <v>8</v>
@@ -2255,7 +2255,7 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z18">
         <v>8</v>
@@ -2281,7 +2281,7 @@
         <v>8</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E19">
         <v>9</v>
@@ -2344,7 +2344,7 @@
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z19">
         <v>9</v>
@@ -2411,7 +2411,7 @@
         <v>7</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E21">
         <v>7</v>
@@ -2474,7 +2474,7 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z21">
         <v>7</v>
@@ -2500,7 +2500,7 @@
         <v>6</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E22">
         <v>7</v>
@@ -2563,7 +2563,7 @@
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z22">
         <v>7</v>
@@ -2589,7 +2589,7 @@
         <v>7</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E23">
         <v>7</v>
@@ -2652,7 +2652,7 @@
         <v>7</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z23">
         <v>7</v>
@@ -2678,7 +2678,7 @@
         <v>8</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E24">
         <v>9</v>
@@ -2741,7 +2741,7 @@
         <v>8</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z24">
         <v>9</v>
@@ -2767,7 +2767,7 @@
         <v>6</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E25">
         <v>7</v>
@@ -2830,7 +2830,7 @@
         <v>6</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z25">
         <v>7</v>
@@ -2856,7 +2856,7 @@
         <v>10</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E26">
         <v>9</v>
@@ -2919,7 +2919,7 @@
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z26">
         <v>9</v>
@@ -2945,7 +2945,7 @@
         <v>8</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E27">
         <v>8</v>
@@ -3008,7 +3008,7 @@
         <v>8</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z27">
         <v>8</v>
@@ -3034,10 +3034,10 @@
         <v>-1</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -3097,10 +3097,10 @@
         <v>-1</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA28">
         <v>5</v>
@@ -3123,7 +3123,7 @@
         <v>10</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E29">
         <v>9</v>
@@ -3186,7 +3186,7 @@
         <v>10</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z29">
         <v>9</v>
@@ -3212,7 +3212,7 @@
         <v>9</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E30">
         <v>7</v>
@@ -3275,7 +3275,7 @@
         <v>9</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z30">
         <v>7</v>
@@ -3301,7 +3301,7 @@
         <v>7</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E31">
         <v>6</v>
@@ -3364,7 +3364,7 @@
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z31">
         <v>6</v>
@@ -3390,7 +3390,7 @@
         <v>6</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E32">
         <v>6</v>
@@ -3453,7 +3453,7 @@
         <v>6</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z32">
         <v>6</v>
@@ -3479,7 +3479,7 @@
         <v>7</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E33">
         <v>7</v>
@@ -3542,7 +3542,7 @@
         <v>7</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z33">
         <v>7</v>
@@ -3568,7 +3568,7 @@
         <v>6</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E34">
         <v>5</v>
@@ -3631,7 +3631,7 @@
         <v>6</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z34">
         <v>5</v>
@@ -3657,7 +3657,7 @@
         <v>5</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E35">
         <v>6</v>
@@ -3720,7 +3720,7 @@
         <v>5</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z35">
         <v>6</v>
@@ -3746,7 +3746,7 @@
         <v>5</v>
       </c>
       <c r="D36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E36">
         <v>7</v>
@@ -3809,7 +3809,7 @@
         <v>5</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z36">
         <v>7</v>
@@ -3835,7 +3835,7 @@
         <v>5</v>
       </c>
       <c r="D37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E37">
         <v>5</v>
@@ -3898,7 +3898,7 @@
         <v>5</v>
       </c>
       <c r="Y37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z37">
         <v>5</v>
@@ -3924,7 +3924,7 @@
         <v>8</v>
       </c>
       <c r="D38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E38">
         <v>8</v>
@@ -3987,7 +3987,7 @@
         <v>8</v>
       </c>
       <c r="Y38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z38">
         <v>8</v>
@@ -4135,7 +4135,7 @@
         <v>80</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E4">
         <v>120</v>
@@ -4203,7 +4203,7 @@
         <v>100</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E5">
         <v>120</v>
@@ -4271,7 +4271,7 @@
         <v>80</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E6">
         <v>120</v>
@@ -4339,7 +4339,7 @@
         <v>75</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="E7">
         <v>120</v>
@@ -4407,7 +4407,7 @@
         <v>90</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E8">
         <v>120</v>
@@ -4475,7 +4475,7 @@
         <v>100</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E9">
         <v>120</v>
@@ -4543,7 +4543,7 @@
         <v>100</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E10">
         <v>120</v>
@@ -4611,7 +4611,7 @@
         <v>90</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>100</v>
@@ -4679,7 +4679,7 @@
         <v>80</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E12">
         <v>120</v>
@@ -4747,7 +4747,7 @@
         <v>100</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E13">
         <v>100</v>
@@ -4815,7 +4815,7 @@
         <v>100</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14">
         <v>120</v>
@@ -4915,7 +4915,7 @@
         <v>80</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E16">
         <v>93.3</v>
@@ -4983,7 +4983,7 @@
         <v>80</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E17">
         <v>120</v>
@@ -5051,7 +5051,7 @@
         <v>90</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E18">
         <v>120</v>
@@ -5119,7 +5119,7 @@
         <v>100</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E19">
         <v>120</v>
@@ -5219,7 +5219,7 @@
         <v>80</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E21">
         <v>120</v>
@@ -5287,7 +5287,7 @@
         <v>80</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E22">
         <v>120</v>
@@ -5355,7 +5355,7 @@
         <v>80</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E23">
         <v>120</v>
@@ -5423,7 +5423,7 @@
         <v>90</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24">
         <v>120</v>
@@ -5491,7 +5491,7 @@
         <v>80</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E25">
         <v>120</v>
@@ -5559,7 +5559,7 @@
         <v>100</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E26">
         <v>120</v>
@@ -5627,7 +5627,7 @@
         <v>100</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E27">
         <v>120</v>
@@ -5763,7 +5763,7 @@
         <v>100</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E29">
         <v>120</v>
@@ -5831,7 +5831,7 @@
         <v>80</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E30">
         <v>120</v>
@@ -5899,7 +5899,7 @@
         <v>80</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E31">
         <v>120</v>
@@ -5967,7 +5967,7 @@
         <v>100</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32">
         <v>120</v>
@@ -6035,7 +6035,7 @@
         <v>80</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E33">
         <v>120</v>
@@ -6103,7 +6103,7 @@
         <v>90</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E34">
         <v>93.3</v>
@@ -6171,7 +6171,7 @@
         <v>80</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E35">
         <v>93.3</v>
@@ -6239,7 +6239,7 @@
         <v>80</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E36">
         <v>120</v>
@@ -6307,7 +6307,7 @@
         <v>80</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E37">
         <v>66.7</v>
@@ -6375,7 +6375,7 @@
         <v>100</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E38">
         <v>120</v>
@@ -6493,22 +6493,25 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>60.61</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>39.39</v>
+      </c>
+      <c r="H2">
+        <v>5.9</v>
       </c>
       <c r="I2">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6685,22 +6688,22 @@
         <v>30</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8">
         <v>90.91</v>
       </c>
       <c r="G8">
-        <v>6.06</v>
+        <v>9.09</v>
       </c>
       <c r="H8">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>3.03</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6710,7 +6713,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6739,702 +6742,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>21330051920071</v>
+        <v>21330051920094</v>
       </c>
       <c r="B2" t="s">
         <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>118</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920074</v>
-      </c>
-      <c r="B3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D3" t="s">
-        <v>119</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920378</v>
-      </c>
-      <c r="B4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D4" t="s">
-        <v>120</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920075</v>
-      </c>
-      <c r="B5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D5" t="s">
-        <v>121</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920108</v>
-      </c>
-      <c r="B6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" t="s">
-        <v>95</v>
-      </c>
-      <c r="D6" t="s">
-        <v>122</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920076</v>
-      </c>
-      <c r="B7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" t="s">
-        <v>123</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920077</v>
-      </c>
-      <c r="B8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D8" t="s">
-        <v>124</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920078</v>
-      </c>
-      <c r="B9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C9" t="s">
-        <v>101</v>
-      </c>
-      <c r="D9" t="s">
-        <v>125</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920079</v>
-      </c>
-      <c r="B10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D10" t="s">
-        <v>126</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920260</v>
-      </c>
-      <c r="B11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" t="s">
-        <v>103</v>
-      </c>
-      <c r="D11" t="s">
-        <v>127</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920080</v>
-      </c>
-      <c r="B12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D12" t="s">
-        <v>124</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920082</v>
-      </c>
-      <c r="B13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" t="s">
-        <v>104</v>
-      </c>
-      <c r="D13" t="s">
-        <v>128</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920083</v>
-      </c>
-      <c r="B14" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" t="s">
-        <v>78</v>
-      </c>
-      <c r="D14" t="s">
-        <v>129</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920084</v>
-      </c>
-      <c r="B15" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" t="s">
-        <v>105</v>
-      </c>
-      <c r="D15" t="s">
-        <v>130</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920085</v>
-      </c>
-      <c r="B16" t="s">
-        <v>81</v>
-      </c>
-      <c r="C16" t="s">
-        <v>101</v>
-      </c>
-      <c r="D16" t="s">
-        <v>131</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920086</v>
-      </c>
-      <c r="B17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C17" t="s">
-        <v>106</v>
-      </c>
-      <c r="D17" t="s">
-        <v>132</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920302</v>
-      </c>
-      <c r="B18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" t="s">
-        <v>107</v>
-      </c>
-      <c r="D18" t="s">
-        <v>133</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920089</v>
-      </c>
-      <c r="B19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" t="s">
-        <v>107</v>
-      </c>
-      <c r="D19" t="s">
-        <v>134</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920092</v>
-      </c>
-      <c r="B20" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" t="s">
-        <v>108</v>
-      </c>
-      <c r="D20" t="s">
-        <v>135</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920093</v>
-      </c>
-      <c r="B21" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" t="s">
-        <v>88</v>
-      </c>
-      <c r="D21" t="s">
-        <v>136</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920094</v>
-      </c>
-      <c r="B22" t="s">
-        <v>85</v>
-      </c>
-      <c r="C22" t="s">
-        <v>109</v>
-      </c>
-      <c r="D22" t="s">
-        <v>137</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920094</v>
-      </c>
-      <c r="B23" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" t="s">
-        <v>109</v>
-      </c>
-      <c r="D23" t="s">
-        <v>137</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920094</v>
-      </c>
-      <c r="B24" t="s">
-        <v>85</v>
-      </c>
-      <c r="C24" t="s">
-        <v>109</v>
-      </c>
-      <c r="D24" t="s">
-        <v>137</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920096</v>
-      </c>
-      <c r="B25" t="s">
-        <v>85</v>
-      </c>
-      <c r="C25" t="s">
-        <v>110</v>
-      </c>
-      <c r="D25" t="s">
-        <v>138</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920097</v>
-      </c>
-      <c r="B26" t="s">
-        <v>86</v>
-      </c>
-      <c r="C26" t="s">
-        <v>111</v>
-      </c>
-      <c r="D26" t="s">
-        <v>139</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920099</v>
-      </c>
-      <c r="B27" t="s">
-        <v>87</v>
-      </c>
-      <c r="C27" t="s">
-        <v>85</v>
-      </c>
-      <c r="D27" t="s">
-        <v>140</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920100</v>
-      </c>
-      <c r="B28" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" t="s">
-        <v>112</v>
-      </c>
-      <c r="D28" t="s">
-        <v>141</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>21330051920383</v>
-      </c>
-      <c r="B29" t="s">
-        <v>89</v>
-      </c>
-      <c r="C29" t="s">
-        <v>90</v>
-      </c>
-      <c r="D29" t="s">
-        <v>142</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051920102</v>
-      </c>
-      <c r="B30" t="s">
-        <v>90</v>
-      </c>
-      <c r="C30" t="s">
-        <v>72</v>
-      </c>
-      <c r="D30" t="s">
-        <v>143</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920103</v>
-      </c>
-      <c r="B31" t="s">
-        <v>91</v>
-      </c>
-      <c r="C31" t="s">
-        <v>81</v>
-      </c>
-      <c r="D31" t="s">
-        <v>144</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920104</v>
-      </c>
-      <c r="B32" t="s">
-        <v>92</v>
-      </c>
-      <c r="C32" t="s">
-        <v>113</v>
-      </c>
-      <c r="D32" t="s">
-        <v>145</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920105</v>
-      </c>
-      <c r="B33" t="s">
-        <v>93</v>
-      </c>
-      <c r="C33" t="s">
-        <v>114</v>
-      </c>
-      <c r="D33" t="s">
-        <v>146</v>
-      </c>
-      <c r="E33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920107</v>
-      </c>
-      <c r="B34" t="s">
-        <v>94</v>
-      </c>
-      <c r="C34" t="s">
-        <v>115</v>
-      </c>
-      <c r="D34" t="s">
-        <v>147</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>21330051920109</v>
-      </c>
-      <c r="B35" t="s">
-        <v>95</v>
-      </c>
-      <c r="C35" t="s">
-        <v>116</v>
-      </c>
-      <c r="D35" t="s">
-        <v>148</v>
-      </c>
-      <c r="E35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920387</v>
-      </c>
-      <c r="B36" t="s">
-        <v>96</v>
-      </c>
-      <c r="C36" t="s">
-        <v>117</v>
-      </c>
-      <c r="D36" t="s">
-        <v>149</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -7473,16 +6796,16 @@
         <v>21330051920094</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>137</v>
+        <v>72</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -7490,16 +6813,16 @@
         <v>21330051920071</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -7507,16 +6830,16 @@
         <v>21330051920074</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -7524,16 +6847,16 @@
         <v>20330051920378</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -7541,16 +6864,16 @@
         <v>21330051920075</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D6" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -7558,16 +6881,16 @@
         <v>21330051920108</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -7575,16 +6898,16 @@
         <v>21330051920076</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -7592,16 +6915,16 @@
         <v>21330051920077</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D9" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -7609,16 +6932,16 @@
         <v>21330051920078</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D10" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -7626,418 +6949,418 @@
         <v>21330051920079</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D11" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920260</v>
+        <v>19330051920195</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D12" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920080</v>
+        <v>21330051920260</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="D13" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920082</v>
+        <v>21330051920080</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="D14" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920083</v>
+        <v>21330051920082</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="D15" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920084</v>
+        <v>21330051920083</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="D16" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920085</v>
+        <v>21330051920084</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="D17" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920086</v>
+        <v>19330051920286</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D18" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920302</v>
+        <v>21330051920085</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920089</v>
+        <v>21330051920086</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D20" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920092</v>
+        <v>20330051920302</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D21" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920093</v>
+        <v>21330051920089</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="D22" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920096</v>
+        <v>21330051920092</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D23" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920097</v>
+        <v>21330051920093</v>
       </c>
       <c r="B24" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="D24" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920099</v>
+        <v>21330051920096</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="C25" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="D25" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920100</v>
+        <v>21330051920097</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D26" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920383</v>
+        <v>21330051920099</v>
       </c>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="D27" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920102</v>
+        <v>21330051920100</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>72</v>
+        <v>117</v>
       </c>
       <c r="D28" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920103</v>
+        <v>21330051920383</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D29" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920104</v>
+        <v>21330051920102</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="D30" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920105</v>
+        <v>21330051920103</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="D31" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920107</v>
+        <v>21330051920104</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C32" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D32" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920109</v>
+        <v>21330051920105</v>
       </c>
       <c r="B33" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D33" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920387</v>
+        <v>21330051920107</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C34" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D34" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>19330051920195</v>
+        <v>21330051920109</v>
       </c>
       <c r="B35" t="s">
-        <v>150</v>
+        <v>99</v>
       </c>
       <c r="C35" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="D35" t="s">
         <v>154</v>
@@ -8048,13 +7371,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>19330051920286</v>
+        <v>21330051920387</v>
       </c>
       <c r="B36" t="s">
-        <v>151</v>
+        <v>100</v>
       </c>
       <c r="C36" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="D36" t="s">
         <v>155</v>
@@ -8070,7 +7393,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8105,13 +7428,13 @@
         <v>20330051920378</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D2" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -8120,7 +7443,7 @@
         <v>60</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -8128,13 +7451,13 @@
         <v>20330051920378</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -8148,16 +7471,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920076</v>
+        <v>21330051920260</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="D4" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -8171,39 +7494,39 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920076</v>
+        <v>21330051920260</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="D5" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920302</v>
+        <v>21330051920100</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="D6" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -8212,21 +7535,21 @@
         <v>60</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920302</v>
+        <v>21330051920100</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="D7" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -8240,39 +7563,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920100</v>
+        <v>21330051920107</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D8" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920100</v>
+        <v>21330051920107</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C9" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D9" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -8286,39 +7609,39 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920074</v>
+        <v>21330051920076</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920075</v>
+        <v>21330051920080</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -8327,21 +7650,21 @@
         <v>60</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920108</v>
+        <v>21330051920084</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="D12" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -8350,21 +7673,21 @@
         <v>60</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920079</v>
+        <v>21330051920086</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="D13" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -8373,44 +7696,44 @@
         <v>60</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920080</v>
+        <v>20330051920302</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="D14" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920083</v>
+        <v>21330051920092</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="D15" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
@@ -8419,21 +7742,21 @@
         <v>60</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920084</v>
+        <v>21330051920097</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C16" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="D16" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
@@ -8442,21 +7765,21 @@
         <v>60</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920085</v>
+        <v>21330051920383</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D17" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
@@ -8465,260 +7788,7 @@
         <v>60</v>
       </c>
       <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920086</v>
-      </c>
-      <c r="B18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" t="s">
-        <v>106</v>
-      </c>
-      <c r="D18" t="s">
-        <v>132</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>60</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920089</v>
-      </c>
-      <c r="B19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" t="s">
-        <v>107</v>
-      </c>
-      <c r="D19" t="s">
-        <v>134</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>60</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920092</v>
-      </c>
-      <c r="B20" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" t="s">
-        <v>108</v>
-      </c>
-      <c r="D20" t="s">
-        <v>135</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>60</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920093</v>
-      </c>
-      <c r="B21" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" t="s">
-        <v>88</v>
-      </c>
-      <c r="D21" t="s">
-        <v>136</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920096</v>
-      </c>
-      <c r="B22" t="s">
-        <v>85</v>
-      </c>
-      <c r="C22" t="s">
-        <v>110</v>
-      </c>
-      <c r="D22" t="s">
-        <v>138</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>60</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920097</v>
-      </c>
-      <c r="B23" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" t="s">
-        <v>111</v>
-      </c>
-      <c r="D23" t="s">
-        <v>139</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>60</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920099</v>
-      </c>
-      <c r="B24" t="s">
-        <v>87</v>
-      </c>
-      <c r="C24" t="s">
-        <v>85</v>
-      </c>
-      <c r="D24" t="s">
-        <v>140</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>60</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>21330051920383</v>
-      </c>
-      <c r="B25" t="s">
-        <v>89</v>
-      </c>
-      <c r="C25" t="s">
-        <v>90</v>
-      </c>
-      <c r="D25" t="s">
-        <v>142</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>60</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>21330051920102</v>
-      </c>
-      <c r="B26" t="s">
-        <v>90</v>
-      </c>
-      <c r="C26" t="s">
-        <v>72</v>
-      </c>
-      <c r="D26" t="s">
-        <v>143</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>60</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>21330051920104</v>
-      </c>
-      <c r="B27" t="s">
-        <v>92</v>
-      </c>
-      <c r="C27" t="s">
-        <v>113</v>
-      </c>
-      <c r="D27" t="s">
-        <v>145</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>60</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>21330051920387</v>
-      </c>
-      <c r="B28" t="s">
-        <v>96</v>
-      </c>
-      <c r="C28" t="s">
-        <v>117</v>
-      </c>
-      <c r="D28" t="s">
-        <v>149</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>60</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/4ALCV - Estadisticos 20222.xlsx
+++ b/grupos/4ALCV - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="159">
   <si>
     <t>Materia</t>
   </si>
@@ -144,6 +144,9 @@
     <t>ROJAS MORENO ALONDRA YURIDIA</t>
   </si>
   <si>
+    <t>ROMERO RAMIREZ CITLALI ESPERANZA</t>
+  </si>
+  <si>
     <t>RUGERIO SANCHEZ KIMBERLY</t>
   </si>
   <si>
@@ -231,226 +234,232 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>CITLALI ESPERANZA</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>ELPIDIO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GUILLEN</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MANZANET</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>RUGERIO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>TENTZOHUA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>LAGUNES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>VALIENTE</t>
+  </si>
+  <si>
+    <t>LINARES</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
     <t>BRAVO</t>
   </si>
   <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>QUIÑONES</t>
+  </si>
+  <si>
+    <t>MENA</t>
+  </si>
+  <si>
+    <t>LEÓN</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>CRISTAL YOSELIN</t>
+  </si>
+  <si>
+    <t>REYLI</t>
+  </si>
+  <si>
+    <t>EVELYN JOHANA</t>
+  </si>
+  <si>
+    <t>MARYFER</t>
+  </si>
+  <si>
+    <t>YARED</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>MIROSLAVA</t>
+  </si>
+  <si>
+    <t>BERENICE</t>
+  </si>
+  <si>
+    <t>EDITH</t>
+  </si>
+  <si>
+    <t>MARIA TERESA</t>
+  </si>
+  <si>
+    <t>VANESSA AMAIRANY</t>
+  </si>
+  <si>
+    <t>REGINA ISABEL</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>JADE EMILY</t>
+  </si>
+  <si>
+    <t>DIANA IVONNE</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>JOSE ISAAC</t>
+  </si>
+  <si>
+    <t>FATIMA MARILYN</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>ITZEL ABIGAIL</t>
+  </si>
+  <si>
     <t>INGRID AMERICA</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>ELPIDIO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GUILLEN</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MANZANET</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>RUGERIO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SANJUAN</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>TENTZOHUA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>VALIENTE</t>
-  </si>
-  <si>
-    <t>LINARES</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>BRETON</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>QUIÑONES</t>
-  </si>
-  <si>
-    <t>MENA</t>
-  </si>
-  <si>
-    <t>LEÓN</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>CRISTAL YOSELIN</t>
-  </si>
-  <si>
-    <t>REYLI</t>
-  </si>
-  <si>
-    <t>EVELYN JOHANA</t>
-  </si>
-  <si>
-    <t>MARYFER</t>
-  </si>
-  <si>
-    <t>YARED</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
-  </si>
-  <si>
-    <t>BERENICE</t>
-  </si>
-  <si>
-    <t>EDITH</t>
-  </si>
-  <si>
-    <t>MARIA TERESA</t>
-  </si>
-  <si>
-    <t>VANESSA AMAIRANY</t>
-  </si>
-  <si>
-    <t>REGINA ISABEL</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>JADE EMILY</t>
-  </si>
-  <si>
-    <t>DIANA IVONNE</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>JOSE ISAAC</t>
-  </si>
-  <si>
-    <t>FATIMA MARILYN</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>ITZEL ABIGAIL</t>
   </si>
   <si>
     <t>JAIME</t>
@@ -844,7 +853,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC38"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -3031,7 +3040,7 @@
         <v>0</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D28">
         <v>5</v>
@@ -3094,7 +3103,7 @@
         <v>5</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y28">
         <v>5</v>
@@ -3384,25 +3393,25 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="C32">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="D32">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="E32">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="F32">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="G32">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="H32">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -3447,25 +3456,25 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="X32">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="Y32">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="Z32">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="AA32">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="AB32">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="AC32">
-        <v>9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3473,25 +3482,25 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -3536,25 +3545,25 @@
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC33">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3562,25 +3571,25 @@
         <v>43</v>
       </c>
       <c r="B34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D34">
         <v>6</v>
       </c>
       <c r="E34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G34">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H34">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -3625,25 +3634,25 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y34">
         <v>6</v>
       </c>
       <c r="Z34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB34">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC34">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -3651,25 +3660,25 @@
         <v>44</v>
       </c>
       <c r="B35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F35">
         <v>0</v>
       </c>
       <c r="G35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -3714,25 +3723,25 @@
         <v>-1</v>
       </c>
       <c r="W35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA35">
         <v>5</v>
       </c>
       <c r="AB35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC35">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:29">
@@ -3746,19 +3755,19 @@
         <v>5</v>
       </c>
       <c r="D36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F36">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G36">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H36">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I36">
         <v>-1</v>
@@ -3809,19 +3818,19 @@
         <v>5</v>
       </c>
       <c r="Y36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA36">
         <v>5</v>
       </c>
       <c r="AB36">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC36">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:29">
@@ -3829,25 +3838,25 @@
         <v>46</v>
       </c>
       <c r="B37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C37">
         <v>5</v>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G37">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H37">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I37">
         <v>-1</v>
@@ -3892,25 +3901,25 @@
         <v>-1</v>
       </c>
       <c r="W37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X37">
         <v>5</v>
       </c>
       <c r="Y37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA37">
         <v>5</v>
       </c>
       <c r="AB37">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC37">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:29">
@@ -3918,25 +3927,25 @@
         <v>47</v>
       </c>
       <c r="B38">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C38">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D38">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E38">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F38">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G38">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H38">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -3981,24 +3990,113 @@
         <v>-1</v>
       </c>
       <c r="W38">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X38">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y38">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z38">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA38">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB38">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AC38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:29">
+      <c r="A39" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39">
+        <v>7</v>
+      </c>
+      <c r="C39">
+        <v>8</v>
+      </c>
+      <c r="D39">
+        <v>8</v>
+      </c>
+      <c r="E39">
+        <v>8</v>
+      </c>
+      <c r="F39">
+        <v>8</v>
+      </c>
+      <c r="G39">
+        <v>9</v>
+      </c>
+      <c r="H39">
+        <v>8</v>
+      </c>
+      <c r="I39">
+        <v>-1</v>
+      </c>
+      <c r="J39">
+        <v>-1</v>
+      </c>
+      <c r="K39">
+        <v>-1</v>
+      </c>
+      <c r="L39">
+        <v>-1</v>
+      </c>
+      <c r="M39">
+        <v>-1</v>
+      </c>
+      <c r="N39">
+        <v>-1</v>
+      </c>
+      <c r="O39">
+        <v>-1</v>
+      </c>
+      <c r="P39">
+        <v>-1</v>
+      </c>
+      <c r="Q39">
+        <v>-1</v>
+      </c>
+      <c r="R39">
+        <v>-1</v>
+      </c>
+      <c r="S39">
+        <v>-1</v>
+      </c>
+      <c r="T39">
+        <v>-1</v>
+      </c>
+      <c r="U39">
+        <v>-1</v>
+      </c>
+      <c r="V39">
+        <v>-1</v>
+      </c>
+      <c r="W39">
+        <v>7</v>
+      </c>
+      <c r="X39">
+        <v>8</v>
+      </c>
+      <c r="Y39">
+        <v>8</v>
+      </c>
+      <c r="Z39">
+        <v>8</v>
+      </c>
+      <c r="AA39">
+        <v>8</v>
+      </c>
+      <c r="AB39">
+        <v>9</v>
+      </c>
+      <c r="AC39">
         <v>8</v>
       </c>
     </row>
@@ -4015,7 +4113,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V38"/>
+  <dimension ref="A1:V39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -4024,7 +4122,7 @@
     <row r="1" spans="1:22">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -4033,7 +4131,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -4042,7 +4140,7 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -5692,7 +5790,7 @@
         <v>0</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -5961,25 +6059,25 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G32">
-        <v>105.7</v>
+        <v>0</v>
       </c>
       <c r="H32">
-        <v>106.7</v>
+        <v>0</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -6029,19 +6127,19 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C33">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D33">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E33">
         <v>120</v>
       </c>
       <c r="F33">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G33">
         <v>105.7</v>
@@ -6100,16 +6198,16 @@
         <v>115</v>
       </c>
       <c r="C34">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D34">
         <v>75</v>
       </c>
       <c r="E34">
-        <v>93.3</v>
+        <v>120</v>
       </c>
       <c r="F34">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="G34">
         <v>105.7</v>
@@ -6168,16 +6266,16 @@
         <v>115</v>
       </c>
       <c r="C35">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="D35">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E35">
         <v>93.3</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G35">
         <v>105.7</v>
@@ -6242,10 +6340,10 @@
         <v>80</v>
       </c>
       <c r="E36">
-        <v>120</v>
+        <v>93.3</v>
       </c>
       <c r="F36">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G36">
         <v>105.7</v>
@@ -6301,7 +6399,7 @@
         <v>46</v>
       </c>
       <c r="B37">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C37">
         <v>80</v>
@@ -6310,16 +6408,16 @@
         <v>80</v>
       </c>
       <c r="E37">
-        <v>66.7</v>
+        <v>120</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G37">
         <v>105.7</v>
       </c>
       <c r="H37">
-        <v>93.3</v>
+        <v>106.7</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -6369,66 +6467,134 @@
         <v>47</v>
       </c>
       <c r="B38">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="C38">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D38">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E38">
-        <v>120</v>
+        <v>66.7</v>
       </c>
       <c r="F38">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G38">
         <v>105.7</v>
       </c>
       <c r="H38">
+        <v>93.3</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38">
+        <v>0</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22">
+      <c r="A39" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39">
+        <v>120</v>
+      </c>
+      <c r="C39">
+        <v>100</v>
+      </c>
+      <c r="D39">
+        <v>100</v>
+      </c>
+      <c r="E39">
+        <v>120</v>
+      </c>
+      <c r="F39">
+        <v>100</v>
+      </c>
+      <c r="G39">
+        <v>105.7</v>
+      </c>
+      <c r="H39">
         <v>106.7</v>
       </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
-      <c r="K38">
-        <v>0</v>
-      </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-      <c r="M38">
-        <v>0</v>
-      </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
-      <c r="O38">
-        <v>0</v>
-      </c>
-      <c r="P38">
-        <v>0</v>
-      </c>
-      <c r="Q38">
-        <v>0</v>
-      </c>
-      <c r="R38">
-        <v>0</v>
-      </c>
-      <c r="S38">
-        <v>0</v>
-      </c>
-      <c r="T38">
-        <v>0</v>
-      </c>
-      <c r="U38">
-        <v>0</v>
-      </c>
-      <c r="V38">
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>0</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <v>0</v>
+      </c>
+      <c r="V39">
         <v>0</v>
       </c>
     </row>
@@ -6455,31 +6621,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -6487,10 +6653,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2">
         <v>20</v>
@@ -6499,19 +6665,19 @@
         <v>13</v>
       </c>
       <c r="F2">
-        <v>60.61</v>
+        <v>58.82</v>
       </c>
       <c r="G2">
-        <v>39.39</v>
+        <v>38.24</v>
       </c>
       <c r="H2">
         <v>5.9</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6519,10 +6685,10 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3">
         <v>24</v>
@@ -6531,19 +6697,19 @@
         <v>11</v>
       </c>
       <c r="F3">
-        <v>68.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="G3">
-        <v>31.43</v>
+        <v>30.56</v>
       </c>
       <c r="H3">
         <v>6.8</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -6551,10 +6717,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4">
         <v>25</v>
@@ -6563,19 +6729,19 @@
         <v>8</v>
       </c>
       <c r="F4">
-        <v>75.76000000000001</v>
+        <v>73.53</v>
       </c>
       <c r="G4">
-        <v>24.24</v>
+        <v>23.53</v>
       </c>
       <c r="H4">
         <v>6.8</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -6583,31 +6749,31 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5">
         <v>26</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>78.79000000000001</v>
+        <v>76.47</v>
       </c>
       <c r="G5">
-        <v>18.18</v>
+        <v>20.59</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="I5">
         <v>1</v>
       </c>
       <c r="J5">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -6615,10 +6781,10 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6">
         <v>29</v>
@@ -6627,19 +6793,19 @@
         <v>6</v>
       </c>
       <c r="F6">
-        <v>82.86</v>
+        <v>80.56</v>
       </c>
       <c r="G6">
-        <v>17.14</v>
+        <v>16.67</v>
       </c>
       <c r="H6">
         <v>8.1</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -6647,10 +6813,10 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7">
         <v>30</v>
@@ -6659,19 +6825,19 @@
         <v>5</v>
       </c>
       <c r="F7">
-        <v>85.70999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="G7">
-        <v>14.29</v>
+        <v>13.89</v>
       </c>
       <c r="H7">
         <v>7.6</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -6679,10 +6845,10 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8">
         <v>30</v>
@@ -6691,19 +6857,19 @@
         <v>3</v>
       </c>
       <c r="F8">
-        <v>90.91</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="G8">
-        <v>9.09</v>
+        <v>8.82</v>
       </c>
       <c r="H8">
         <v>7.2</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
   </sheetData>
@@ -6713,7 +6879,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6722,16 +6888,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -6742,22 +6908,142 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>21330051920094</v>
+        <v>21330051920101</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>21330051920101</v>
+      </c>
+      <c r="B3" t="s">
         <v>71</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
         <v>72</v>
       </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="D3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>21330051920101</v>
+      </c>
+      <c r="B4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" t="s">
         <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>21330051920101</v>
+      </c>
+      <c r="B5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>21330051920101</v>
+      </c>
+      <c r="B6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>21330051920101</v>
+      </c>
+      <c r="B7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>21330051920101</v>
+      </c>
+      <c r="B8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -6767,7 +7053,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6776,36 +7062,36 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920094</v>
+        <v>21330051920101</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -6813,13 +7099,13 @@
         <v>21330051920071</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -6830,13 +7116,13 @@
         <v>21330051920074</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -6847,13 +7133,13 @@
         <v>20330051920378</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -6864,13 +7150,13 @@
         <v>21330051920075</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -6881,13 +7167,13 @@
         <v>21330051920108</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -6898,13 +7184,13 @@
         <v>21330051920076</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -6915,13 +7201,13 @@
         <v>21330051920077</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D9" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -6932,13 +7218,13 @@
         <v>21330051920078</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -6949,13 +7235,13 @@
         <v>21330051920079</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -6966,13 +7252,13 @@
         <v>19330051920195</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -6983,13 +7269,13 @@
         <v>21330051920260</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -7000,13 +7286,13 @@
         <v>21330051920080</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -7017,13 +7303,13 @@
         <v>21330051920082</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -7034,13 +7320,13 @@
         <v>21330051920083</v>
       </c>
       <c r="B16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" t="s">
         <v>83</v>
       </c>
-      <c r="C16" t="s">
-        <v>82</v>
-      </c>
       <c r="D16" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -7051,13 +7337,13 @@
         <v>21330051920084</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D17" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -7068,13 +7354,13 @@
         <v>19330051920286</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C18" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -7085,13 +7371,13 @@
         <v>21330051920085</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D19" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -7102,13 +7388,13 @@
         <v>21330051920086</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D20" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -7119,13 +7405,13 @@
         <v>20330051920302</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D21" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -7136,13 +7422,13 @@
         <v>21330051920089</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D22" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -7153,13 +7439,13 @@
         <v>21330051920092</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D23" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -7170,13 +7456,13 @@
         <v>21330051920093</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -7184,16 +7470,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920096</v>
+        <v>21330051920094</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="C25" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D25" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -7201,16 +7487,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920097</v>
+        <v>21330051920096</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D26" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -7218,16 +7504,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920099</v>
+        <v>21330051920097</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="D27" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -7235,16 +7521,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920100</v>
+        <v>21330051920099</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="C28" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="D28" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -7252,16 +7538,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920383</v>
+        <v>21330051920100</v>
       </c>
       <c r="B29" t="s">
         <v>93</v>
       </c>
       <c r="C29" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="D29" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -7269,16 +7555,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920102</v>
+        <v>21330051920383</v>
       </c>
       <c r="B30" t="s">
         <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="D30" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -7286,16 +7572,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920103</v>
+        <v>21330051920102</v>
       </c>
       <c r="B31" t="s">
         <v>95</v>
       </c>
       <c r="C31" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="D31" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -7303,16 +7589,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920104</v>
+        <v>21330051920103</v>
       </c>
       <c r="B32" t="s">
         <v>96</v>
       </c>
       <c r="C32" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="D32" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -7320,16 +7606,16 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920105</v>
+        <v>21330051920104</v>
       </c>
       <c r="B33" t="s">
         <v>97</v>
       </c>
       <c r="C33" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D33" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -7337,16 +7623,16 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920107</v>
+        <v>21330051920105</v>
       </c>
       <c r="B34" t="s">
         <v>98</v>
       </c>
       <c r="C34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D34" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -7354,16 +7640,16 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920109</v>
+        <v>21330051920107</v>
       </c>
       <c r="B35" t="s">
         <v>99</v>
       </c>
       <c r="C35" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D35" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -7371,18 +7657,35 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>21330051920387</v>
+        <v>21330051920109</v>
       </c>
       <c r="B36" t="s">
         <v>100</v>
       </c>
       <c r="C36" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D36" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37">
+        <v>21330051920387</v>
+      </c>
+      <c r="B37" t="s">
+        <v>101</v>
+      </c>
+      <c r="C37" t="s">
+        <v>124</v>
+      </c>
+      <c r="D37" t="s">
+        <v>158</v>
+      </c>
+      <c r="E37">
         <v>0</v>
       </c>
     </row>
@@ -7402,22 +7705,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -7428,19 +7731,19 @@
         <v>20330051920378</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7451,19 +7754,19 @@
         <v>20330051920378</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7474,19 +7777,19 @@
         <v>21330051920260</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7497,19 +7800,19 @@
         <v>21330051920260</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7520,19 +7823,19 @@
         <v>21330051920100</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D6" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7543,19 +7846,19 @@
         <v>21330051920100</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D7" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7566,19 +7869,19 @@
         <v>21330051920107</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D8" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7589,19 +7892,19 @@
         <v>21330051920107</v>
       </c>
       <c r="B9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7612,19 +7915,19 @@
         <v>21330051920076</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7635,19 +7938,19 @@
         <v>21330051920080</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7658,19 +7961,19 @@
         <v>21330051920084</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D12" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -7681,19 +7984,19 @@
         <v>21330051920086</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7704,19 +8007,19 @@
         <v>20330051920302</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D14" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -7727,19 +8030,19 @@
         <v>21330051920092</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D15" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -7750,19 +8053,19 @@
         <v>21330051920097</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D16" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -7773,19 +8076,19 @@
         <v>21330051920383</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D17" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G17">
         <v>5</v>

--- a/grupos/4ALCV - Estadisticos 20222.xlsx
+++ b/grupos/4ALCV - Estadisticos 20222.xlsx
@@ -207,7 +207,7 @@
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>Mateos Sanchez Jorge</t>
   </si>
   <si>
     <t>Muñoz Rivadeneyra Salvador</t>

--- a/grupos/4ALCV - Estadisticos 20222.xlsx
+++ b/grupos/4ALCV - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="111">
   <si>
     <t>Materia</t>
   </si>
@@ -207,18 +206,18 @@
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
+    <t>Gomez Lopez Javier</t>
+  </si>
+  <si>
+    <t>Rivera Serra Alma Lilian</t>
+  </si>
+  <si>
     <t>Mateos Sanchez Jorge</t>
   </si>
   <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>Gomez Lopez Javier</t>
-  </si>
-  <si>
-    <t>Rivera Serra Alma Lilian</t>
-  </si>
-  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
@@ -243,10 +242,10 @@
     <t>CITLALI ESPERANZA</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>TENTZOHUA</t>
   </si>
   <si>
     <t>CRUZ</t>
@@ -255,151 +254,67 @@
     <t>ESPIRITU</t>
   </si>
   <si>
-    <t>ELPIDIO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GUILLEN</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>RUGERIO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>LEÓN</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MANZANET</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>RUGERIO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SANJUAN</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>TENTZOHUA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>LAGUNES</t>
+    <t>DE LA LUZ</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>VALIENTE</t>
-  </si>
-  <si>
-    <t>LINARES</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>BRETON</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
     <t>RIVERA</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>HIPOLITO</t>
   </si>
   <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
     <t>TEQUIHUATLE</t>
   </si>
   <si>
     <t>MORENO</t>
   </si>
   <si>
-    <t>QUIÑONES</t>
-  </si>
-  <si>
-    <t>MENA</t>
-  </si>
-  <si>
-    <t>LEÓN</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>CRISTAL YOSELIN</t>
+    <t>YARED</t>
+  </si>
+  <si>
+    <t>RUBI</t>
   </si>
   <si>
     <t>REYLI</t>
@@ -408,69 +323,27 @@
     <t>EVELYN JOHANA</t>
   </si>
   <si>
-    <t>MARYFER</t>
-  </si>
-  <si>
-    <t>YARED</t>
-  </si>
-  <si>
     <t>MARIA FERNANDA</t>
   </si>
   <si>
-    <t>MIROSLAVA</t>
-  </si>
-  <si>
-    <t>BERENICE</t>
-  </si>
-  <si>
-    <t>EDITH</t>
-  </si>
-  <si>
-    <t>MARIA TERESA</t>
-  </si>
-  <si>
-    <t>VANESSA AMAIRANY</t>
-  </si>
-  <si>
     <t>REGINA ISABEL</t>
   </si>
   <si>
     <t>VANESSA</t>
   </si>
   <si>
-    <t>JADE EMILY</t>
-  </si>
-  <si>
     <t>DIANA IVONNE</t>
   </si>
   <si>
     <t>FATIMA</t>
   </si>
   <si>
-    <t>JOSE ISAAC</t>
-  </si>
-  <si>
-    <t>FATIMA MARILYN</t>
-  </si>
-  <si>
     <t>JOSE JULIAN</t>
   </si>
   <si>
-    <t>ITZEL ABIGAIL</t>
-  </si>
-  <si>
-    <t>INGRID AMERICA</t>
-  </si>
-  <si>
-    <t>JAIME</t>
-  </si>
-  <si>
     <t>JAZMIN</t>
   </si>
   <si>
-    <t>LUIS REY</t>
-  </si>
-  <si>
     <t>ALONDRA YURIDIA</t>
   </si>
   <si>
@@ -478,30 +351,15 @@
   </si>
   <si>
     <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>ALMA KAREN</t>
-  </si>
-  <si>
-    <t>GABRIELA</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>RUBI</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>FLOR GUADALUPE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -554,11 +412,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1024,13 +883,13 @@
         <v>-1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L4">
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1072,7 +931,7 @@
         <v>9</v>
       </c>
       <c r="AA4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB4">
         <v>8</v>
@@ -1113,13 +972,13 @@
         <v>-1</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1155,13 +1014,13 @@
         <v>8</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z5">
         <v>9</v>
       </c>
       <c r="AA5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB5">
         <v>9</v>
@@ -1187,7 +1046,7 @@
         <v>6</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G6">
         <v>9</v>
@@ -1202,13 +1061,13 @@
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1250,7 +1109,7 @@
         <v>6</v>
       </c>
       <c r="AA6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB6">
         <v>9</v>
@@ -1276,7 +1135,7 @@
         <v>7</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -1291,13 +1150,13 @@
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1339,7 +1198,7 @@
         <v>7</v>
       </c>
       <c r="AA7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB7">
         <v>5</v>
@@ -1380,13 +1239,13 @@
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1428,7 +1287,7 @@
         <v>7</v>
       </c>
       <c r="AA8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB8">
         <v>8</v>
@@ -1469,13 +1328,13 @@
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L9">
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1511,7 +1370,7 @@
         <v>9</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z9">
         <v>8</v>
@@ -1558,13 +1417,13 @@
         <v>-1</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1600,13 +1459,13 @@
         <v>9</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z10">
         <v>8</v>
       </c>
       <c r="AA10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB10">
         <v>10</v>
@@ -1647,13 +1506,13 @@
         <v>-1</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1689,13 +1548,13 @@
         <v>7</v>
       </c>
       <c r="Y11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z11">
         <v>7</v>
       </c>
       <c r="AA11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB11">
         <v>9</v>
@@ -1736,13 +1595,13 @@
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1778,7 +1637,7 @@
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z12">
         <v>8</v>
@@ -1810,7 +1669,7 @@
         <v>6</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -1825,13 +1684,13 @@
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L13">
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1867,7 +1726,7 @@
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z13">
         <v>6</v>
@@ -1914,13 +1773,13 @@
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1962,7 +1821,7 @@
         <v>8</v>
       </c>
       <c r="AA14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB14">
         <v>10</v>
@@ -1985,7 +1844,7 @@
         <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -2003,7 +1862,7 @@
         <v>-1</v>
       </c>
       <c r="AA15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB15">
         <v>10</v>
@@ -2044,13 +1903,13 @@
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -2086,7 +1945,7 @@
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z16">
         <v>6</v>
@@ -2133,13 +1992,13 @@
         <v>-1</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2181,7 +2040,7 @@
         <v>7</v>
       </c>
       <c r="AA17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB17">
         <v>7</v>
@@ -2222,13 +2081,13 @@
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L18">
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2264,13 +2123,13 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z18">
         <v>8</v>
       </c>
       <c r="AA18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB18">
         <v>8</v>
@@ -2311,13 +2170,13 @@
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2359,7 +2218,7 @@
         <v>9</v>
       </c>
       <c r="AA19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB19">
         <v>9</v>
@@ -2382,7 +2241,7 @@
         <v>8</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2441,13 +2300,13 @@
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L21">
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2483,13 +2342,13 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z21">
         <v>7</v>
       </c>
       <c r="AA21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB21">
         <v>9</v>
@@ -2530,13 +2389,13 @@
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2578,7 +2437,7 @@
         <v>7</v>
       </c>
       <c r="AA22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB22">
         <v>8</v>
@@ -2604,7 +2463,7 @@
         <v>7</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G23">
         <v>8</v>
@@ -2619,13 +2478,13 @@
         <v>-1</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2667,7 +2526,7 @@
         <v>7</v>
       </c>
       <c r="AA23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB23">
         <v>8</v>
@@ -2708,13 +2567,13 @@
         <v>-1</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2756,7 +2615,7 @@
         <v>9</v>
       </c>
       <c r="AA24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB24">
         <v>9</v>
@@ -2797,13 +2656,13 @@
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L25">
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2845,7 +2704,7 @@
         <v>7</v>
       </c>
       <c r="AA25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB25">
         <v>10</v>
@@ -2886,13 +2745,13 @@
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L26">
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2928,13 +2787,13 @@
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z26">
         <v>9</v>
       </c>
       <c r="AA26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB26">
         <v>10</v>
@@ -2975,13 +2834,13 @@
         <v>-1</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L27">
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -3023,7 +2882,7 @@
         <v>8</v>
       </c>
       <c r="AA27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB27">
         <v>10</v>
@@ -3064,13 +2923,13 @@
         <v>-1</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -3153,13 +3012,13 @@
         <v>-1</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -3201,7 +3060,7 @@
         <v>9</v>
       </c>
       <c r="AA29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB29">
         <v>10</v>
@@ -3242,13 +3101,13 @@
         <v>-1</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L30">
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3284,13 +3143,13 @@
         <v>9</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z30">
         <v>7</v>
       </c>
       <c r="AA30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB30">
         <v>8</v>
@@ -3331,13 +3190,13 @@
         <v>-1</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L31">
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3379,7 +3238,7 @@
         <v>6</v>
       </c>
       <c r="AA31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB31">
         <v>8</v>
@@ -3399,13 +3258,13 @@
         <v>-1</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E32">
         <v>-1</v>
       </c>
       <c r="F32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G32">
         <v>-1</v>
@@ -3420,13 +3279,13 @@
         <v>-1</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L32">
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3462,13 +3321,13 @@
         <v>-1</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z32">
         <v>-1</v>
       </c>
       <c r="AA32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB32">
         <v>-1</v>
@@ -3509,13 +3368,13 @@
         <v>-1</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L33">
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3598,13 +3457,13 @@
         <v>-1</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L34">
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3640,7 +3499,7 @@
         <v>7</v>
       </c>
       <c r="Y34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z34">
         <v>7</v>
@@ -3672,7 +3531,7 @@
         <v>5</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G35">
         <v>5</v>
@@ -3687,13 +3546,13 @@
         <v>-1</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L35">
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3729,13 +3588,13 @@
         <v>6</v>
       </c>
       <c r="Y35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z35">
         <v>5</v>
       </c>
       <c r="AA35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB35">
         <v>5</v>
@@ -3761,7 +3620,7 @@
         <v>6</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G36">
         <v>6</v>
@@ -3776,13 +3635,13 @@
         <v>-1</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L36">
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3865,13 +3724,13 @@
         <v>-1</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L37">
         <v>-1</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3907,13 +3766,13 @@
         <v>5</v>
       </c>
       <c r="Y37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z37">
         <v>7</v>
       </c>
       <c r="AA37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB37">
         <v>8</v>
@@ -3939,7 +3798,7 @@
         <v>5</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G38">
         <v>5</v>
@@ -3954,13 +3813,13 @@
         <v>-1</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L38">
         <v>-1</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -4043,13 +3902,13 @@
         <v>-1</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L39">
         <v>-1</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -4085,13 +3944,13 @@
         <v>8</v>
       </c>
       <c r="Y39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z39">
         <v>8</v>
       </c>
       <c r="AA39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB39">
         <v>9</v>
@@ -4254,13 +4113,13 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -4322,13 +4181,13 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -4375,7 +4234,7 @@
         <v>120</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>105.7</v>
@@ -4390,13 +4249,13 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -4443,7 +4302,7 @@
         <v>120</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>105.7</v>
@@ -4458,13 +4317,13 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -4526,13 +4385,13 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -4594,13 +4453,13 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -4662,13 +4521,13 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -4730,13 +4589,13 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -4783,7 +4642,7 @@
         <v>120</v>
       </c>
       <c r="F12">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="G12">
         <v>105.7</v>
@@ -4798,13 +4657,13 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -4851,7 +4710,7 @@
         <v>100</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G13">
         <v>105.7</v>
@@ -4866,13 +4725,13 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -4934,13 +4793,13 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -4984,7 +4843,7 @@
         <v>106.7</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -5034,13 +4893,13 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -5102,13 +4961,13 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -5170,13 +5029,13 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -5238,13 +5097,13 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -5288,7 +5147,7 @@
         <v>106.7</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -5338,13 +5197,13 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -5406,13 +5265,13 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -5459,7 +5318,7 @@
         <v>120</v>
       </c>
       <c r="F23">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G23">
         <v>105.7</v>
@@ -5474,13 +5333,13 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -5542,13 +5401,13 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -5610,13 +5469,13 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L25">
         <v>0</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -5678,13 +5537,13 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L26">
         <v>0</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -5746,13 +5605,13 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -5882,13 +5741,13 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29">
         <v>0</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -5950,13 +5809,13 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="L30">
         <v>0</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -6018,13 +5877,13 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="L31">
         <v>0</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -6065,13 +5924,13 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32">
         <v>0</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -6086,13 +5945,13 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L32">
         <v>0</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N32">
         <v>0</v>
@@ -6154,13 +6013,13 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="L33">
         <v>0</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -6222,13 +6081,13 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L34">
         <v>0</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N34">
         <v>0</v>
@@ -6275,7 +6134,7 @@
         <v>93.3</v>
       </c>
       <c r="F35">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="G35">
         <v>105.7</v>
@@ -6290,13 +6149,13 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L35">
         <v>0</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N35">
         <v>0</v>
@@ -6343,7 +6202,7 @@
         <v>93.3</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G36">
         <v>105.7</v>
@@ -6358,13 +6217,13 @@
         <v>0</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L36">
         <v>0</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N36">
         <v>0</v>
@@ -6411,7 +6270,7 @@
         <v>120</v>
       </c>
       <c r="F37">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="G37">
         <v>105.7</v>
@@ -6426,13 +6285,13 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L37">
         <v>0</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N37">
         <v>0</v>
@@ -6479,7 +6338,7 @@
         <v>66.7</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G38">
         <v>105.7</v>
@@ -6494,13 +6353,13 @@
         <v>0</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="L38">
         <v>0</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N38">
         <v>0</v>
@@ -6562,13 +6421,13 @@
         <v>0</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L39">
         <v>0</v>
       </c>
       <c r="M39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N39">
         <v>0</v>
@@ -6614,6 +6473,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -6659,48 +6520,48 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E2">
-        <v>13</v>
-      </c>
-      <c r="F2">
-        <v>58.82</v>
-      </c>
-      <c r="G2">
-        <v>38.24</v>
+        <v>23</v>
+      </c>
+      <c r="F2" s="2">
+        <v>32.4</v>
+      </c>
+      <c r="G2" s="2">
+        <v>67.59999999999999</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>2.94</v>
+        <v>0</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
       </c>
       <c r="C3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3">
-        <v>11</v>
-      </c>
-      <c r="F3">
-        <v>66.67</v>
-      </c>
-      <c r="G3">
-        <v>30.56</v>
+        <v>8</v>
+      </c>
+      <c r="F3" s="2">
+        <v>73.5</v>
+      </c>
+      <c r="G3" s="2">
+        <v>23.5</v>
       </c>
       <c r="H3">
         <v>6.8</v>
@@ -6708,13 +6569,13 @@
       <c r="I3">
         <v>1</v>
       </c>
-      <c r="J3">
-        <v>2.78</v>
+      <c r="J3" s="2">
+        <v>2.9</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
@@ -6723,94 +6584,94 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>8</v>
-      </c>
-      <c r="F4">
-        <v>73.53</v>
-      </c>
-      <c r="G4">
-        <v>23.53</v>
+        <v>7</v>
+      </c>
+      <c r="F4" s="2">
+        <v>76.5</v>
+      </c>
+      <c r="G4" s="2">
+        <v>20.6</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="I4">
         <v>1</v>
       </c>
-      <c r="J4">
-        <v>2.94</v>
+      <c r="J4" s="2">
+        <v>2.9</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
       </c>
       <c r="C5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E5">
-        <v>7</v>
-      </c>
-      <c r="F5">
-        <v>76.47</v>
-      </c>
-      <c r="G5">
-        <v>20.59</v>
+        <v>6</v>
+      </c>
+      <c r="F5" s="2">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="G5" s="2">
+        <v>16.7</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
         <v>1</v>
       </c>
-      <c r="J5">
-        <v>2.94</v>
+      <c r="J5" s="2">
+        <v>2.8</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C6">
         <v>36</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>80.56</v>
-      </c>
-      <c r="G6">
-        <v>16.67</v>
+        <v>5</v>
+      </c>
+      <c r="F6" s="2">
+        <v>83.3</v>
+      </c>
+      <c r="G6" s="2">
+        <v>13.9</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="I6">
         <v>1</v>
       </c>
-      <c r="J6">
-        <v>2.78</v>
+      <c r="J6" s="2">
+        <v>2.8</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>65</v>
@@ -6819,25 +6680,25 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7">
         <v>5</v>
       </c>
-      <c r="F7">
-        <v>83.33</v>
-      </c>
-      <c r="G7">
-        <v>13.89</v>
+      <c r="F7" s="2">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="G7" s="2">
+        <v>13.9</v>
       </c>
       <c r="H7">
         <v>7.6</v>
       </c>
       <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>2.78</v>
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -6856,11 +6717,11 @@
       <c r="E8">
         <v>3</v>
       </c>
-      <c r="F8">
-        <v>88.23999999999999</v>
-      </c>
-      <c r="G8">
-        <v>8.82</v>
+      <c r="F8" s="2">
+        <v>88.2</v>
+      </c>
+      <c r="G8" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="H8">
         <v>7.2</v>
@@ -6868,8 +6729,8 @@
       <c r="I8">
         <v>1</v>
       </c>
-      <c r="J8">
-        <v>2.94</v>
+      <c r="J8" s="2">
+        <v>2.9</v>
       </c>
     </row>
   </sheetData>
@@ -6879,7 +6740,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6923,7 +6784,7 @@
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -6940,10 +6801,10 @@
         <v>73</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -6960,10 +6821,10 @@
         <v>73</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -6980,10 +6841,10 @@
         <v>73</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -7000,50 +6861,10 @@
         <v>73</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920101</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920101</v>
-      </c>
-      <c r="B8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -7052,649 +6873,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E37"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>21330051920101</v>
-      </c>
-      <c r="B2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>21330051920071</v>
-      </c>
-      <c r="B3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>21330051920074</v>
-      </c>
-      <c r="B4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>20330051920378</v>
-      </c>
-      <c r="B5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D5" t="s">
-        <v>127</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>21330051920075</v>
-      </c>
-      <c r="B6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D6" t="s">
-        <v>128</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>21330051920108</v>
-      </c>
-      <c r="B7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" t="s">
-        <v>100</v>
-      </c>
-      <c r="D7" t="s">
-        <v>129</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>21330051920076</v>
-      </c>
-      <c r="B8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D8" t="s">
-        <v>130</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>21330051920077</v>
-      </c>
-      <c r="B9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" t="s">
-        <v>105</v>
-      </c>
-      <c r="D9" t="s">
-        <v>131</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>21330051920078</v>
-      </c>
-      <c r="B10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" t="s">
-        <v>106</v>
-      </c>
-      <c r="D10" t="s">
-        <v>132</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>21330051920079</v>
-      </c>
-      <c r="B11" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" t="s">
-        <v>107</v>
-      </c>
-      <c r="D11" t="s">
-        <v>133</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>19330051920195</v>
-      </c>
-      <c r="B12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" t="s">
-        <v>108</v>
-      </c>
-      <c r="D12" t="s">
-        <v>134</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>21330051920260</v>
-      </c>
-      <c r="B13" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13" t="s">
-        <v>109</v>
-      </c>
-      <c r="D13" t="s">
-        <v>135</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>21330051920080</v>
-      </c>
-      <c r="B14" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14" t="s">
-        <v>84</v>
-      </c>
-      <c r="D14" t="s">
-        <v>131</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>21330051920082</v>
-      </c>
-      <c r="B15" t="s">
-        <v>83</v>
-      </c>
-      <c r="C15" t="s">
-        <v>110</v>
-      </c>
-      <c r="D15" t="s">
-        <v>136</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>21330051920083</v>
-      </c>
-      <c r="B16" t="s">
-        <v>84</v>
-      </c>
-      <c r="C16" t="s">
-        <v>83</v>
-      </c>
-      <c r="D16" t="s">
-        <v>137</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>21330051920084</v>
-      </c>
-      <c r="B17" t="s">
-        <v>85</v>
-      </c>
-      <c r="C17" t="s">
-        <v>111</v>
-      </c>
-      <c r="D17" t="s">
-        <v>138</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>19330051920286</v>
-      </c>
-      <c r="B18" t="s">
-        <v>86</v>
-      </c>
-      <c r="C18" t="s">
-        <v>112</v>
-      </c>
-      <c r="D18" t="s">
-        <v>139</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>21330051920085</v>
-      </c>
-      <c r="B19" t="s">
-        <v>87</v>
-      </c>
-      <c r="C19" t="s">
-        <v>106</v>
-      </c>
-      <c r="D19" t="s">
-        <v>140</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>21330051920086</v>
-      </c>
-      <c r="B20" t="s">
-        <v>87</v>
-      </c>
-      <c r="C20" t="s">
-        <v>113</v>
-      </c>
-      <c r="D20" t="s">
-        <v>141</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>20330051920302</v>
-      </c>
-      <c r="B21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C21" t="s">
-        <v>114</v>
-      </c>
-      <c r="D21" t="s">
-        <v>142</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>21330051920089</v>
-      </c>
-      <c r="B22" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" t="s">
-        <v>114</v>
-      </c>
-      <c r="D22" t="s">
-        <v>143</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>21330051920092</v>
-      </c>
-      <c r="B23" t="s">
-        <v>89</v>
-      </c>
-      <c r="C23" t="s">
-        <v>115</v>
-      </c>
-      <c r="D23" t="s">
-        <v>144</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>21330051920093</v>
-      </c>
-      <c r="B24" t="s">
-        <v>90</v>
-      </c>
-      <c r="C24" t="s">
-        <v>93</v>
-      </c>
-      <c r="D24" t="s">
-        <v>145</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>21330051920094</v>
-      </c>
-      <c r="B25" t="s">
-        <v>91</v>
-      </c>
-      <c r="C25" t="s">
-        <v>116</v>
-      </c>
-      <c r="D25" t="s">
-        <v>146</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>21330051920096</v>
-      </c>
-      <c r="B26" t="s">
-        <v>91</v>
-      </c>
-      <c r="C26" t="s">
-        <v>117</v>
-      </c>
-      <c r="D26" t="s">
-        <v>147</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>21330051920097</v>
-      </c>
-      <c r="B27" t="s">
-        <v>92</v>
-      </c>
-      <c r="C27" t="s">
-        <v>118</v>
-      </c>
-      <c r="D27" t="s">
-        <v>148</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
-        <v>21330051920099</v>
-      </c>
-      <c r="B28" t="s">
-        <v>72</v>
-      </c>
-      <c r="C28" t="s">
-        <v>91</v>
-      </c>
-      <c r="D28" t="s">
-        <v>149</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>21330051920100</v>
-      </c>
-      <c r="B29" t="s">
-        <v>93</v>
-      </c>
-      <c r="C29" t="s">
-        <v>119</v>
-      </c>
-      <c r="D29" t="s">
-        <v>150</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30">
-        <v>21330051920383</v>
-      </c>
-      <c r="B30" t="s">
-        <v>94</v>
-      </c>
-      <c r="C30" t="s">
-        <v>95</v>
-      </c>
-      <c r="D30" t="s">
-        <v>151</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31">
-        <v>21330051920102</v>
-      </c>
-      <c r="B31" t="s">
-        <v>95</v>
-      </c>
-      <c r="C31" t="s">
-        <v>76</v>
-      </c>
-      <c r="D31" t="s">
-        <v>152</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32">
-        <v>21330051920103</v>
-      </c>
-      <c r="B32" t="s">
-        <v>96</v>
-      </c>
-      <c r="C32" t="s">
-        <v>87</v>
-      </c>
-      <c r="D32" t="s">
-        <v>153</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33">
-        <v>21330051920104</v>
-      </c>
-      <c r="B33" t="s">
-        <v>97</v>
-      </c>
-      <c r="C33" t="s">
-        <v>120</v>
-      </c>
-      <c r="D33" t="s">
-        <v>154</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34">
-        <v>21330051920105</v>
-      </c>
-      <c r="B34" t="s">
-        <v>98</v>
-      </c>
-      <c r="C34" t="s">
-        <v>121</v>
-      </c>
-      <c r="D34" t="s">
-        <v>155</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35">
-        <v>21330051920107</v>
-      </c>
-      <c r="B35" t="s">
-        <v>99</v>
-      </c>
-      <c r="C35" t="s">
-        <v>122</v>
-      </c>
-      <c r="D35" t="s">
-        <v>156</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36">
-        <v>21330051920109</v>
-      </c>
-      <c r="B36" t="s">
-        <v>100</v>
-      </c>
-      <c r="C36" t="s">
-        <v>123</v>
-      </c>
-      <c r="D36" t="s">
-        <v>157</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37">
-        <v>21330051920387</v>
-      </c>
-      <c r="B37" t="s">
-        <v>101</v>
-      </c>
-      <c r="C37" t="s">
-        <v>124</v>
-      </c>
-      <c r="D37" t="s">
-        <v>158</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7728,22 +6906,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920378</v>
+        <v>21330051920076</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7751,22 +6929,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920378</v>
+        <v>21330051920076</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7774,19 +6952,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920260</v>
+        <v>21330051920107</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
         <v>63</v>
@@ -7797,22 +6975,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920260</v>
+        <v>21330051920107</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>135</v>
+        <v>98</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7820,16 +6998,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920100</v>
+        <v>20330051920378</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>150</v>
+        <v>99</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -7843,22 +7021,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920100</v>
+        <v>21330051920075</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7866,22 +7044,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920107</v>
+        <v>21330051920080</v>
       </c>
       <c r="B8" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>122</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>156</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7889,22 +7067,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920107</v>
+        <v>21330051920083</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>156</v>
+        <v>102</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7912,22 +7090,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920076</v>
+        <v>21330051920084</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7935,16 +7113,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920080</v>
+        <v>21330051920085</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -7958,16 +7136,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920084</v>
+        <v>21330051920086</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -7981,16 +7159,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920086</v>
+        <v>21330051920092</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -8004,22 +7182,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920302</v>
+        <v>21330051920097</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -8027,16 +7205,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920092</v>
+        <v>21330051920100</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
@@ -8050,16 +7228,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920097</v>
+        <v>21330051920383</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="D16" t="s">
-        <v>148</v>
+        <v>109</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
@@ -8073,16 +7251,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920383</v>
+        <v>21330051920102</v>
       </c>
       <c r="B17" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="D17" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>

--- a/grupos/4ALCV - Estadisticos 20222.xlsx
+++ b/grupos/4ALCV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="108">
   <si>
     <t>Materia</t>
   </si>
@@ -242,18 +242,24 @@
     <t>CITLALI ESPERANZA</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>TENTZOHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -263,25 +269,19 @@
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>OLIVARES</t>
   </si>
   <si>
     <t>PELLICO</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
     <t>RUGERIO</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>LEÓN</t>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>MORENO</t>
   </si>
   <si>
     <t>MENDEZ</t>
@@ -299,30 +299,30 @@
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
     <t>HIPOLITO</t>
   </si>
   <si>
     <t>TEQUIHUATLE</t>
   </si>
   <si>
-    <t>MORENO</t>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>ALONDRA YURIDIA</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>REYLI</t>
+  </si>
+  <si>
+    <t>EVELYN JOHANA</t>
   </si>
   <si>
     <t>YARED</t>
   </si>
   <si>
-    <t>RUBI</t>
-  </si>
-  <si>
-    <t>REYLI</t>
-  </si>
-  <si>
-    <t>EVELYN JOHANA</t>
-  </si>
-  <si>
     <t>MARIA FERNANDA</t>
   </si>
   <si>
@@ -335,22 +335,13 @@
     <t>DIANA IVONNE</t>
   </si>
   <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
     <t>JOSE JULIAN</t>
   </si>
   <si>
     <t>JAZMIN</t>
   </si>
   <si>
-    <t>ALONDRA YURIDIA</t>
-  </si>
-  <si>
     <t>KIMBERLY</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
   </si>
 </sst>
 </file>
@@ -877,10 +868,10 @@
         <v>7</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
         <v>5</v>
@@ -966,10 +957,10 @@
         <v>9</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
         <v>7</v>
@@ -1011,7 +1002,7 @@
         <v>9</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y5">
         <v>7</v>
@@ -1055,10 +1046,10 @@
         <v>9</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
         <v>6</v>
@@ -1144,10 +1135,10 @@
         <v>5</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K7">
         <v>6</v>
@@ -1189,7 +1180,7 @@
         <v>7</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y7">
         <v>5</v>
@@ -1233,10 +1224,10 @@
         <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
         <v>6</v>
@@ -1278,7 +1269,7 @@
         <v>7</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y8">
         <v>6</v>
@@ -1322,10 +1313,10 @@
         <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
         <v>5</v>
@@ -1364,10 +1355,10 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -1411,10 +1402,10 @@
         <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
         <v>5</v>
@@ -1453,7 +1444,7 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>9</v>
@@ -1500,10 +1491,10 @@
         <v>7</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
         <v>5</v>
@@ -1542,7 +1533,7 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>7</v>
@@ -1589,10 +1580,10 @@
         <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
         <v>5</v>
@@ -1678,10 +1669,10 @@
         <v>5</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
         <v>5</v>
@@ -1767,10 +1758,10 @@
         <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
         <v>7</v>
@@ -1809,7 +1800,7 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>9</v>
@@ -1897,10 +1888,10 @@
         <v>6</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
         <v>5</v>
@@ -1986,10 +1977,10 @@
         <v>7</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
         <v>5</v>
@@ -2031,7 +2022,7 @@
         <v>8</v>
       </c>
       <c r="X17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y17">
         <v>5</v>
@@ -2075,10 +2066,10 @@
         <v>9</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
         <v>5</v>
@@ -2164,10 +2155,10 @@
         <v>9</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
         <v>6</v>
@@ -2294,10 +2285,10 @@
         <v>9</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
         <v>5</v>
@@ -2336,7 +2327,7 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2383,10 +2374,10 @@
         <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
         <v>5</v>
@@ -2425,10 +2416,10 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2472,10 +2463,10 @@
         <v>7</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
         <v>6</v>
@@ -2561,10 +2552,10 @@
         <v>9</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K24">
         <v>6</v>
@@ -2650,10 +2641,10 @@
         <v>8</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K25">
         <v>5</v>
@@ -2692,10 +2683,10 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y25">
         <v>5</v>
@@ -2739,10 +2730,10 @@
         <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
         <v>6</v>
@@ -2828,10 +2819,10 @@
         <v>7</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K27">
         <v>5</v>
@@ -2917,10 +2908,10 @@
         <v>5</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
         <v>5</v>
@@ -3006,10 +2997,10 @@
         <v>9</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K29">
         <v>6</v>
@@ -3095,10 +3086,10 @@
         <v>8</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
         <v>5</v>
@@ -3184,10 +3175,10 @@
         <v>8</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K31">
         <v>5</v>
@@ -3226,10 +3217,10 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y31">
         <v>5</v>
@@ -3252,10 +3243,10 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D32">
         <v>6</v>
@@ -3273,10 +3264,10 @@
         <v>-1</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K32">
         <v>5</v>
@@ -3315,10 +3306,10 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y32">
         <v>5</v>
@@ -3362,10 +3353,10 @@
         <v>9</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K33">
         <v>5</v>
@@ -3404,7 +3395,7 @@
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X33">
         <v>6</v>
@@ -3451,10 +3442,10 @@
         <v>8</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K34">
         <v>5</v>
@@ -3493,10 +3484,10 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y34">
         <v>5</v>
@@ -3540,10 +3531,10 @@
         <v>5</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K35">
         <v>5</v>
@@ -3629,10 +3620,10 @@
         <v>6</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K36">
         <v>5</v>
@@ -3671,7 +3662,7 @@
         <v>-1</v>
       </c>
       <c r="W36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X36">
         <v>5</v>
@@ -3718,10 +3709,10 @@
         <v>8</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K37">
         <v>5</v>
@@ -3760,7 +3751,7 @@
         <v>-1</v>
       </c>
       <c r="W37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X37">
         <v>5</v>
@@ -3807,10 +3798,10 @@
         <v>5</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K38">
         <v>5</v>
@@ -3896,10 +3887,10 @@
         <v>8</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K39">
         <v>5</v>
@@ -3941,7 +3932,7 @@
         <v>7</v>
       </c>
       <c r="X39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y39">
         <v>7</v>
@@ -4107,10 +4098,10 @@
         <v>106.7</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K4">
         <v>85</v>
@@ -4175,10 +4166,10 @@
         <v>106.7</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K5">
         <v>100</v>
@@ -4243,10 +4234,10 @@
         <v>106.7</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K6">
         <v>90</v>
@@ -4311,10 +4302,10 @@
         <v>106.7</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K7">
         <v>95</v>
@@ -4379,10 +4370,10 @@
         <v>106.7</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K8">
         <v>95</v>
@@ -4447,10 +4438,10 @@
         <v>106.7</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K9">
         <v>100</v>
@@ -4515,10 +4506,10 @@
         <v>106.7</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K10">
         <v>100</v>
@@ -4583,10 +4574,10 @@
         <v>106.7</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K11">
         <v>90</v>
@@ -4651,10 +4642,10 @@
         <v>106.7</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K12">
         <v>70</v>
@@ -4719,10 +4710,10 @@
         <v>106.7</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K13">
         <v>90</v>
@@ -4787,10 +4778,10 @@
         <v>106.7</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K14">
         <v>100</v>
@@ -4887,10 +4878,10 @@
         <v>106.7</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K16">
         <v>100</v>
@@ -4955,10 +4946,10 @@
         <v>106.7</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K17">
         <v>95</v>
@@ -5023,10 +5014,10 @@
         <v>106.7</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K18">
         <v>85</v>
@@ -5091,10 +5082,10 @@
         <v>106.7</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K19">
         <v>100</v>
@@ -5191,10 +5182,10 @@
         <v>106.7</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K21">
         <v>95</v>
@@ -5259,10 +5250,10 @@
         <v>106.7</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K22">
         <v>70</v>
@@ -5327,10 +5318,10 @@
         <v>106.7</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K23">
         <v>95</v>
@@ -5395,10 +5386,10 @@
         <v>106.7</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K24">
         <v>95</v>
@@ -5463,10 +5454,10 @@
         <v>106.7</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K25">
         <v>100</v>
@@ -5531,10 +5522,10 @@
         <v>106.7</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K26">
         <v>100</v>
@@ -5599,10 +5590,10 @@
         <v>106.7</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K27">
         <v>100</v>
@@ -5735,10 +5726,10 @@
         <v>106.7</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K29">
         <v>100</v>
@@ -5803,10 +5794,10 @@
         <v>100</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K30">
         <v>95</v>
@@ -5871,10 +5862,10 @@
         <v>106.7</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K31">
         <v>75</v>
@@ -5918,10 +5909,10 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D32">
         <v>100</v>
@@ -5939,10 +5930,10 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K32">
         <v>100</v>
@@ -6007,10 +5998,10 @@
         <v>106.7</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K33">
         <v>95</v>
@@ -6075,10 +6066,10 @@
         <v>106.7</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K34">
         <v>90</v>
@@ -6143,10 +6134,10 @@
         <v>106.7</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K35">
         <v>80</v>
@@ -6211,10 +6202,10 @@
         <v>106.7</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K36">
         <v>80</v>
@@ -6279,10 +6270,10 @@
         <v>106.7</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K37">
         <v>70</v>
@@ -6347,10 +6338,10 @@
         <v>93.3</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K38">
         <v>85</v>
@@ -6415,10 +6406,10 @@
         <v>106.7</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K39">
         <v>100</v>
@@ -6552,25 +6543,25 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F3" s="2">
-        <v>73.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>23.5</v>
+        <v>32.4</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2">
-        <v>2.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -6584,25 +6575,25 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E4">
         <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>76.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G4" s="2">
         <v>20.6</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2">
-        <v>2.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -6740,7 +6731,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6781,10 +6772,10 @@
         <v>73</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -6801,10 +6792,10 @@
         <v>73</v>
       </c>
       <c r="E3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -6821,49 +6812,9 @@
         <v>73</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920101</v>
-      </c>
-      <c r="B5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920101</v>
-      </c>
-      <c r="B6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" t="s">
-        <v>73</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" t="s">
         <v>64</v>
       </c>
     </row>
@@ -6906,22 +6857,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920076</v>
+        <v>21330051920086</v>
       </c>
       <c r="B2" t="s">
         <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6929,16 +6880,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920076</v>
+        <v>21330051920086</v>
       </c>
       <c r="B3" t="s">
         <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -6952,7 +6903,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920107</v>
+        <v>21330051920100</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
@@ -6961,13 +6912,13 @@
         <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6975,7 +6926,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920107</v>
+        <v>21330051920100</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
@@ -6984,7 +6935,7 @@
         <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -6998,22 +6949,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920378</v>
+        <v>21330051920102</v>
       </c>
       <c r="B6" t="s">
         <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7021,16 +6972,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920075</v>
+        <v>21330051920102</v>
       </c>
       <c r="B7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" t="s">
         <v>77</v>
       </c>
-      <c r="C7" t="s">
-        <v>89</v>
-      </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -7044,16 +6995,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920080</v>
+        <v>20330051920378</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -7067,16 +7018,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920083</v>
+        <v>21330051920075</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -7090,16 +7041,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920084</v>
+        <v>21330051920076</v>
       </c>
       <c r="B10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" t="s">
         <v>80</v>
       </c>
-      <c r="C10" t="s">
-        <v>91</v>
-      </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -7113,16 +7064,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920085</v>
+        <v>21330051920080</v>
       </c>
       <c r="B11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" t="s">
         <v>81</v>
       </c>
-      <c r="C11" t="s">
-        <v>92</v>
-      </c>
       <c r="D11" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -7136,16 +7087,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920086</v>
+        <v>21330051920083</v>
       </c>
       <c r="B12" t="s">
         <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -7159,16 +7110,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920092</v>
+        <v>21330051920084</v>
       </c>
       <c r="B13" t="s">
         <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -7182,16 +7133,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920097</v>
+        <v>21330051920085</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D14" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -7205,16 +7156,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920100</v>
+        <v>21330051920092</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D15" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
@@ -7228,16 +7179,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920383</v>
+        <v>21330051920097</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="D16" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
@@ -7251,16 +7202,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920102</v>
+        <v>21330051920383</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s">
         <v>76</v>
       </c>
       <c r="D17" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>

--- a/grupos/4ALCV - Estadisticos 20222.xlsx
+++ b/grupos/4ALCV - Estadisticos 20222.xlsx
@@ -212,13 +212,13 @@
     <t>Gomez Lopez Javier</t>
   </si>
   <si>
+    <t>Mateos Sanchez Jorge</t>
+  </si>
+  <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>Rivera Serra Alma Lilian</t>
-  </si>
-  <si>
-    <t>Mateos Sanchez Jorge</t>
-  </si>
-  <si>
-    <t>González Nuñez Veronica</t>
   </si>
   <si>
     <t>NC</t>
@@ -883,10 +883,10 @@
         <v>8</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -928,7 +928,7 @@
         <v>8</v>
       </c>
       <c r="AC4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -972,10 +972,10 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1061,10 +1061,10 @@
         <v>7</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1103,10 +1103,10 @@
         <v>6</v>
       </c>
       <c r="AB6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1150,10 +1150,10 @@
         <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1239,10 +1239,10 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1281,10 +1281,10 @@
         <v>9</v>
       </c>
       <c r="AB8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC8">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1328,10 +1328,10 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1373,7 +1373,7 @@
         <v>10</v>
       </c>
       <c r="AC9">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1417,10 +1417,10 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1462,7 +1462,7 @@
         <v>10</v>
       </c>
       <c r="AC10">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1506,10 +1506,10 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1551,7 +1551,7 @@
         <v>9</v>
       </c>
       <c r="AC11">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1595,10 +1595,10 @@
         <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1684,10 +1684,10 @@
         <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1726,10 +1726,10 @@
         <v>5</v>
       </c>
       <c r="AB13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC13">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1773,10 +1773,10 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1818,7 +1818,7 @@
         <v>10</v>
       </c>
       <c r="AC14">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1838,10 +1838,10 @@
         <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>-1</v>
@@ -1859,7 +1859,7 @@
         <v>10</v>
       </c>
       <c r="AC15">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1903,10 +1903,10 @@
         <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1948,7 +1948,7 @@
         <v>7</v>
       </c>
       <c r="AC16">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -1992,10 +1992,10 @@
         <v>6</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2037,7 +2037,7 @@
         <v>7</v>
       </c>
       <c r="AC17">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2081,10 +2081,10 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2123,7 +2123,7 @@
         <v>9</v>
       </c>
       <c r="AB18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC18">
         <v>9</v>
@@ -2170,10 +2170,10 @@
         <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2212,7 +2212,7 @@
         <v>9</v>
       </c>
       <c r="AB19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC19">
         <v>9</v>
@@ -2235,10 +2235,10 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>-1</v>
@@ -2253,7 +2253,7 @@
         <v>10</v>
       </c>
       <c r="AB20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC20">
         <v>8</v>
@@ -2300,10 +2300,10 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2342,7 +2342,7 @@
         <v>9</v>
       </c>
       <c r="AB21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC21">
         <v>9</v>
@@ -2389,10 +2389,10 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2431,10 +2431,10 @@
         <v>7</v>
       </c>
       <c r="AB22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC22">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2478,10 +2478,10 @@
         <v>8</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2520,10 +2520,10 @@
         <v>7</v>
       </c>
       <c r="AB23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC23">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2567,10 +2567,10 @@
         <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2609,7 +2609,7 @@
         <v>9</v>
       </c>
       <c r="AB24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC24">
         <v>9</v>
@@ -2656,10 +2656,10 @@
         <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2745,10 +2745,10 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2790,7 +2790,7 @@
         <v>10</v>
       </c>
       <c r="AC26">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2834,10 +2834,10 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2879,7 +2879,7 @@
         <v>10</v>
       </c>
       <c r="AC27">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -2923,10 +2923,10 @@
         <v>0</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3012,10 +3012,10 @@
         <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3057,7 +3057,7 @@
         <v>10</v>
       </c>
       <c r="AC29">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3101,10 +3101,10 @@
         <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3143,10 +3143,10 @@
         <v>7</v>
       </c>
       <c r="AB30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC30">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3190,10 +3190,10 @@
         <v>7</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3232,10 +3232,10 @@
         <v>6</v>
       </c>
       <c r="AB31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC31">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3258,10 +3258,10 @@
         <v>10</v>
       </c>
       <c r="G32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I32">
         <v>6</v>
@@ -3279,10 +3279,10 @@
         <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3321,10 +3321,10 @@
         <v>10</v>
       </c>
       <c r="AB32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC32">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3368,10 +3368,10 @@
         <v>8</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3410,7 +3410,7 @@
         <v>8</v>
       </c>
       <c r="AB33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC33">
         <v>9</v>
@@ -3457,10 +3457,10 @@
         <v>6</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3499,10 +3499,10 @@
         <v>6</v>
       </c>
       <c r="AB34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC34">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -3546,10 +3546,10 @@
         <v>9</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3588,10 +3588,10 @@
         <v>7</v>
       </c>
       <c r="AB35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC35">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:29">
@@ -3635,10 +3635,10 @@
         <v>5</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3677,10 +3677,10 @@
         <v>5</v>
       </c>
       <c r="AB36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC36">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:29">
@@ -3724,10 +3724,10 @@
         <v>7</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P37">
         <v>-1</v>
@@ -3769,7 +3769,7 @@
         <v>8</v>
       </c>
       <c r="AC37">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:29">
@@ -3813,10 +3813,10 @@
         <v>0</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P38">
         <v>-1</v>
@@ -3902,10 +3902,10 @@
         <v>10</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P39">
         <v>-1</v>
@@ -3944,10 +3944,10 @@
         <v>9</v>
       </c>
       <c r="AB39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC39">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -4113,10 +4113,10 @@
         <v>100</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -4181,10 +4181,10 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -4249,10 +4249,10 @@
         <v>95</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -4317,10 +4317,10 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -4385,10 +4385,10 @@
         <v>100</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -4453,10 +4453,10 @@
         <v>100</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -4521,10 +4521,10 @@
         <v>100</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -4657,10 +4657,10 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -4725,10 +4725,10 @@
         <v>95</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -4793,10 +4793,10 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -4837,10 +4837,10 @@
         <v>95</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="T15">
         <v>0</v>
@@ -4893,10 +4893,10 @@
         <v>95</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -4961,10 +4961,10 @@
         <v>100</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -5029,10 +5029,10 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -5097,10 +5097,10 @@
         <v>100</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -5141,10 +5141,10 @@
         <v>100</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="T20">
         <v>0</v>
@@ -5197,10 +5197,10 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -5265,10 +5265,10 @@
         <v>100</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -5333,10 +5333,10 @@
         <v>100</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -5401,10 +5401,10 @@
         <v>100</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P24">
         <v>0</v>
@@ -5469,10 +5469,10 @@
         <v>95</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -5537,10 +5537,10 @@
         <v>100</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -5605,10 +5605,10 @@
         <v>100</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -5673,10 +5673,10 @@
         <v>0</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>57.1</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -5741,10 +5741,10 @@
         <v>100</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P29">
         <v>0</v>
@@ -5809,10 +5809,10 @@
         <v>100</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P30">
         <v>0</v>
@@ -5877,10 +5877,10 @@
         <v>100</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P31">
         <v>0</v>
@@ -5924,10 +5924,10 @@
         <v>100</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="I32">
         <v>110</v>
@@ -5945,10 +5945,10 @@
         <v>95</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P32">
         <v>0</v>
@@ -6013,10 +6013,10 @@
         <v>100</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P33">
         <v>0</v>
@@ -6081,10 +6081,10 @@
         <v>100</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P34">
         <v>0</v>
@@ -6149,10 +6149,10 @@
         <v>100</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P35">
         <v>0</v>
@@ -6217,10 +6217,10 @@
         <v>90</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P36">
         <v>0</v>
@@ -6285,10 +6285,10 @@
         <v>95</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P37">
         <v>0</v>
@@ -6353,10 +6353,10 @@
         <v>90</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P38">
         <v>0</v>
@@ -6421,10 +6421,10 @@
         <v>100</v>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="P39">
         <v>0</v>
@@ -6598,7 +6598,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
@@ -6607,83 +6607,83 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5" s="2">
-        <v>80.59999999999999</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>16.7</v>
+        <v>13.9</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2">
-        <v>2.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D6">
         <v>30</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>83.3</v>
+        <v>88.2</v>
       </c>
       <c r="G6" s="2">
-        <v>13.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="I6">
         <v>1</v>
       </c>
       <c r="J6" s="2">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C7">
         <v>36</v>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F7" s="2">
-        <v>86.09999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G7" s="2">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6694,34 +6694,34 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>66</v>
       </c>
       <c r="C8">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D8">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8" s="2">
-        <v>88.2</v>
+        <v>91.7</v>
       </c>
       <c r="G8" s="2">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H8">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="2">
-        <v>2.9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6731,7 +6731,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6775,47 +6775,7 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920101</v>
-      </c>
-      <c r="B3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920101</v>
-      </c>
-      <c r="B4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -6825,7 +6785,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6949,22 +6909,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920102</v>
+        <v>21330051920101</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6972,45 +6932,45 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920102</v>
+        <v>21330051920101</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920378</v>
+        <v>21330051920102</v>
       </c>
       <c r="B8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" t="s">
         <v>77</v>
       </c>
-      <c r="C8" t="s">
-        <v>88</v>
-      </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7018,16 +6978,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920075</v>
+        <v>21330051920102</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -7041,16 +7001,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920076</v>
+        <v>20330051920378</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -7064,16 +7024,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920080</v>
+        <v>21330051920075</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -7087,16 +7047,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920083</v>
+        <v>21330051920076</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -7110,16 +7070,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920084</v>
+        <v>21330051920080</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -7133,16 +7093,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920085</v>
+        <v>21330051920083</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -7156,16 +7116,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920092</v>
+        <v>21330051920084</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D15" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
@@ -7179,16 +7139,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920097</v>
+        <v>21330051920085</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
@@ -7202,16 +7162,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920383</v>
+        <v>21330051920092</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="D17" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
@@ -7220,6 +7180,52 @@
         <v>61</v>
       </c>
       <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>21330051920097</v>
+      </c>
+      <c r="B18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" t="s">
+        <v>61</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>21330051920383</v>
+      </c>
+      <c r="B19" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19" t="s">
+        <v>76</v>
+      </c>
+      <c r="D19" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4ALCV - Estadisticos 20222.xlsx
+++ b/grupos/4ALCV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="110">
   <si>
     <t>Materia</t>
   </si>
@@ -215,12 +215,12 @@
     <t>Mateos Sanchez Jorge</t>
   </si>
   <si>
+    <t>Rivera Serra Alma Lilian</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>Rivera Serra Alma Lilian</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -251,6 +251,9 @@
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
@@ -312,6 +315,9 @@
   </si>
   <si>
     <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>ALMA KAREN</t>
   </si>
   <si>
     <t>REYLI</t>
@@ -877,7 +883,7 @@
         <v>5</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
         <v>8</v>
@@ -919,7 +925,7 @@
         <v>5</v>
       </c>
       <c r="Z4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA4">
         <v>7</v>
@@ -966,7 +972,7 @@
         <v>7</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M5">
         <v>10</v>
@@ -1055,7 +1061,7 @@
         <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M6">
         <v>7</v>
@@ -1097,7 +1103,7 @@
         <v>5</v>
       </c>
       <c r="Z6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA6">
         <v>6</v>
@@ -1144,7 +1150,7 @@
         <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>8</v>
@@ -1186,7 +1192,7 @@
         <v>5</v>
       </c>
       <c r="Z7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA7">
         <v>7</v>
@@ -1233,7 +1239,7 @@
         <v>6</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
         <v>10</v>
@@ -1275,7 +1281,7 @@
         <v>6</v>
       </c>
       <c r="Z8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA8">
         <v>9</v>
@@ -1322,7 +1328,7 @@
         <v>5</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
         <v>8</v>
@@ -1411,7 +1417,7 @@
         <v>5</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
         <v>10</v>
@@ -1500,7 +1506,7 @@
         <v>5</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
         <v>10</v>
@@ -1542,7 +1548,7 @@
         <v>5</v>
       </c>
       <c r="Z11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA11">
         <v>8</v>
@@ -1589,7 +1595,7 @@
         <v>5</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
         <v>6</v>
@@ -1678,7 +1684,7 @@
         <v>5</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M13">
         <v>5</v>
@@ -1720,7 +1726,7 @@
         <v>5</v>
       </c>
       <c r="Z13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA13">
         <v>5</v>
@@ -1767,7 +1773,7 @@
         <v>7</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
         <v>10</v>
@@ -1809,7 +1815,7 @@
         <v>7</v>
       </c>
       <c r="Z14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA14">
         <v>9</v>
@@ -1897,7 +1903,7 @@
         <v>5</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M16">
         <v>6</v>
@@ -1939,7 +1945,7 @@
         <v>5</v>
       </c>
       <c r="Z16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA16">
         <v>7</v>
@@ -1986,7 +1992,7 @@
         <v>5</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M17">
         <v>6</v>
@@ -2075,7 +2081,7 @@
         <v>5</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
         <v>10</v>
@@ -2164,7 +2170,7 @@
         <v>6</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
         <v>10</v>
@@ -2294,7 +2300,7 @@
         <v>5</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
         <v>9</v>
@@ -2383,7 +2389,7 @@
         <v>5</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
         <v>6</v>
@@ -2472,7 +2478,7 @@
         <v>6</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
         <v>8</v>
@@ -2561,7 +2567,7 @@
         <v>6</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
         <v>9</v>
@@ -2650,7 +2656,7 @@
         <v>5</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M25">
         <v>8</v>
@@ -2739,7 +2745,7 @@
         <v>6</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
         <v>10</v>
@@ -2828,7 +2834,7 @@
         <v>5</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
         <v>10</v>
@@ -2870,7 +2876,7 @@
         <v>5</v>
       </c>
       <c r="Z27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA27">
         <v>9</v>
@@ -2917,7 +2923,7 @@
         <v>5</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M28">
         <v>0</v>
@@ -3006,7 +3012,7 @@
         <v>6</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
         <v>10</v>
@@ -3095,7 +3101,7 @@
         <v>5</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M30">
         <v>8</v>
@@ -3137,7 +3143,7 @@
         <v>7</v>
       </c>
       <c r="Z30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA30">
         <v>7</v>
@@ -3184,7 +3190,7 @@
         <v>5</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M31">
         <v>7</v>
@@ -3362,7 +3368,7 @@
         <v>5</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M33">
         <v>8</v>
@@ -3404,7 +3410,7 @@
         <v>5</v>
       </c>
       <c r="Z33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA33">
         <v>8</v>
@@ -3451,7 +3457,7 @@
         <v>5</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M34">
         <v>6</v>
@@ -3540,7 +3546,7 @@
         <v>5</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M35">
         <v>9</v>
@@ -3582,7 +3588,7 @@
         <v>5</v>
       </c>
       <c r="Z35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA35">
         <v>7</v>
@@ -3629,7 +3635,7 @@
         <v>5</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M36">
         <v>5</v>
@@ -3718,7 +3724,7 @@
         <v>5</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M37">
         <v>7</v>
@@ -3807,7 +3813,7 @@
         <v>5</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M38">
         <v>0</v>
@@ -3849,7 +3855,7 @@
         <v>5</v>
       </c>
       <c r="Z38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA38">
         <v>5</v>
@@ -3896,7 +3902,7 @@
         <v>5</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M39">
         <v>10</v>
@@ -4107,7 +4113,7 @@
         <v>85</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M4">
         <v>100</v>
@@ -4175,7 +4181,7 @@
         <v>100</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M5">
         <v>100</v>
@@ -4243,7 +4249,7 @@
         <v>90</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M6">
         <v>95</v>
@@ -4311,7 +4317,7 @@
         <v>95</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M7">
         <v>100</v>
@@ -4379,7 +4385,7 @@
         <v>95</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M8">
         <v>100</v>
@@ -4447,7 +4453,7 @@
         <v>100</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="M9">
         <v>100</v>
@@ -4515,7 +4521,7 @@
         <v>100</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M10">
         <v>100</v>
@@ -4583,7 +4589,7 @@
         <v>90</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M11">
         <v>100</v>
@@ -4651,7 +4657,7 @@
         <v>70</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M12">
         <v>100</v>
@@ -4719,7 +4725,7 @@
         <v>90</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M13">
         <v>95</v>
@@ -4787,7 +4793,7 @@
         <v>100</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M14">
         <v>100</v>
@@ -4887,7 +4893,7 @@
         <v>100</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M16">
         <v>95</v>
@@ -4955,7 +4961,7 @@
         <v>95</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M17">
         <v>100</v>
@@ -5023,7 +5029,7 @@
         <v>85</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M18">
         <v>100</v>
@@ -5091,7 +5097,7 @@
         <v>100</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M19">
         <v>100</v>
@@ -5191,7 +5197,7 @@
         <v>95</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M21">
         <v>100</v>
@@ -5259,7 +5265,7 @@
         <v>70</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="M22">
         <v>100</v>
@@ -5327,7 +5333,7 @@
         <v>95</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M23">
         <v>100</v>
@@ -5395,7 +5401,7 @@
         <v>95</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M24">
         <v>100</v>
@@ -5463,7 +5469,7 @@
         <v>100</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M25">
         <v>95</v>
@@ -5531,7 +5537,7 @@
         <v>100</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M26">
         <v>100</v>
@@ -5599,7 +5605,7 @@
         <v>100</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M27">
         <v>100</v>
@@ -5735,7 +5741,7 @@
         <v>100</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M29">
         <v>100</v>
@@ -5803,7 +5809,7 @@
         <v>95</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="M30">
         <v>100</v>
@@ -5871,7 +5877,7 @@
         <v>75</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M31">
         <v>100</v>
@@ -6007,7 +6013,7 @@
         <v>95</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M33">
         <v>100</v>
@@ -6075,7 +6081,7 @@
         <v>90</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M34">
         <v>100</v>
@@ -6143,7 +6149,7 @@
         <v>80</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M35">
         <v>100</v>
@@ -6211,7 +6217,7 @@
         <v>80</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="M36">
         <v>90</v>
@@ -6279,7 +6285,7 @@
         <v>70</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M37">
         <v>95</v>
@@ -6347,7 +6353,7 @@
         <v>85</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M38">
         <v>90</v>
@@ -6415,7 +6421,7 @@
         <v>100</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M39">
         <v>100</v>
@@ -6630,60 +6636,60 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
       </c>
       <c r="C6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2">
-        <v>88.2</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>8.800000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>8.5</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2">
-        <v>2.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C7">
         <v>36</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>88.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="G7" s="2">
-        <v>11.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H7">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6694,34 +6700,34 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>66</v>
       </c>
       <c r="C8">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D8">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>91.7</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="G8" s="2">
-        <v>8.300000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="H8">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="2">
-        <v>0</v>
+        <v>2.9</v>
       </c>
     </row>
   </sheetData>
@@ -6775,7 +6781,7 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -6785,7 +6791,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6823,10 +6829,10 @@
         <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -6846,10 +6852,10 @@
         <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -6869,10 +6875,10 @@
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -6892,10 +6898,10 @@
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -6947,7 +6953,7 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -6961,10 +6967,10 @@
         <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -6984,10 +6990,10 @@
         <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -7001,22 +7007,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920378</v>
+        <v>21330051920103</v>
       </c>
       <c r="B10" t="s">
         <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7024,13 +7030,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920075</v>
+        <v>21330051920103</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
         <v>99</v>
@@ -7047,13 +7053,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920076</v>
+        <v>20330051920378</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
         <v>100</v>
@@ -7070,13 +7076,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920080</v>
+        <v>21330051920075</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
         <v>101</v>
@@ -7093,13 +7099,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920083</v>
+        <v>21330051920076</v>
       </c>
       <c r="B14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" t="s">
         <v>81</v>
-      </c>
-      <c r="C14" t="s">
-        <v>90</v>
       </c>
       <c r="D14" t="s">
         <v>102</v>
@@ -7116,13 +7122,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920084</v>
+        <v>21330051920080</v>
       </c>
       <c r="B15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" t="s">
         <v>82</v>
-      </c>
-      <c r="C15" t="s">
-        <v>91</v>
       </c>
       <c r="D15" t="s">
         <v>103</v>
@@ -7139,13 +7145,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920085</v>
+        <v>21330051920083</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D16" t="s">
         <v>104</v>
@@ -7162,13 +7168,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920092</v>
+        <v>21330051920084</v>
       </c>
       <c r="B17" t="s">
         <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D17" t="s">
         <v>105</v>
@@ -7185,13 +7191,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920097</v>
+        <v>21330051920085</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D18" t="s">
         <v>106</v>
@@ -7208,13 +7214,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920383</v>
+        <v>21330051920092</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D19" t="s">
         <v>107</v>
@@ -7226,6 +7232,52 @@
         <v>61</v>
       </c>
       <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>21330051920097</v>
+      </c>
+      <c r="B20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" t="s">
+        <v>108</v>
+      </c>
+      <c r="E20" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" t="s">
+        <v>61</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>21330051920383</v>
+      </c>
+      <c r="B21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" t="s">
+        <v>109</v>
+      </c>
+      <c r="E21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" t="s">
+        <v>61</v>
+      </c>
+      <c r="G21">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4ALCV - Estadisticos 20222.xlsx
+++ b/grupos/4ALCV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="110">
   <si>
     <t>Materia</t>
   </si>
@@ -233,118 +233,118 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
+    <t>RUGERIO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>ALONDRA YURIDIA</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>ALMA KAREN</t>
+  </si>
+  <si>
+    <t>REYLI</t>
+  </si>
+  <si>
+    <t>EVELYN JOHANA</t>
+  </si>
+  <si>
+    <t>YARED</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>REGINA ISABEL</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>DIANA IVONNE</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
     <t>CITLALI ESPERANZA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SANJUAN</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>RUGERIO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>ALONDRA YURIDIA</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>ALMA KAREN</t>
-  </si>
-  <si>
-    <t>REYLI</t>
-  </si>
-  <si>
-    <t>EVELYN JOHANA</t>
-  </si>
-  <si>
-    <t>YARED</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>REGINA ISABEL</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>DIANA IVONNE</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
   </si>
   <si>
     <t>KIMBERLY</t>
@@ -3258,7 +3258,7 @@
         <v>6</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F32">
         <v>10</v>
@@ -3279,7 +3279,7 @@
         <v>5</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M32">
         <v>10</v>
@@ -3321,7 +3321,7 @@
         <v>5</v>
       </c>
       <c r="Z32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA32">
         <v>10</v>
@@ -5924,7 +5924,7 @@
         <v>100</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F32">
         <v>100</v>
@@ -5945,7 +5945,7 @@
         <v>100</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="M32">
         <v>95</v>
@@ -6709,13 +6709,13 @@
         <v>34</v>
       </c>
       <c r="D8">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>94.09999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="G8" s="2">
         <v>2.9</v>
@@ -6724,10 +6724,10 @@
         <v>7.5</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="2">
-        <v>2.9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6737,7 +6737,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6764,26 +6764,6 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920101</v>
-      </c>
-      <c r="B2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>66</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6791,7 +6771,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6826,13 +6806,13 @@
         <v>21330051920086</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -6849,13 +6829,13 @@
         <v>21330051920086</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -6872,13 +6852,13 @@
         <v>21330051920100</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -6895,13 +6875,13 @@
         <v>21330051920100</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -6915,22 +6895,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920101</v>
+        <v>21330051920102</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6938,36 +6918,36 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920101</v>
+        <v>21330051920102</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920102</v>
+        <v>21330051920103</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
         <v>98</v>
@@ -6984,13 +6964,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920102</v>
+        <v>21330051920103</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
         <v>98</v>
@@ -7007,22 +6987,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920103</v>
+        <v>20330051920378</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="D10" t="s">
         <v>99</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7030,16 +7010,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920103</v>
+        <v>21330051920075</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -7053,16 +7033,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920378</v>
+        <v>21330051920076</v>
       </c>
       <c r="B12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" t="s">
         <v>78</v>
       </c>
-      <c r="C12" t="s">
-        <v>89</v>
-      </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -7076,16 +7056,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920075</v>
+        <v>21330051920080</v>
       </c>
       <c r="B13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" t="s">
         <v>79</v>
       </c>
-      <c r="C13" t="s">
-        <v>90</v>
-      </c>
       <c r="D13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -7099,16 +7079,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920076</v>
+        <v>21330051920083</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -7122,16 +7102,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920080</v>
+        <v>21330051920084</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
@@ -7145,16 +7125,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920083</v>
+        <v>21330051920085</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
         <v>91</v>
       </c>
       <c r="D16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
@@ -7168,16 +7148,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920084</v>
+        <v>21330051920092</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
         <v>92</v>
       </c>
       <c r="D17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
@@ -7191,16 +7171,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920085</v>
+        <v>21330051920097</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
         <v>93</v>
       </c>
       <c r="D18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E18" t="s">
         <v>7</v>
@@ -7214,16 +7194,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920092</v>
+        <v>21330051920101</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
         <v>94</v>
       </c>
       <c r="D19" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
@@ -7237,16 +7217,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920097</v>
+        <v>21330051920383</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="D20" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E20" t="s">
         <v>7</v>
@@ -7255,29 +7235,6 @@
         <v>61</v>
       </c>
       <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920383</v>
-      </c>
-      <c r="B21" t="s">
-        <v>86</v>
-      </c>
-      <c r="C21" t="s">
-        <v>76</v>
-      </c>
-      <c r="D21" t="s">
-        <v>109</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>61</v>
-      </c>
-      <c r="G21">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4ALCV - Estadisticos 20222.xlsx
+++ b/grupos/4ALCV - Estadisticos 20222.xlsx
@@ -4083,7 +4083,7 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C4">
         <v>80</v>
@@ -4092,58 +4092,58 @@
         <v>90</v>
       </c>
       <c r="E4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F4">
         <v>100</v>
       </c>
       <c r="G4">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I4">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J4">
         <v>80</v>
       </c>
       <c r="K4">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="L4">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="M4">
         <v>100</v>
       </c>
       <c r="N4">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O4">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>91.7</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -4151,7 +4151,7 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -4160,58 +4160,58 @@
         <v>95</v>
       </c>
       <c r="E5">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F5">
         <v>90</v>
       </c>
       <c r="G5">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I5">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J5">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="L5">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M5">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N5">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O5">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -4219,7 +4219,7 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C6">
         <v>80</v>
@@ -4228,58 +4228,58 @@
         <v>45</v>
       </c>
       <c r="E6">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F6">
         <v>100</v>
       </c>
       <c r="G6">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I6">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J6">
         <v>80</v>
       </c>
       <c r="K6">
-        <v>90</v>
+        <v>67.5</v>
       </c>
       <c r="L6">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M6">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N6">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O6">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>67.5</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -4287,7 +4287,7 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C7">
         <v>75</v>
@@ -4296,58 +4296,58 @@
         <v>55</v>
       </c>
       <c r="E7">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F7">
         <v>100</v>
       </c>
       <c r="G7">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I7">
-        <v>110</v>
+        <v>97.8</v>
       </c>
       <c r="J7">
-        <v>80</v>
+        <v>77.5</v>
       </c>
       <c r="K7">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="L7">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M7">
         <v>100</v>
       </c>
       <c r="N7">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O7">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>97.8</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -4355,7 +4355,7 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C8">
         <v>90</v>
@@ -4364,58 +4364,58 @@
         <v>90</v>
       </c>
       <c r="E8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F8">
         <v>100</v>
       </c>
       <c r="G8">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H8">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I8">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J8">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K8">
+        <v>92.5</v>
+      </c>
+      <c r="L8">
+        <v>100</v>
+      </c>
+      <c r="M8">
+        <v>100</v>
+      </c>
+      <c r="N8">
+        <v>100</v>
+      </c>
+      <c r="O8">
+        <v>100</v>
+      </c>
+      <c r="P8">
+        <v>100</v>
+      </c>
+      <c r="Q8">
         <v>95</v>
       </c>
-      <c r="L8">
-        <v>120</v>
-      </c>
-      <c r="M8">
-        <v>100</v>
-      </c>
-      <c r="N8">
-        <v>105.7</v>
-      </c>
-      <c r="O8">
-        <v>106.7</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
       <c r="R8">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -4423,7 +4423,7 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -4432,58 +4432,58 @@
         <v>100</v>
       </c>
       <c r="E9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F9">
         <v>100</v>
       </c>
       <c r="G9">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H9">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I9">
-        <v>110</v>
+        <v>97.8</v>
       </c>
       <c r="J9">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K9">
         <v>100</v>
       </c>
       <c r="L9">
-        <v>93.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="M9">
         <v>100</v>
       </c>
       <c r="N9">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O9">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>97.8</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -4491,7 +4491,7 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C10">
         <v>100</v>
@@ -4500,19 +4500,19 @@
         <v>100</v>
       </c>
       <c r="E10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F10">
         <v>100</v>
       </c>
       <c r="G10">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H10">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I10">
-        <v>110</v>
+        <v>97.8</v>
       </c>
       <c r="J10">
         <v>100</v>
@@ -4521,37 +4521,37 @@
         <v>100</v>
       </c>
       <c r="L10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M10">
         <v>100</v>
       </c>
       <c r="N10">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O10">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>97.8</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -4559,7 +4559,7 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C11">
         <v>90</v>
@@ -4568,58 +4568,58 @@
         <v>100</v>
       </c>
       <c r="E11">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="F11">
         <v>100</v>
       </c>
       <c r="G11">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H11">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I11">
-        <v>110</v>
+        <v>97.8</v>
       </c>
       <c r="J11">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K11">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="L11">
-        <v>120</v>
+        <v>91.7</v>
       </c>
       <c r="M11">
         <v>100</v>
       </c>
       <c r="N11">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O11">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>97.8</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>91.7</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -4627,7 +4627,7 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C12">
         <v>80</v>
@@ -4636,58 +4636,58 @@
         <v>85</v>
       </c>
       <c r="E12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F12">
         <v>100</v>
       </c>
       <c r="G12">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H12">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I12">
-        <v>105</v>
+        <v>95.7</v>
       </c>
       <c r="J12">
         <v>80</v>
       </c>
       <c r="K12">
-        <v>70</v>
+        <v>77.5</v>
       </c>
       <c r="L12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M12">
         <v>100</v>
       </c>
       <c r="N12">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O12">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>95.7</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -4695,7 +4695,7 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -4704,58 +4704,58 @@
         <v>90</v>
       </c>
       <c r="E13">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="F13">
         <v>100</v>
       </c>
       <c r="G13">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H13">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I13">
-        <v>105</v>
+        <v>95.7</v>
       </c>
       <c r="J13">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K13">
         <v>90</v>
       </c>
       <c r="L13">
-        <v>106.7</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="M13">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N13">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O13">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>95.7</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -4763,7 +4763,7 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C14">
         <v>100</v>
@@ -4772,58 +4772,58 @@
         <v>100</v>
       </c>
       <c r="E14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F14">
         <v>100</v>
       </c>
       <c r="G14">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H14">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I14">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J14">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K14">
         <v>100</v>
       </c>
       <c r="L14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M14">
         <v>100</v>
       </c>
       <c r="N14">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O14">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -4834,28 +4834,28 @@
         <v>90</v>
       </c>
       <c r="G15">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H15">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M15">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="N15">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O15">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -4863,7 +4863,7 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C16">
         <v>80</v>
@@ -4872,58 +4872,58 @@
         <v>85</v>
       </c>
       <c r="E16">
-        <v>93.3</v>
+        <v>77.8</v>
       </c>
       <c r="F16">
         <v>90</v>
       </c>
       <c r="G16">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H16">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I16">
-        <v>105</v>
+        <v>95.7</v>
       </c>
       <c r="J16">
         <v>80</v>
       </c>
       <c r="K16">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="L16">
-        <v>120</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="M16">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="N16">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O16">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>95.7</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -4931,7 +4931,7 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C17">
         <v>80</v>
@@ -4940,58 +4940,58 @@
         <v>85</v>
       </c>
       <c r="E17">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F17">
         <v>100</v>
       </c>
       <c r="G17">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H17">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I17">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J17">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K17">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="L17">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M17">
         <v>100</v>
       </c>
       <c r="N17">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O17">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -4999,7 +4999,7 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C18">
         <v>90</v>
@@ -5008,58 +5008,58 @@
         <v>95</v>
       </c>
       <c r="E18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F18">
         <v>90</v>
       </c>
       <c r="G18">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H18">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I18">
-        <v>110</v>
+        <v>97.8</v>
       </c>
       <c r="J18">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K18">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="L18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M18">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N18">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O18">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>97.8</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -5067,7 +5067,7 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -5076,19 +5076,19 @@
         <v>100</v>
       </c>
       <c r="E19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F19">
         <v>100</v>
       </c>
       <c r="G19">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H19">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I19">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J19">
         <v>100</v>
@@ -5097,37 +5097,37 @@
         <v>100</v>
       </c>
       <c r="L19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M19">
         <v>100</v>
       </c>
       <c r="N19">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O19">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -5138,28 +5138,28 @@
         <v>95</v>
       </c>
       <c r="G20">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H20">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M20">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N20">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O20">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -5167,7 +5167,7 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C21">
         <v>80</v>
@@ -5176,58 +5176,58 @@
         <v>85</v>
       </c>
       <c r="E21">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F21">
         <v>100</v>
       </c>
       <c r="G21">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H21">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I21">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J21">
         <v>80</v>
       </c>
       <c r="K21">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="L21">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="M21">
         <v>100</v>
       </c>
       <c r="N21">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O21">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>91.7</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -5235,7 +5235,7 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C22">
         <v>80</v>
@@ -5244,58 +5244,58 @@
         <v>75</v>
       </c>
       <c r="E22">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F22">
         <v>100</v>
       </c>
       <c r="G22">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H22">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I22">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J22">
         <v>80</v>
       </c>
       <c r="K22">
-        <v>70</v>
+        <v>72.5</v>
       </c>
       <c r="L22">
-        <v>113.3</v>
+        <v>97.2</v>
       </c>
       <c r="M22">
         <v>100</v>
       </c>
       <c r="N22">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O22">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>72.5</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>97.2</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -5303,7 +5303,7 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C23">
         <v>80</v>
@@ -5312,58 +5312,58 @@
         <v>75</v>
       </c>
       <c r="E23">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F23">
         <v>100</v>
       </c>
       <c r="G23">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H23">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I23">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J23">
         <v>80</v>
       </c>
       <c r="K23">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="L23">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M23">
         <v>100</v>
       </c>
       <c r="N23">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O23">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -5371,7 +5371,7 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C24">
         <v>90</v>
@@ -5380,58 +5380,58 @@
         <v>100</v>
       </c>
       <c r="E24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F24">
         <v>100</v>
       </c>
       <c r="G24">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H24">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I24">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J24">
         <v>90</v>
       </c>
       <c r="K24">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M24">
         <v>100</v>
       </c>
       <c r="N24">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O24">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -5439,7 +5439,7 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C25">
         <v>80</v>
@@ -5448,58 +5448,58 @@
         <v>85</v>
       </c>
       <c r="E25">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F25">
         <v>100</v>
       </c>
       <c r="G25">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H25">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I25">
-        <v>110</v>
+        <v>97.8</v>
       </c>
       <c r="J25">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="K25">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="L25">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M25">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N25">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O25">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>97.8</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -5507,7 +5507,7 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C26">
         <v>100</v>
@@ -5516,19 +5516,19 @@
         <v>100</v>
       </c>
       <c r="E26">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F26">
         <v>100</v>
       </c>
       <c r="G26">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H26">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I26">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J26">
         <v>100</v>
@@ -5537,37 +5537,37 @@
         <v>100</v>
       </c>
       <c r="L26">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M26">
         <v>100</v>
       </c>
       <c r="N26">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O26">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -5575,7 +5575,7 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C27">
         <v>100</v>
@@ -5584,58 +5584,58 @@
         <v>95</v>
       </c>
       <c r="E27">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F27">
         <v>100</v>
       </c>
       <c r="G27">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H27">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I27">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J27">
         <v>100</v>
       </c>
       <c r="K27">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="L27">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M27">
         <v>100</v>
       </c>
       <c r="N27">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O27">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -5652,58 +5652,58 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>6.7</v>
+        <v>5.6</v>
       </c>
       <c r="F28">
         <v>0</v>
       </c>
       <c r="G28">
-        <v>85.7</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="H28">
-        <v>93.3</v>
+        <v>87.5</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M28">
         <v>0</v>
       </c>
       <c r="N28">
-        <v>57.1</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="O28">
-        <v>33.3</v>
+        <v>59.4</v>
       </c>
       <c r="P28">
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="R28">
         <v>0</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T28">
         <v>0</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -5711,7 +5711,7 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C29">
         <v>100</v>
@@ -5720,19 +5720,19 @@
         <v>100</v>
       </c>
       <c r="E29">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F29">
         <v>100</v>
       </c>
       <c r="G29">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H29">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I29">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J29">
         <v>100</v>
@@ -5741,37 +5741,37 @@
         <v>100</v>
       </c>
       <c r="L29">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M29">
         <v>100</v>
       </c>
       <c r="N29">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O29">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -5779,7 +5779,7 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C30">
         <v>80</v>
@@ -5788,19 +5788,19 @@
         <v>95</v>
       </c>
       <c r="E30">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F30">
         <v>90</v>
       </c>
       <c r="G30">
-        <v>94.3</v>
+        <v>89.2</v>
       </c>
       <c r="H30">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="I30">
-        <v>110</v>
+        <v>97.8</v>
       </c>
       <c r="J30">
         <v>80</v>
@@ -5809,37 +5809,37 @@
         <v>95</v>
       </c>
       <c r="L30">
-        <v>93.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="M30">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N30">
-        <v>105.7</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="O30">
-        <v>106.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>97.8</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -5847,7 +5847,7 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C31">
         <v>80</v>
@@ -5856,58 +5856,58 @@
         <v>85</v>
       </c>
       <c r="E31">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F31">
         <v>90</v>
       </c>
       <c r="G31">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H31">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I31">
-        <v>105</v>
+        <v>95.7</v>
       </c>
       <c r="J31">
         <v>80</v>
       </c>
       <c r="K31">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="L31">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M31">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N31">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O31">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>95.7</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -5915,7 +5915,7 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C32">
         <v>80</v>
@@ -5924,19 +5924,19 @@
         <v>100</v>
       </c>
       <c r="E32">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F32">
         <v>100</v>
       </c>
       <c r="G32">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H32">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I32">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J32">
         <v>80</v>
@@ -5945,37 +5945,37 @@
         <v>100</v>
       </c>
       <c r="L32">
-        <v>113.3</v>
+        <v>97.2</v>
       </c>
       <c r="M32">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N32">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O32">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>97.2</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -5983,7 +5983,7 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C33">
         <v>100</v>
@@ -5992,58 +5992,58 @@
         <v>100</v>
       </c>
       <c r="E33">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F33">
         <v>100</v>
       </c>
       <c r="G33">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H33">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I33">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J33">
         <v>100</v>
       </c>
       <c r="K33">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L33">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="M33">
         <v>100</v>
       </c>
       <c r="N33">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O33">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>91.7</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -6051,7 +6051,7 @@
         <v>43</v>
       </c>
       <c r="B34">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C34">
         <v>80</v>
@@ -6060,58 +6060,58 @@
         <v>75</v>
       </c>
       <c r="E34">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F34">
         <v>90</v>
       </c>
       <c r="G34">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H34">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I34">
-        <v>105</v>
+        <v>95.7</v>
       </c>
       <c r="J34">
         <v>80</v>
       </c>
       <c r="K34">
-        <v>90</v>
+        <v>82.5</v>
       </c>
       <c r="L34">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M34">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N34">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O34">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>95.7</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -6119,7 +6119,7 @@
         <v>44</v>
       </c>
       <c r="B35">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C35">
         <v>90</v>
@@ -6128,58 +6128,58 @@
         <v>75</v>
       </c>
       <c r="E35">
-        <v>93.3</v>
+        <v>77.8</v>
       </c>
       <c r="F35">
         <v>100</v>
       </c>
       <c r="G35">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H35">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I35">
-        <v>110</v>
+        <v>97.8</v>
       </c>
       <c r="J35">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K35">
-        <v>80</v>
+        <v>77.5</v>
       </c>
       <c r="L35">
-        <v>120</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="M35">
         <v>100</v>
       </c>
       <c r="N35">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O35">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>97.8</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -6187,7 +6187,7 @@
         <v>45</v>
       </c>
       <c r="B36">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C36">
         <v>80</v>
@@ -6196,19 +6196,19 @@
         <v>80</v>
       </c>
       <c r="E36">
-        <v>93.3</v>
+        <v>77.8</v>
       </c>
       <c r="F36">
         <v>100</v>
       </c>
       <c r="G36">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H36">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I36">
-        <v>105</v>
+        <v>95.7</v>
       </c>
       <c r="J36">
         <v>80</v>
@@ -6217,37 +6217,37 @@
         <v>80</v>
       </c>
       <c r="L36">
-        <v>93.3</v>
+        <v>77.8</v>
       </c>
       <c r="M36">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N36">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O36">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>95.7</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>77.8</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -6255,7 +6255,7 @@
         <v>46</v>
       </c>
       <c r="B37">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C37">
         <v>80</v>
@@ -6264,58 +6264,58 @@
         <v>80</v>
       </c>
       <c r="E37">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F37">
         <v>100</v>
       </c>
       <c r="G37">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H37">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I37">
-        <v>105</v>
+        <v>95.7</v>
       </c>
       <c r="J37">
         <v>80</v>
       </c>
       <c r="K37">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L37">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M37">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N37">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O37">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>95.7</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -6323,7 +6323,7 @@
         <v>47</v>
       </c>
       <c r="B38">
-        <v>110</v>
+        <v>91.7</v>
       </c>
       <c r="C38">
         <v>80</v>
@@ -6332,58 +6332,58 @@
         <v>80</v>
       </c>
       <c r="E38">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="F38">
         <v>100</v>
       </c>
       <c r="G38">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H38">
-        <v>93.3</v>
+        <v>87.5</v>
       </c>
       <c r="I38">
-        <v>105</v>
+        <v>93.5</v>
       </c>
       <c r="J38">
         <v>80</v>
       </c>
       <c r="K38">
-        <v>85</v>
+        <v>82.5</v>
       </c>
       <c r="L38">
-        <v>120</v>
+        <v>77.8</v>
       </c>
       <c r="M38">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N38">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O38">
-        <v>106.7</v>
+        <v>93.8</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>93.5</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>77.8</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -6391,7 +6391,7 @@
         <v>48</v>
       </c>
       <c r="B39">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C39">
         <v>100</v>
@@ -6400,19 +6400,19 @@
         <v>100</v>
       </c>
       <c r="E39">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F39">
         <v>100</v>
       </c>
       <c r="G39">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="H39">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="I39">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J39">
         <v>100</v>
@@ -6421,37 +6421,37 @@
         <v>100</v>
       </c>
       <c r="L39">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M39">
         <v>100</v>
       </c>
       <c r="N39">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="O39">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/4ALCV - Estadisticos 20222.xlsx
+++ b/grupos/4ALCV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="105">
   <si>
     <t>Materia</t>
   </si>
@@ -206,18 +206,18 @@
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
+    <t>Gomez Lopez Javier</t>
+  </si>
+  <si>
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
-    <t>Gomez Lopez Javier</t>
+    <t>Rivera Serra Alma Lilian</t>
   </si>
   <si>
     <t>Mateos Sanchez Jorge</t>
   </si>
   <si>
-    <t>Rivera Serra Alma Lilian</t>
-  </si>
-  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
@@ -233,121 +233,106 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
+    <t>TENTZOHUA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SANJUAN</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>LEÓN</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>LAGUNES</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
   </si>
   <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RUGERIO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
+    <t>HIPOLITO</t>
   </si>
   <si>
     <t>MORENO</t>
   </si>
   <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
+    <t>MIROSLAVA</t>
+  </si>
+  <si>
+    <t>VANESSA AMAIRANY</t>
   </si>
   <si>
     <t>FATIMA</t>
   </si>
   <si>
+    <t>ALMA KAREN</t>
+  </si>
+  <si>
+    <t>RUBI</t>
+  </si>
+  <si>
+    <t>REYLI</t>
+  </si>
+  <si>
+    <t>EVELYN JOHANA</t>
+  </si>
+  <si>
+    <t>YARED</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>MARIA TERESA</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
     <t>ALONDRA YURIDIA</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>ALMA KAREN</t>
-  </si>
-  <si>
-    <t>REYLI</t>
-  </si>
-  <si>
-    <t>EVELYN JOHANA</t>
-  </si>
-  <si>
-    <t>YARED</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>REGINA ISABEL</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>DIANA IVONNE</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>CITLALI ESPERANZA</t>
-  </si>
-  <si>
-    <t>KIMBERLY</t>
   </si>
 </sst>
 </file>
@@ -895,19 +880,19 @@
         <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S4">
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U4">
         <v>-1</v>
@@ -984,19 +969,19 @@
         <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U5">
         <v>-1</v>
@@ -1005,10 +990,10 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>7</v>
@@ -1073,19 +1058,19 @@
         <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U6">
         <v>-1</v>
@@ -1097,7 +1082,7 @@
         <v>9</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y6">
         <v>5</v>
@@ -1162,19 +1147,19 @@
         <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U7">
         <v>-1</v>
@@ -1189,13 +1174,13 @@
         <v>6</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z7">
         <v>8</v>
       </c>
       <c r="AA7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB7">
         <v>5</v>
@@ -1251,19 +1236,19 @@
         <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S8">
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U8">
         <v>-1</v>
@@ -1275,7 +1260,7 @@
         <v>7</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y8">
         <v>6</v>
@@ -1340,19 +1325,19 @@
         <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S9">
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U9">
         <v>-1</v>
@@ -1364,7 +1349,7 @@
         <v>6</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -1429,19 +1414,19 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S10">
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U10">
         <v>-1</v>
@@ -1450,10 +1435,10 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>5</v>
@@ -1518,19 +1503,19 @@
         <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S11">
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U11">
         <v>-1</v>
@@ -1539,10 +1524,10 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y11">
         <v>5</v>
@@ -1551,7 +1536,7 @@
         <v>8</v>
       </c>
       <c r="AA11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB11">
         <v>9</v>
@@ -1607,19 +1592,19 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S12">
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U12">
         <v>-1</v>
@@ -1628,10 +1613,10 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <v>6</v>
@@ -1640,7 +1625,7 @@
         <v>8</v>
       </c>
       <c r="AA12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB12">
         <v>5</v>
@@ -1696,19 +1681,19 @@
         <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S13">
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U13">
         <v>-1</v>
@@ -1729,7 +1714,7 @@
         <v>7</v>
       </c>
       <c r="AA13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB13">
         <v>6</v>
@@ -1785,19 +1770,19 @@
         <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U14">
         <v>-1</v>
@@ -1806,13 +1791,13 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z14">
         <v>9</v>
@@ -1850,7 +1835,7 @@
         <v>10</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U15">
         <v>-1</v>
@@ -1859,7 +1844,7 @@
         <v>-1</v>
       </c>
       <c r="AA15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB15">
         <v>10</v>
@@ -1915,19 +1900,19 @@
         <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U16">
         <v>-1</v>
@@ -1936,13 +1921,13 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z16">
         <v>7</v>
@@ -2004,19 +1989,19 @@
         <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S17">
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U17">
         <v>-1</v>
@@ -2025,10 +2010,10 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>5</v>
@@ -2037,7 +2022,7 @@
         <v>7</v>
       </c>
       <c r="AA17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB17">
         <v>7</v>
@@ -2093,19 +2078,19 @@
         <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U18">
         <v>-1</v>
@@ -2120,7 +2105,7 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z18">
         <v>8</v>
@@ -2182,19 +2167,19 @@
         <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U19">
         <v>-1</v>
@@ -2203,13 +2188,13 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z19">
         <v>9</v>
@@ -2247,7 +2232,7 @@
         <v>8</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U20">
         <v>-1</v>
@@ -2312,19 +2297,19 @@
         <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>-1</v>
@@ -2336,16 +2321,16 @@
         <v>7</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z21">
         <v>7</v>
       </c>
       <c r="AA21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB21">
         <v>10</v>
@@ -2401,19 +2386,19 @@
         <v>6</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S22">
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U22">
         <v>-1</v>
@@ -2490,19 +2475,19 @@
         <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U23">
         <v>-1</v>
@@ -2514,10 +2499,10 @@
         <v>8</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z23">
         <v>7</v>
@@ -2579,19 +2564,19 @@
         <v>9</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S24">
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U24">
         <v>-1</v>
@@ -2603,10 +2588,10 @@
         <v>8</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z24">
         <v>9</v>
@@ -2668,19 +2653,19 @@
         <v>7</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S25">
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U25">
         <v>-1</v>
@@ -2692,7 +2677,7 @@
         <v>7</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y25">
         <v>5</v>
@@ -2757,19 +2742,19 @@
         <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U26">
         <v>-1</v>
@@ -2781,10 +2766,10 @@
         <v>7</v>
       </c>
       <c r="X26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z26">
         <v>9</v>
@@ -2846,19 +2831,19 @@
         <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U27">
         <v>-1</v>
@@ -2870,10 +2855,10 @@
         <v>7</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z27">
         <v>9</v>
@@ -2935,19 +2920,19 @@
         <v>5</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S28">
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U28">
         <v>-1</v>
@@ -3024,19 +3009,19 @@
         <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U29">
         <v>-1</v>
@@ -3048,16 +3033,16 @@
         <v>9</v>
       </c>
       <c r="X29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z29">
         <v>9</v>
       </c>
       <c r="AA29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB29">
         <v>10</v>
@@ -3113,19 +3098,19 @@
         <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S30">
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U30">
         <v>-1</v>
@@ -3137,10 +3122,10 @@
         <v>7</v>
       </c>
       <c r="X30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z30">
         <v>8</v>
@@ -3202,19 +3187,19 @@
         <v>6</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S31">
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U31">
         <v>-1</v>
@@ -3223,7 +3208,7 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X31">
         <v>6</v>
@@ -3235,7 +3220,7 @@
         <v>6</v>
       </c>
       <c r="AA31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB31">
         <v>7</v>
@@ -3291,19 +3276,19 @@
         <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S32">
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U32">
         <v>-1</v>
@@ -3312,13 +3297,13 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X32">
         <v>7</v>
       </c>
       <c r="Y32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z32">
         <v>8</v>
@@ -3380,19 +3365,19 @@
         <v>9</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S33">
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U33">
         <v>-1</v>
@@ -3407,7 +3392,7 @@
         <v>6</v>
       </c>
       <c r="Y33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z33">
         <v>7</v>
@@ -3469,19 +3454,19 @@
         <v>9</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S34">
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U34">
         <v>-1</v>
@@ -3490,13 +3475,13 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X34">
         <v>6</v>
       </c>
       <c r="Y34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z34">
         <v>7</v>
@@ -3558,19 +3543,19 @@
         <v>9</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S35">
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U35">
         <v>-1</v>
@@ -3579,7 +3564,7 @@
         <v>-1</v>
       </c>
       <c r="W35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X35">
         <v>6</v>
@@ -3591,7 +3576,7 @@
         <v>6</v>
       </c>
       <c r="AA35">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB35">
         <v>7</v>
@@ -3647,19 +3632,19 @@
         <v>7</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S36">
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U36">
         <v>-1</v>
@@ -3680,7 +3665,7 @@
         <v>6</v>
       </c>
       <c r="AA36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB36">
         <v>7</v>
@@ -3736,19 +3721,19 @@
         <v>6</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S37">
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U37">
         <v>-1</v>
@@ -3757,7 +3742,7 @@
         <v>-1</v>
       </c>
       <c r="W37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X37">
         <v>5</v>
@@ -3825,19 +3810,19 @@
         <v>6</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S38">
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U38">
         <v>-1</v>
@@ -3914,19 +3899,19 @@
         <v>10</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S39">
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U39">
         <v>-1</v>
@@ -3941,7 +3926,7 @@
         <v>7</v>
       </c>
       <c r="Y39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z39">
         <v>8</v>
@@ -4125,13 +4110,13 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q4">
-        <v>80</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="R4">
-        <v>87.5</v>
+        <v>78.3</v>
       </c>
       <c r="S4">
         <v>91.7</v>
@@ -4196,16 +4181,16 @@
         <v>100</v>
       </c>
       <c r="Q5">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="R5">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="S5">
         <v>100</v>
       </c>
       <c r="T5">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U5">
         <v>100</v>
@@ -4264,16 +4249,16 @@
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>80</v>
+        <v>81.3</v>
       </c>
       <c r="R6">
-        <v>67.5</v>
+        <v>70</v>
       </c>
       <c r="S6">
         <v>100</v>
       </c>
       <c r="T6">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="U6">
         <v>100</v>
@@ -4329,19 +4314,19 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="Q7">
-        <v>77.5</v>
+        <v>82.8</v>
       </c>
       <c r="R7">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="S7">
         <v>100</v>
       </c>
       <c r="T7">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="U7">
         <v>100</v>
@@ -4400,10 +4385,10 @@
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R8">
-        <v>92.5</v>
+        <v>91.7</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -4465,13 +4450,13 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="Q9">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R9">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="S9">
         <v>88.90000000000001</v>
@@ -4533,7 +4518,7 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -4601,19 +4586,19 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="Q11">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="R11">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="S11">
         <v>91.7</v>
       </c>
       <c r="T11">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="U11">
         <v>100</v>
@@ -4669,19 +4654,19 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>95.7</v>
+        <v>97</v>
       </c>
       <c r="Q12">
-        <v>80</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="R12">
-        <v>77.5</v>
+        <v>81.7</v>
       </c>
       <c r="S12">
         <v>100</v>
       </c>
       <c r="T12">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="U12">
         <v>100</v>
@@ -4737,19 +4722,19 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="Q13">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R13">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="S13">
         <v>86.09999999999999</v>
       </c>
       <c r="T13">
-        <v>97.5</v>
+        <v>96.7</v>
       </c>
       <c r="U13">
         <v>100</v>
@@ -4808,7 +4793,7 @@
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="R14">
         <v>100</v>
@@ -4849,7 +4834,7 @@
         <v>100</v>
       </c>
       <c r="T15">
-        <v>92.5</v>
+        <v>91.7</v>
       </c>
       <c r="U15">
         <v>100</v>
@@ -4905,19 +4890,19 @@
         <v>100</v>
       </c>
       <c r="P16">
-        <v>95.7</v>
+        <v>97</v>
       </c>
       <c r="Q16">
-        <v>80</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="R16">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="S16">
         <v>88.90000000000001</v>
       </c>
       <c r="T16">
-        <v>92.5</v>
+        <v>93.3</v>
       </c>
       <c r="U16">
         <v>100</v>
@@ -4976,10 +4961,10 @@
         <v>100</v>
       </c>
       <c r="Q17">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R17">
-        <v>90</v>
+        <v>83.3</v>
       </c>
       <c r="S17">
         <v>100</v>
@@ -5041,19 +5026,19 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="Q18">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="R18">
-        <v>90</v>
+        <v>88.3</v>
       </c>
       <c r="S18">
         <v>100</v>
       </c>
       <c r="T18">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U18">
         <v>100</v>
@@ -5153,7 +5138,7 @@
         <v>100</v>
       </c>
       <c r="T20">
-        <v>97.5</v>
+        <v>96.7</v>
       </c>
       <c r="U20">
         <v>100</v>
@@ -5212,7 +5197,7 @@
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>80</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="R21">
         <v>90</v>
@@ -5280,10 +5265,10 @@
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>80</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="R22">
-        <v>72.5</v>
+        <v>71.7</v>
       </c>
       <c r="S22">
         <v>97.2</v>
@@ -5348,7 +5333,7 @@
         <v>100</v>
       </c>
       <c r="Q23">
-        <v>80</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="R23">
         <v>85</v>
@@ -5416,10 +5401,10 @@
         <v>100</v>
       </c>
       <c r="Q24">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R24">
-        <v>97.5</v>
+        <v>96.7</v>
       </c>
       <c r="S24">
         <v>100</v>
@@ -5481,19 +5466,19 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="Q25">
+        <v>87.5</v>
+      </c>
+      <c r="R25">
         <v>85</v>
       </c>
-      <c r="R25">
-        <v>92.5</v>
-      </c>
       <c r="S25">
         <v>100</v>
       </c>
       <c r="T25">
-        <v>97.5</v>
+        <v>96.7</v>
       </c>
       <c r="U25">
         <v>100</v>
@@ -5555,7 +5540,7 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -5623,7 +5608,7 @@
         <v>100</v>
       </c>
       <c r="R27">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="S27">
         <v>100</v>
@@ -5688,7 +5673,7 @@
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -5697,7 +5682,7 @@
         <v>2.8</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="U28">
         <v>67.59999999999999</v>
@@ -5759,7 +5744,7 @@
         <v>100</v>
       </c>
       <c r="R29">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="S29">
         <v>100</v>
@@ -5821,10 +5806,10 @@
         <v>96.90000000000001</v>
       </c>
       <c r="P30">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="Q30">
-        <v>80</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="R30">
         <v>95</v>
@@ -5833,7 +5818,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="T30">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U30">
         <v>94.59999999999999</v>
@@ -5889,10 +5874,10 @@
         <v>100</v>
       </c>
       <c r="P31">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="Q31">
-        <v>80</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="R31">
         <v>80</v>
@@ -5901,7 +5886,7 @@
         <v>100</v>
       </c>
       <c r="T31">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U31">
         <v>100</v>
@@ -5960,16 +5945,16 @@
         <v>100</v>
       </c>
       <c r="Q32">
-        <v>80</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="R32">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S32">
         <v>97.2</v>
       </c>
       <c r="T32">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="U32">
         <v>100</v>
@@ -6028,10 +6013,10 @@
         <v>100</v>
       </c>
       <c r="Q33">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R33">
-        <v>97.5</v>
+        <v>91.7</v>
       </c>
       <c r="S33">
         <v>91.7</v>
@@ -6093,19 +6078,19 @@
         <v>100</v>
       </c>
       <c r="P34">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="Q34">
-        <v>80</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="R34">
-        <v>82.5</v>
+        <v>85</v>
       </c>
       <c r="S34">
         <v>100</v>
       </c>
       <c r="T34">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U34">
         <v>100</v>
@@ -6161,19 +6146,19 @@
         <v>100</v>
       </c>
       <c r="P35">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="Q35">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="R35">
-        <v>77.5</v>
+        <v>80</v>
       </c>
       <c r="S35">
         <v>88.90000000000001</v>
       </c>
       <c r="T35">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="U35">
         <v>100</v>
@@ -6229,19 +6214,19 @@
         <v>100</v>
       </c>
       <c r="P36">
-        <v>95.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="Q36">
-        <v>80</v>
+        <v>81.3</v>
       </c>
       <c r="R36">
-        <v>80</v>
+        <v>71.7</v>
       </c>
       <c r="S36">
         <v>77.8</v>
       </c>
       <c r="T36">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="U36">
         <v>100</v>
@@ -6297,10 +6282,10 @@
         <v>100</v>
       </c>
       <c r="P37">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="Q37">
-        <v>80</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="R37">
         <v>75</v>
@@ -6309,7 +6294,7 @@
         <v>100</v>
       </c>
       <c r="T37">
-        <v>97.5</v>
+        <v>96.7</v>
       </c>
       <c r="U37">
         <v>100</v>
@@ -6365,19 +6350,19 @@
         <v>93.8</v>
       </c>
       <c r="P38">
-        <v>93.5</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="Q38">
-        <v>80</v>
+        <v>81.3</v>
       </c>
       <c r="R38">
-        <v>82.5</v>
+        <v>83.3</v>
       </c>
       <c r="S38">
         <v>77.8</v>
       </c>
       <c r="T38">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="U38">
         <v>100</v>
@@ -6436,7 +6421,7 @@
         <v>100</v>
       </c>
       <c r="Q39">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R39">
         <v>100</v>
@@ -6517,19 +6502,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>32.4</v>
+        <v>58.8</v>
       </c>
       <c r="G2" s="2">
-        <v>67.59999999999999</v>
+        <v>41.2</v>
       </c>
       <c r="H2">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6540,7 +6525,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
@@ -6549,19 +6534,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2">
-        <v>67.59999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G3" s="2">
-        <v>32.4</v>
+        <v>20.6</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6572,7 +6557,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
@@ -6581,19 +6566,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2">
-        <v>79.40000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="G4" s="2">
-        <v>20.6</v>
+        <v>14.7</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6604,7 +6589,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
@@ -6613,19 +6598,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2">
-        <v>86.09999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6636,7 +6621,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
@@ -6645,19 +6630,19 @@
         <v>36</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>88.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="G6" s="2">
-        <v>11.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6671,7 +6656,7 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C7">
         <v>36</v>
@@ -6771,7 +6756,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6803,19 +6788,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920086</v>
+        <v>21330051920078</v>
       </c>
       <c r="B2" t="s">
         <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>63</v>
@@ -6826,16 +6811,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920086</v>
+        <v>21330051920078</v>
       </c>
       <c r="B3" t="s">
         <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -6849,22 +6834,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920100</v>
+        <v>21330051920082</v>
       </c>
       <c r="B4" t="s">
         <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6872,22 +6857,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920100</v>
+        <v>21330051920082</v>
       </c>
       <c r="B5" t="s">
         <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6895,19 +6880,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920102</v>
+        <v>21330051920086</v>
       </c>
       <c r="B6" t="s">
         <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
         <v>62</v>
@@ -6918,16 +6903,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920102</v>
+        <v>21330051920086</v>
       </c>
       <c r="B7" t="s">
         <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -6947,16 +6932,16 @@
         <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6970,16 +6955,16 @@
         <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6987,22 +6972,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920378</v>
+        <v>21330051920107</v>
       </c>
       <c r="B10" t="s">
         <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7010,16 +6995,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920075</v>
+        <v>21330051920107</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -7033,16 +7018,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920076</v>
+        <v>20330051920378</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -7056,16 +7041,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920080</v>
+        <v>21330051920075</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -7079,16 +7064,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920083</v>
+        <v>21330051920076</v>
       </c>
       <c r="B14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" t="s">
         <v>79</v>
       </c>
-      <c r="C14" t="s">
-        <v>89</v>
-      </c>
       <c r="D14" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -7102,22 +7087,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920084</v>
+        <v>21330051920077</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -7125,22 +7110,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920085</v>
+        <v>21330051920260</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D16" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -7148,16 +7133,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920092</v>
+        <v>21330051920080</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
@@ -7171,16 +7156,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920097</v>
+        <v>21330051920092</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D18" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E18" t="s">
         <v>7</v>
@@ -7194,16 +7179,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920101</v>
+        <v>21330051920100</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D19" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
@@ -7212,29 +7197,6 @@
         <v>61</v>
       </c>
       <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920383</v>
-      </c>
-      <c r="B20" t="s">
-        <v>84</v>
-      </c>
-      <c r="C20" t="s">
-        <v>73</v>
-      </c>
-      <c r="D20" t="s">
-        <v>109</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>61</v>
-      </c>
-      <c r="G20">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4ALCV - Estadisticos 20222.xlsx
+++ b/grupos/4ALCV - Estadisticos 20222.xlsx
@@ -889,7 +889,7 @@
         <v>5</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T4">
         <v>6</v>
@@ -978,7 +978,7 @@
         <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>9</v>
@@ -999,7 +999,7 @@
         <v>7</v>
       </c>
       <c r="Z5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA5">
         <v>9</v>
@@ -1067,7 +1067,7 @@
         <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T6">
         <v>7</v>
@@ -1088,7 +1088,7 @@
         <v>5</v>
       </c>
       <c r="Z6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA6">
         <v>6</v>
@@ -1156,7 +1156,7 @@
         <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>5</v>
@@ -1245,7 +1245,7 @@
         <v>7</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -1334,7 +1334,7 @@
         <v>7</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
         <v>9</v>
@@ -1423,7 +1423,7 @@
         <v>5</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
         <v>9</v>
@@ -1512,7 +1512,7 @@
         <v>5</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
         <v>5</v>
@@ -1601,7 +1601,7 @@
         <v>6</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>9</v>
@@ -1690,7 +1690,7 @@
         <v>5</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
         <v>8</v>
@@ -1779,7 +1779,7 @@
         <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -1800,7 +1800,7 @@
         <v>8</v>
       </c>
       <c r="Z14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA14">
         <v>9</v>
@@ -1909,7 +1909,7 @@
         <v>7</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
         <v>9</v>
@@ -1998,7 +1998,7 @@
         <v>5</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
         <v>9</v>
@@ -2087,7 +2087,7 @@
         <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>9</v>
@@ -2176,7 +2176,7 @@
         <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
         <v>10</v>
@@ -2306,7 +2306,7 @@
         <v>7</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
         <v>8</v>
@@ -2395,7 +2395,7 @@
         <v>5</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
         <v>6</v>
@@ -2484,7 +2484,7 @@
         <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
         <v>7</v>
@@ -2505,7 +2505,7 @@
         <v>7</v>
       </c>
       <c r="Z23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA23">
         <v>7</v>
@@ -2573,7 +2573,7 @@
         <v>8</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -2662,7 +2662,7 @@
         <v>5</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T25">
         <v>6</v>
@@ -2683,7 +2683,7 @@
         <v>5</v>
       </c>
       <c r="Z25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA25">
         <v>7</v>
@@ -2751,7 +2751,7 @@
         <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
         <v>9</v>
@@ -2840,7 +2840,7 @@
         <v>8</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
         <v>10</v>
@@ -2861,7 +2861,7 @@
         <v>6</v>
       </c>
       <c r="Z27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA27">
         <v>9</v>
@@ -2929,7 +2929,7 @@
         <v>5</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T28">
         <v>7</v>
@@ -3018,7 +3018,7 @@
         <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
         <v>7</v>
@@ -3107,7 +3107,7 @@
         <v>5</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
         <v>7</v>
@@ -3196,7 +3196,7 @@
         <v>5</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
         <v>8</v>
@@ -3285,7 +3285,7 @@
         <v>7</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T32">
         <v>10</v>
@@ -3374,7 +3374,7 @@
         <v>8</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T33">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>7</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T34">
         <v>6</v>
@@ -3552,7 +3552,7 @@
         <v>5</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T35">
         <v>0</v>
@@ -3641,7 +3641,7 @@
         <v>5</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T36">
         <v>8</v>
@@ -3730,7 +3730,7 @@
         <v>7</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T37">
         <v>7</v>
@@ -3819,7 +3819,7 @@
         <v>5</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T38">
         <v>5</v>
@@ -3908,7 +3908,7 @@
         <v>10</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T39">
         <v>8</v>
@@ -4119,7 +4119,7 @@
         <v>78.3</v>
       </c>
       <c r="S4">
-        <v>91.7</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="T4">
         <v>100</v>
@@ -4459,7 +4459,7 @@
         <v>96.7</v>
       </c>
       <c r="S9">
-        <v>88.90000000000001</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="T9">
         <v>100</v>
@@ -4595,7 +4595,7 @@
         <v>90</v>
       </c>
       <c r="S11">
-        <v>91.7</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="T11">
         <v>91.7</v>
@@ -4731,7 +4731,7 @@
         <v>93.3</v>
       </c>
       <c r="S13">
-        <v>86.09999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="T13">
         <v>96.7</v>
@@ -4899,7 +4899,7 @@
         <v>95</v>
       </c>
       <c r="S16">
-        <v>88.90000000000001</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="T16">
         <v>93.3</v>
@@ -5203,7 +5203,7 @@
         <v>90</v>
       </c>
       <c r="S21">
-        <v>91.7</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="T21">
         <v>100</v>
@@ -5271,7 +5271,7 @@
         <v>71.7</v>
       </c>
       <c r="S22">
-        <v>97.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="T22">
         <v>100</v>
@@ -5679,7 +5679,7 @@
         <v>0</v>
       </c>
       <c r="S28">
-        <v>2.8</v>
+        <v>35.2</v>
       </c>
       <c r="T28">
         <v>33.3</v>
@@ -5815,7 +5815,7 @@
         <v>95</v>
       </c>
       <c r="S30">
-        <v>88.90000000000001</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="T30">
         <v>96.7</v>
@@ -5951,7 +5951,7 @@
         <v>95</v>
       </c>
       <c r="S32">
-        <v>97.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="T32">
         <v>98.3</v>
@@ -6019,7 +6019,7 @@
         <v>91.7</v>
       </c>
       <c r="S33">
-        <v>91.7</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="T33">
         <v>100</v>
@@ -6155,7 +6155,7 @@
         <v>80</v>
       </c>
       <c r="S35">
-        <v>88.90000000000001</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="T35">
         <v>66.7</v>
@@ -6223,7 +6223,7 @@
         <v>71.7</v>
       </c>
       <c r="S36">
-        <v>77.8</v>
+        <v>85.2</v>
       </c>
       <c r="T36">
         <v>93.3</v>
@@ -6359,7 +6359,7 @@
         <v>83.3</v>
       </c>
       <c r="S38">
-        <v>77.8</v>
+        <v>85.2</v>
       </c>
       <c r="T38">
         <v>93.3</v>
@@ -6706,7 +6706,7 @@
         <v>2.9</v>
       </c>
       <c r="H8">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="I8">
         <v>0</v>

--- a/grupos/4ALCV - Estadisticos 20222.xlsx
+++ b/grupos/4ALCV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="101">
   <si>
     <t>Materia</t>
   </si>
@@ -212,15 +212,15 @@
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
+    <t>Mateos Sanchez Jorge</t>
+  </si>
+  <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>Rivera Serra Alma Lilian</t>
   </si>
   <si>
-    <t>Mateos Sanchez Jorge</t>
-  </si>
-  <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -236,9 +236,6 @@
     <t>GARCIA</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
@@ -269,9 +266,6 @@
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>BRETON</t>
-  </si>
-  <si>
     <t>RIVERA</t>
   </si>
   <si>
@@ -284,9 +278,6 @@
     <t>ARIAS</t>
   </si>
   <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
     <t>CAMPOS</t>
   </si>
   <si>
@@ -302,9 +293,6 @@
     <t>MIROSLAVA</t>
   </si>
   <si>
-    <t>VANESSA AMAIRANY</t>
-  </si>
-  <si>
     <t>FATIMA</t>
   </si>
   <si>
@@ -323,10 +311,10 @@
     <t>YARED</t>
   </si>
   <si>
+    <t>MARIA TERESA</t>
+  </si>
+  <si>
     <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>MARIA TERESA</t>
   </si>
   <si>
     <t>JOSE JULIAN</t>
@@ -895,10 +883,10 @@
         <v>6</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>5</v>
@@ -919,7 +907,7 @@
         <v>8</v>
       </c>
       <c r="AC4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -984,10 +972,10 @@
         <v>9</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W5">
         <v>8</v>
@@ -1073,10 +1061,10 @@
         <v>7</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W6">
         <v>9</v>
@@ -1162,10 +1150,10 @@
         <v>5</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W7">
         <v>7</v>
@@ -1183,10 +1171,10 @@
         <v>6</v>
       </c>
       <c r="AB7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC7">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1251,10 +1239,10 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W8">
         <v>7</v>
@@ -1340,10 +1328,10 @@
         <v>9</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>6</v>
@@ -1429,10 +1417,10 @@
         <v>9</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W10">
         <v>7</v>
@@ -1518,10 +1506,10 @@
         <v>5</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>6</v>
@@ -1607,10 +1595,10 @@
         <v>9</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>6</v>
@@ -1628,10 +1616,10 @@
         <v>7</v>
       </c>
       <c r="AB12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC12">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1696,10 +1684,10 @@
         <v>8</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>5</v>
@@ -1717,10 +1705,10 @@
         <v>6</v>
       </c>
       <c r="AB13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC13">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1785,10 +1773,10 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W14">
         <v>8</v>
@@ -1838,10 +1826,10 @@
         <v>6</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA15">
         <v>7</v>
@@ -1915,10 +1903,10 @@
         <v>9</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W16">
         <v>6</v>
@@ -1936,10 +1924,10 @@
         <v>7</v>
       </c>
       <c r="AB16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC16">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2004,10 +1992,10 @@
         <v>9</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>7</v>
@@ -2025,7 +2013,7 @@
         <v>8</v>
       </c>
       <c r="AB17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC17">
         <v>8</v>
@@ -2093,10 +2081,10 @@
         <v>9</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W18">
         <v>6</v>
@@ -2182,10 +2170,10 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W19">
         <v>8</v>
@@ -2235,10 +2223,10 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA20">
         <v>10</v>
@@ -2247,7 +2235,7 @@
         <v>8</v>
       </c>
       <c r="AC20">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2312,10 +2300,10 @@
         <v>8</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W21">
         <v>7</v>
@@ -2401,10 +2389,10 @@
         <v>6</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>7</v>
@@ -2422,7 +2410,7 @@
         <v>7</v>
       </c>
       <c r="AB22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC22">
         <v>7</v>
@@ -2490,10 +2478,10 @@
         <v>7</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W23">
         <v>8</v>
@@ -2579,10 +2567,10 @@
         <v>10</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W24">
         <v>8</v>
@@ -2668,10 +2656,10 @@
         <v>6</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>7</v>
@@ -2689,7 +2677,7 @@
         <v>7</v>
       </c>
       <c r="AB25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC25">
         <v>8</v>
@@ -2757,10 +2745,10 @@
         <v>9</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W26">
         <v>7</v>
@@ -2846,10 +2834,10 @@
         <v>10</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W27">
         <v>7</v>
@@ -2935,10 +2923,10 @@
         <v>7</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W28">
         <v>5</v>
@@ -3024,10 +3012,10 @@
         <v>7</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W29">
         <v>9</v>
@@ -3113,10 +3101,10 @@
         <v>7</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W30">
         <v>7</v>
@@ -3202,10 +3190,10 @@
         <v>8</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>6</v>
@@ -3223,10 +3211,10 @@
         <v>7</v>
       </c>
       <c r="AB31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC31">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3291,10 +3279,10 @@
         <v>10</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W32">
         <v>6</v>
@@ -3380,10 +3368,10 @@
         <v>8</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W33">
         <v>7</v>
@@ -3469,10 +3457,10 @@
         <v>6</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W34">
         <v>6</v>
@@ -3558,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W35">
         <v>6</v>
@@ -3647,10 +3635,10 @@
         <v>8</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W36">
         <v>5</v>
@@ -3668,10 +3656,10 @@
         <v>6</v>
       </c>
       <c r="AB36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC36">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:29">
@@ -3736,10 +3724,10 @@
         <v>7</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W37">
         <v>6</v>
@@ -3757,7 +3745,7 @@
         <v>6</v>
       </c>
       <c r="AB37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC37">
         <v>7</v>
@@ -3825,10 +3813,10 @@
         <v>5</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W38">
         <v>5</v>
@@ -3846,10 +3834,10 @@
         <v>5</v>
       </c>
       <c r="AB38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC38">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:29">
@@ -3914,10 +3902,10 @@
         <v>8</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W39">
         <v>7</v>
@@ -5685,10 +5673,10 @@
         <v>33.3</v>
       </c>
       <c r="U28">
-        <v>67.59999999999999</v>
+        <v>44.6</v>
       </c>
       <c r="V28">
-        <v>59.4</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -5821,10 +5809,10 @@
         <v>96.7</v>
       </c>
       <c r="U30">
-        <v>94.59999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="V30">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -6229,7 +6217,7 @@
         <v>93.3</v>
       </c>
       <c r="U36">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="V36">
         <v>100</v>
@@ -6368,7 +6356,7 @@
         <v>100</v>
       </c>
       <c r="V38">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -6589,7 +6577,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
@@ -6598,19 +6586,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>88.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="G5" s="2">
-        <v>11.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6621,28 +6609,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
       </c>
       <c r="C6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D6">
         <v>33</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>91.7</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>8.300000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6653,28 +6641,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C7">
         <v>36</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>91.7</v>
+        <v>97.2</v>
       </c>
       <c r="G7" s="2">
-        <v>8.300000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="H7">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6685,28 +6673,28 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>66</v>
       </c>
       <c r="C8">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D8">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>97.09999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="G8" s="2">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="H8">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6756,7 +6744,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6794,10 +6782,10 @@
         <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -6817,10 +6805,10 @@
         <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -6834,22 +6822,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920082</v>
+        <v>21330051920086</v>
       </c>
       <c r="B4" t="s">
         <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6857,22 +6845,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920082</v>
+        <v>21330051920086</v>
       </c>
       <c r="B5" t="s">
         <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6880,22 +6868,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920086</v>
+        <v>21330051920103</v>
       </c>
       <c r="B6" t="s">
         <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6903,22 +6891,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920086</v>
+        <v>21330051920103</v>
       </c>
       <c r="B7" t="s">
         <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6926,22 +6914,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920103</v>
+        <v>21330051920107</v>
       </c>
       <c r="B8" t="s">
         <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6949,22 +6937,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920103</v>
+        <v>21330051920107</v>
       </c>
       <c r="B9" t="s">
         <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6972,22 +6960,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920107</v>
+        <v>20330051920378</v>
       </c>
       <c r="B10" t="s">
         <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -6995,16 +6983,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920107</v>
+        <v>21330051920075</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
         <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -7018,16 +7006,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920378</v>
+        <v>21330051920076</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -7041,22 +7029,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920075</v>
+        <v>21330051920260</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7064,16 +7052,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920076</v>
+        <v>21330051920080</v>
       </c>
       <c r="B14" t="s">
         <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -7087,22 +7075,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920077</v>
+        <v>21330051920092</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
         <v>88</v>
       </c>
       <c r="D15" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -7110,93 +7098,24 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920260</v>
+        <v>21330051920100</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
         <v>89</v>
       </c>
       <c r="D16" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920080</v>
-      </c>
-      <c r="B17" t="s">
-        <v>79</v>
-      </c>
-      <c r="C17" t="s">
-        <v>90</v>
-      </c>
-      <c r="D17" t="s">
-        <v>101</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>61</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920092</v>
-      </c>
-      <c r="B18" t="s">
-        <v>80</v>
-      </c>
-      <c r="C18" t="s">
-        <v>91</v>
-      </c>
-      <c r="D18" t="s">
-        <v>103</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>61</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920100</v>
-      </c>
-      <c r="B19" t="s">
-        <v>81</v>
-      </c>
-      <c r="C19" t="s">
-        <v>92</v>
-      </c>
-      <c r="D19" t="s">
-        <v>104</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>61</v>
-      </c>
-      <c r="G19">
         <v>5</v>
       </c>
     </row>
